--- a/financials/TCX/TCX.xlsx
+++ b/financials/TCX/TCX.xlsx
@@ -11,6 +11,8 @@
     <sheet name="income_statement" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="cash_flow" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="chi_so_tai_chinh" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Dự báo tăng trưởng" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Hiệu quả thực hiện kế hoạch" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,13 +21,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
-    <numFmt numFmtId="166" formatCode="0.00&quot;x&quot;"/>
-    <numFmt numFmtId="167" formatCode="#,##0 &quot;ngày&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0;\(#,##0\);&quot;-&quot;"/>
+    <numFmt numFmtId="167" formatCode="#,##0;\(#,##0\);\-"/>
+    <numFmt numFmtId="168" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -47,48 +50,76 @@
     </font>
     <font>
       <name val="Tahoma"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <name val="Tahoma"/>
+      <family val="2"/>
       <b val="1"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Tahoma"/>
-      <b val="1"/>
-    </font>
-    <font>
-      <name val="Tahoma"/>
-      <b val="1"/>
-      <i val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Tahoma"/>
+      <family val="2"/>
       <b val="1"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Tahoma"/>
-      <i val="1"/>
-      <color rgb="00808080"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Tahoma"/>
-      <color rgb="00000000"/>
+      <family val="2"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Tahoma"/>
-      <color rgb="00008000"/>
+      <family val="2"/>
+      <i val="1"/>
+      <color rgb="FF808080"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <color rgb="FF008000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF008000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF7030A0"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <color rgb="FF7030A0"/>
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -102,11 +133,35 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
+        <fgColor theme="5" tint="0.7999816888943144"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.7999816888943144"/>
+        <bgColor theme="7" tint="0.5999938962981048"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.7999816888943144"/>
+        <bgColor theme="7" tint="0.7999816888943144"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.5999938962981048"/>
+        <bgColor theme="7" tint="0.5999938962981048"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9E1F2"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -134,11 +189,26 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
@@ -148,24 +218,80 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="4" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="6" fillId="3" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="5" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="6" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="6" fillId="3" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="43" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="13" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="14" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="14" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="4">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="9"/>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -14076,1727 +14202,3228 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:J46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="56" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
-    <col width="3" customWidth="1" min="10" max="10"/>
+    <col width="13.109375" customWidth="1" min="2" max="2"/>
+    <col width="20.5546875" customWidth="1" min="9" max="9"/>
+    <col width="19.33203125" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
+    <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>CHỈ SỐ TÀI CHÍNH — TCX</t>
-        </is>
+          <t>Chỉ tiêu</t>
+        </is>
+      </c>
+      <c r="B1" s="6">
+        <f>balance_sheet!B1</f>
+        <v/>
+      </c>
+      <c r="C1" s="6">
+        <f>balance_sheet!C1</f>
+        <v/>
+      </c>
+      <c r="D1" s="6">
+        <f>balance_sheet!D1</f>
+        <v/>
+      </c>
+      <c r="E1" s="6">
+        <f>balance_sheet!E1</f>
+        <v/>
+      </c>
+      <c r="F1" s="6">
+        <f>balance_sheet!F1</f>
+        <v/>
+      </c>
+      <c r="G1" s="6">
+        <f>balance_sheet!G1</f>
+        <v/>
+      </c>
+      <c r="H1" s="6">
+        <f>balance_sheet!H1</f>
+        <v/>
+      </c>
+      <c r="I1" s="6">
+        <f>balance_sheet!I1</f>
+        <v/>
+      </c>
+      <c r="J1" s="6" t="n">
+        <v>2026</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>I. CHỈ SỐ TÀI CHÍNH</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="n"/>
-      <c r="C2" s="7" t="n"/>
-      <c r="D2" s="7" t="n"/>
-      <c r="E2" s="7" t="n"/>
-      <c r="F2" s="7" t="n"/>
-      <c r="G2" s="7" t="n"/>
-      <c r="H2" s="7" t="n"/>
-      <c r="I2" s="7" t="n"/>
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>ROE</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C2" s="8">
+        <f>IFERROR(C$46/((C$34+B$34)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="D2" s="8">
+        <f>IFERROR(D$46/((D$34+C$34)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="E2" s="8">
+        <f>IFERROR(E$46/((E$34+D$34)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="F2" s="8">
+        <f>IFERROR(F$46/((F$34+E$34)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="G2" s="8">
+        <f>IFERROR(G$46/((G$34+F$34)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="H2" s="8">
+        <f>IFERROR(H$46/((H$34+G$34)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="I2" s="8">
+        <f>IFERROR(I$46/((I$34+H$34)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="J2" s="9" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>ROA</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C3" s="10">
+        <f>IFERROR(C$45/((C$26+B$26)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="D3" s="10">
+        <f>IFERROR(D$45/((D$26+C$26)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="E3" s="10">
+        <f>IFERROR(E$45/((E$26+D$26)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="F3" s="10">
+        <f>IFERROR(F$45/((F$26+E$26)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="G3" s="10">
+        <f>IFERROR(G$45/((G$26+F$26)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="H3" s="10">
+        <f>IFERROR(H$45/((H$26+G$26)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="I3" s="10">
+        <f>IFERROR(I$45/((I$26+H$26)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="J3" s="9" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Tăng trưởng LN Cổ đông Cty mẹ</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C4" s="8">
+        <f>IFERROR((C$46-B$46)/ABS(B$46),"n/a")</f>
+        <v/>
+      </c>
+      <c r="D4" s="8">
+        <f>IFERROR((D$46-C$46)/ABS(C$46),"n/a")</f>
+        <v/>
+      </c>
+      <c r="E4" s="8">
+        <f>IFERROR((E$46-D$46)/ABS(D$46),"n/a")</f>
+        <v/>
+      </c>
+      <c r="F4" s="8">
+        <f>IFERROR((F$46-E$46)/ABS(E$46),"n/a")</f>
+        <v/>
+      </c>
+      <c r="G4" s="8">
+        <f>IFERROR((G$46-F$46)/ABS(F$46),"n/a")</f>
+        <v/>
+      </c>
+      <c r="H4" s="8">
+        <f>IFERROR((H$46-G$46)/ABS(G$46),"n/a")</f>
+        <v/>
+      </c>
+      <c r="I4" s="8">
+        <f>IFERROR((I$46-H$46)/ABS(H$46),"n/a")</f>
+        <v/>
+      </c>
+      <c r="J4" s="9" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Tăng trưởng Doanh thu thuần</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C5" s="8">
+        <f>IFERROR((C$38-B$38)/ABS(B$38),"n/a")</f>
+        <v/>
+      </c>
+      <c r="D5" s="8">
+        <f>IFERROR((D$38-C$38)/ABS(C$38),"n/a")</f>
+        <v/>
+      </c>
+      <c r="E5" s="8">
+        <f>IFERROR((E$38-D$38)/ABS(D$38),"n/a")</f>
+        <v/>
+      </c>
+      <c r="F5" s="8">
+        <f>IFERROR((F$38-E$38)/ABS(E$38),"n/a")</f>
+        <v/>
+      </c>
+      <c r="G5" s="8">
+        <f>IFERROR((G$38-F$38)/ABS(F$38),"n/a")</f>
+        <v/>
+      </c>
+      <c r="H5" s="8">
+        <f>IFERROR((H$38-G$38)/ABS(G$38),"n/a")</f>
+        <v/>
+      </c>
+      <c r="I5" s="8">
+        <f>IFERROR((I$38-H$38)/ABS(H$38),"n/a")</f>
+        <v/>
+      </c>
+      <c r="J5" s="9" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Biên lợi nhuận gộp</t>
+        </is>
+      </c>
+      <c r="B6" s="8">
+        <f>IFERROR(B$40/B$38,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C6" s="8">
+        <f>IFERROR(C$40/C$38,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D6" s="8">
+        <f>IFERROR(D$40/D$38,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E6" s="8">
+        <f>IFERROR(E$40/E$38,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F6" s="8">
+        <f>IFERROR(F$40/F$38,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G6" s="8">
+        <f>IFERROR(G$40/G$38,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H6" s="8">
+        <f>IFERROR(H$40/H$38,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I6" s="8">
+        <f>IFERROR(I$40/I$38,"n/a")</f>
+        <v/>
+      </c>
+      <c r="J6" s="9" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Biên lợi nhuận ròng</t>
+        </is>
+      </c>
+      <c r="B7" s="11">
+        <f>IFERROR(B$45/B$38,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C7" s="11">
+        <f>IFERROR(C$45/C$38,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D7" s="11">
+        <f>IFERROR(D$45/D$38,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E7" s="11">
+        <f>IFERROR(E$45/E$38,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F7" s="11">
+        <f>IFERROR(F$45/F$38,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G7" s="11">
+        <f>IFERROR(G$45/G$38,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H7" s="11">
+        <f>IFERROR(H$45/H$38,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I7" s="11">
+        <f>IFERROR(I$45/I$38,"n/a")</f>
+        <v/>
+      </c>
+      <c r="J7" s="9" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>D/E (Nợ vay / Vốn chủ sở hữu)</t>
+        </is>
+      </c>
+      <c r="B8" s="8">
+        <f>IFERROR((B$29+B$31)/B$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C8" s="8">
+        <f>IFERROR((C$29+C$31)/C$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D8" s="8">
+        <f>IFERROR((D$29+D$31)/D$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E8" s="8">
+        <f>IFERROR((E$29+E$31)/E$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F8" s="8">
+        <f>IFERROR((F$29+F$31)/F$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G8" s="8">
+        <f>IFERROR((G$29+G$31)/G$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H8" s="8">
+        <f>IFERROR((H$29+H$31)/H$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I8" s="8">
+        <f>IFERROR((I$29+I$31)/I$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="J8" s="9" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     - Nợ vay dài hạn/Vốn chủ sở hữu</t>
+        </is>
+      </c>
+      <c r="B9" s="10">
+        <f>IFERROR(B$31/B$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C9" s="10">
+        <f>IFERROR(C$31/C$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D9" s="10">
+        <f>IFERROR(D$31/D$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E9" s="10">
+        <f>IFERROR(E$31/E$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F9" s="10">
+        <f>IFERROR(F$31/F$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G9" s="10">
+        <f>IFERROR(G$31/G$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H9" s="10">
+        <f>IFERROR(H$31/H$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I9" s="10">
+        <f>IFERROR(I$31/I$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="J9" s="9" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     - Nợ vay ngắn hạn/Vốn chủ sở hữu</t>
+        </is>
+      </c>
+      <c r="B10" s="10">
+        <f>IFERROR(B$29/B$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C10" s="10">
+        <f>IFERROR(C$29/C$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D10" s="10">
+        <f>IFERROR(D$29/D$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E10" s="10">
+        <f>IFERROR(E$29/E$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F10" s="10">
+        <f>IFERROR(F$29/F$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G10" s="10">
+        <f>IFERROR(G$29/G$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H10" s="10">
+        <f>IFERROR(H$29/H$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I10" s="10">
+        <f>IFERROR(I$29/I$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="J10" s="9" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Nợ phải trả/Vốn chủ sở hữu</t>
+        </is>
+      </c>
+      <c r="B11" s="11">
+        <f>IFERROR(B$33/B$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C11" s="11">
+        <f>IFERROR(C$33/C$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D11" s="11">
+        <f>IFERROR(D$33/D$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E11" s="11">
+        <f>IFERROR(E$33/E$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F11" s="11">
+        <f>IFERROR(F$33/F$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G11" s="11">
+        <f>IFERROR(G$33/G$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H11" s="11">
+        <f>IFERROR(H$33/H$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I11" s="11">
+        <f>IFERROR(I$33/I$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="J11" s="9" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     - Nợ dài hạn/Vốn chủ sở hữu</t>
+        </is>
+      </c>
+      <c r="B12" s="10">
+        <f>IFERROR(B$32/B$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C12" s="10">
+        <f>IFERROR(C$32/C$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D12" s="10">
+        <f>IFERROR(D$32/D$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E12" s="10">
+        <f>IFERROR(E$32/E$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F12" s="10">
+        <f>IFERROR(F$32/F$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G12" s="10">
+        <f>IFERROR(G$32/G$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H12" s="10">
+        <f>IFERROR(H$32/H$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I12" s="10">
+        <f>IFERROR(I$32/I$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="J12" s="9" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     - Nợ ngắn hạn/Vốn chủ sở hữu</t>
+        </is>
+      </c>
+      <c r="B13" s="10">
+        <f>IFERROR(B$30/B$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C13" s="10">
+        <f>IFERROR(C$30/C$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D13" s="10">
+        <f>IFERROR(D$30/D$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E13" s="10">
+        <f>IFERROR(E$30/E$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F13" s="10">
+        <f>IFERROR(F$30/F$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G13" s="10">
+        <f>IFERROR(G$30/G$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H13" s="10">
+        <f>IFERROR(H$30/H$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I13" s="10">
+        <f>IFERROR(I$30/I$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="J13" s="9" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Chi phí bán hàng, quản lý/LN gộp</t>
+        </is>
+      </c>
+      <c r="B14" s="13">
+        <f>IFERROR((ABS(B$41)+ABS(B$42))/B$40,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C14" s="13">
+        <f>IFERROR((ABS(C$41)+ABS(C$42))/C$40,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D14" s="13">
+        <f>IFERROR((ABS(D$41)+ABS(D$42))/D$40,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E14" s="13">
+        <f>IFERROR((ABS(E$41)+ABS(E$42))/E$40,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F14" s="13">
+        <f>IFERROR((ABS(F$41)+ABS(F$42))/F$40,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G14" s="13">
+        <f>IFERROR((ABS(G$41)+ABS(G$42))/G$40,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H14" s="13">
+        <f>IFERROR((ABS(H$41)+ABS(H$42))/H$40,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I14" s="13">
+        <f>IFERROR((ABS(I$41)+ABS(I$42))/I$40,"n/a")</f>
+        <v/>
+      </c>
+      <c r="J14" s="9" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Chi phí lãi vay/LN từ hoạt động kinh doanh</t>
+        </is>
+      </c>
+      <c r="B15" s="14">
+        <f>IFERROR(ABS(B$44)/B$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C15" s="14">
+        <f>IFERROR(ABS(C$44)/C$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D15" s="14">
+        <f>IFERROR(ABS(D$44)/D$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E15" s="14">
+        <f>IFERROR(ABS(E$44)/E$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F15" s="14">
+        <f>IFERROR(ABS(F$44)/F$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G15" s="14">
+        <f>IFERROR(ABS(G$44)/G$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H15" s="14">
+        <f>IFERROR(ABS(H$44)/H$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I15" s="14">
+        <f>IFERROR(ABS(I$44)/I$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="J15" s="9" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Số ngày phải trả (DPO)</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C16" s="16">
+        <f>IFERROR(((C$28+B$28)/2)/ABS(C$39)*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D16" s="16">
+        <f>IFERROR(((D$28+C$28)/2)/ABS(D$39)*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E16" s="16">
+        <f>IFERROR(((E$28+D$28)/2)/ABS(E$39)*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F16" s="16">
+        <f>IFERROR(((F$28+E$28)/2)/ABS(F$39)*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G16" s="16">
+        <f>IFERROR(((G$28+F$28)/2)/ABS(G$39)*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H16" s="16">
+        <f>IFERROR(((H$28+G$28)/2)/ABS(H$39)*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I16" s="16">
+        <f>IFERROR(((I$28+H$28)/2)/ABS(I$39)*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="J16" s="9" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Tiền và tương đương tiền/Tài sản</t>
+        </is>
+      </c>
+      <c r="B17" s="8">
+        <f>IFERROR(B$23/B$26,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C17" s="8">
+        <f>IFERROR(C$23/C$26,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D17" s="8">
+        <f>IFERROR(D$23/D$26,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E17" s="8">
+        <f>IFERROR(E$23/E$26,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F17" s="8">
+        <f>IFERROR(F$23/F$26,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G17" s="8">
+        <f>IFERROR(G$23/G$26,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H17" s="8">
+        <f>IFERROR(H$23/H$26,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I17" s="8">
+        <f>IFERROR(I$23/I$26,"n/a")</f>
+        <v/>
+      </c>
+      <c r="J17" s="9" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="n"/>
+      <c r="B18" s="9" t="n"/>
+      <c r="C18" s="9" t="n"/>
+      <c r="D18" s="9" t="n"/>
+      <c r="E18" s="9" t="n"/>
+      <c r="F18" s="9" t="n"/>
+      <c r="G18" s="9" t="n"/>
+      <c r="H18" s="9" t="n"/>
+      <c r="I18" s="9" t="n"/>
+      <c r="J18" s="9" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t>II. DỮ LIỆU TRÍCH XUẤT (tự động dò theo tên khoản mục)</t>
+        </is>
+      </c>
+      <c r="B19" s="18" t="n"/>
+      <c r="C19" s="18" t="n"/>
+      <c r="D19" s="18" t="n"/>
+      <c r="E19" s="18" t="n"/>
+      <c r="F19" s="18" t="n"/>
+      <c r="G19" s="18" t="n"/>
+      <c r="H19" s="18" t="n"/>
+      <c r="I19" s="18" t="n"/>
+      <c r="J19" s="9" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>Khoản mục</t>
+        </is>
+      </c>
+      <c r="B20" s="20">
+        <f>balance_sheet!B1</f>
+        <v/>
+      </c>
+      <c r="C20" s="20">
+        <f>balance_sheet!C1</f>
+        <v/>
+      </c>
+      <c r="D20" s="20">
+        <f>balance_sheet!D1</f>
+        <v/>
+      </c>
+      <c r="E20" s="20">
+        <f>balance_sheet!E1</f>
+        <v/>
+      </c>
+      <c r="F20" s="20">
+        <f>balance_sheet!F1</f>
+        <v/>
+      </c>
+      <c r="G20" s="20">
+        <f>balance_sheet!G1</f>
+        <v/>
+      </c>
+      <c r="H20" s="20">
+        <f>balance_sheet!H1</f>
+        <v/>
+      </c>
+      <c r="I20" s="20">
+        <f>balance_sheet!I1</f>
+        <v/>
+      </c>
+      <c r="J20" s="9" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="21" t="inlineStr">
+        <is>
+          <t>CĐKT</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="n"/>
+      <c r="C21" s="20" t="n"/>
+      <c r="D21" s="20" t="n"/>
+      <c r="E21" s="20" t="n"/>
+      <c r="F21" s="20" t="n"/>
+      <c r="G21" s="20" t="n"/>
+      <c r="H21" s="20" t="n"/>
+      <c r="I21" s="20" t="n"/>
+      <c r="J21" s="9" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="21" t="inlineStr">
+        <is>
+          <t>Tài sản</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="n"/>
+      <c r="C22" s="20" t="n"/>
+      <c r="D22" s="20" t="n"/>
+      <c r="E22" s="20" t="n"/>
+      <c r="F22" s="20" t="n"/>
+      <c r="G22" s="20" t="n"/>
+      <c r="H22" s="20" t="n"/>
+      <c r="I22" s="20" t="n"/>
+      <c r="J22" s="9" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="22" t="inlineStr">
+        <is>
+          <t>Tiền và tương đương tiền</t>
+        </is>
+      </c>
+      <c r="B23" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(B$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C23" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(C$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D23" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(D$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E23" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(E$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F23" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(F$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G23" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(G$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H23" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(H$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I23" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(I$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J23" s="9" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="22" t="inlineStr">
+        <is>
+          <t>Phải thu khách hàng</t>
+        </is>
+      </c>
+      <c r="B24" s="24" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C24" s="24" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D24" s="24" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="E24" s="24" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F24" s="24" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G24" s="24" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H24" s="24" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I24" s="24" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J24" s="9" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="22" t="inlineStr">
+        <is>
+          <t>Hàng tồn kho, ròng</t>
+        </is>
+      </c>
+      <c r="B25" s="24" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C25" s="24" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D25" s="24" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="E25" s="24" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F25" s="24" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G25" s="24" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H25" s="24" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I25" s="24" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J25" s="9" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="22" t="inlineStr">
+        <is>
+          <t>TỔNG CỘNG TÀI SẢN</t>
+        </is>
+      </c>
+      <c r="B26" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(B$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C26" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(C$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D26" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(D$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E26" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(E$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F26" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(F$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G26" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(G$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H26" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(H$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I26" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(I$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J26" s="9" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="21" t="inlineStr">
+        <is>
+          <t>Nguồn vốn</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="n"/>
+      <c r="C27" s="20" t="n"/>
+      <c r="D27" s="20" t="n"/>
+      <c r="E27" s="20" t="n"/>
+      <c r="F27" s="20" t="n"/>
+      <c r="G27" s="20" t="n"/>
+      <c r="H27" s="20" t="n"/>
+      <c r="I27" s="20" t="n"/>
+      <c r="J27" s="9" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="22" t="inlineStr">
+        <is>
+          <t>Phải trả người bán ngắn hạn</t>
+        </is>
+      </c>
+      <c r="B28" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán ngắn hạn",balance_sheet!$A:$A,0),MATCH(B$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C28" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán ngắn hạn",balance_sheet!$A:$A,0),MATCH(C$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D28" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán ngắn hạn",balance_sheet!$A:$A,0),MATCH(D$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E28" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán ngắn hạn",balance_sheet!$A:$A,0),MATCH(E$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F28" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán ngắn hạn",balance_sheet!$A:$A,0),MATCH(F$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G28" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán ngắn hạn",balance_sheet!$A:$A,0),MATCH(G$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H28" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán ngắn hạn",balance_sheet!$A:$A,0),MATCH(H$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I28" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán ngắn hạn",balance_sheet!$A:$A,0),MATCH(I$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J28" s="9" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="22" t="inlineStr">
+        <is>
+          <t>Vay ngắn hạn</t>
+        </is>
+      </c>
+      <c r="B29" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(B$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C29" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(C$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D29" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(D$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E29" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(E$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F29" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(F$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G29" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(G$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H29" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(H$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I29" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(I$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J29" s="9" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="22" t="inlineStr">
+        <is>
+          <t>Nợ phải trả ngắn hạn</t>
+        </is>
+      </c>
+      <c r="B30" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả ngắn hạn",balance_sheet!$A:$A,0),MATCH(B$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C30" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả ngắn hạn",balance_sheet!$A:$A,0),MATCH(C$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D30" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả ngắn hạn",balance_sheet!$A:$A,0),MATCH(D$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E30" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả ngắn hạn",balance_sheet!$A:$A,0),MATCH(E$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F30" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả ngắn hạn",balance_sheet!$A:$A,0),MATCH(F$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G30" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả ngắn hạn",balance_sheet!$A:$A,0),MATCH(G$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H30" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả ngắn hạn",balance_sheet!$A:$A,0),MATCH(H$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I30" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả ngắn hạn",balance_sheet!$A:$A,0),MATCH(I$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J30" s="9" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="22" t="inlineStr">
+        <is>
+          <t>Vay dài hạn</t>
+        </is>
+      </c>
+      <c r="B31" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(B$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C31" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(C$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D31" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(D$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E31" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(E$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F31" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(F$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G31" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(G$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H31" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(H$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I31" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(I$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J31" s="9" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="22" t="inlineStr">
+        <is>
+          <t>Nợ phải trả dài hạn</t>
+        </is>
+      </c>
+      <c r="B32" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả dài hạn",balance_sheet!$A:$A,0),MATCH(B$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C32" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả dài hạn",balance_sheet!$A:$A,0),MATCH(C$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D32" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả dài hạn",balance_sheet!$A:$A,0),MATCH(D$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E32" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả dài hạn",balance_sheet!$A:$A,0),MATCH(E$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F32" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả dài hạn",balance_sheet!$A:$A,0),MATCH(F$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G32" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả dài hạn",balance_sheet!$A:$A,0),MATCH(G$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H32" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả dài hạn",balance_sheet!$A:$A,0),MATCH(H$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I32" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả dài hạn",balance_sheet!$A:$A,0),MATCH(I$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J32" s="9" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="22" t="inlineStr">
+        <is>
+          <t>NỢ PHẢI TRẢ</t>
+        </is>
+      </c>
+      <c r="B33" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(B$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C33" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(C$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D33" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(D$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E33" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(E$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F33" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(F$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G33" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(G$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H33" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(H$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I33" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(I$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J33" s="9" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="21" t="inlineStr">
+        <is>
+          <t>Vốn chủ sở hữu</t>
+        </is>
+      </c>
+      <c r="B34" s="25">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(B$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C34" s="25">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(C$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D34" s="25">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(D$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E34" s="25">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(E$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F34" s="25">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(F$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G34" s="25">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(G$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H34" s="25">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(H$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I34" s="25">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(I$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J34" s="25">
+        <f>I34+J46*0.7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="26" t="inlineStr">
+        <is>
+          <t>Tăng VCSH/LN cổ đông cty mẹ</t>
+        </is>
+      </c>
+      <c r="B35" s="27" t="n"/>
+      <c r="C35" s="28">
+        <f>(C34-B34)/C46</f>
+        <v/>
+      </c>
+      <c r="D35" s="28">
+        <f>(D34-C34)/D46</f>
+        <v/>
+      </c>
+      <c r="E35" s="28">
+        <f>(E34-D34)/E46</f>
+        <v/>
+      </c>
+      <c r="F35" s="28">
+        <f>(F34-E34)/F46</f>
+        <v/>
+      </c>
+      <c r="G35" s="28">
+        <f>(G34-F34)/G46</f>
+        <v/>
+      </c>
+      <c r="H35" s="28">
+        <f>(H34-G34)/H46</f>
+        <v/>
+      </c>
+      <c r="I35" s="28">
+        <f>(I34-H34)/I46</f>
+        <v/>
+      </c>
+      <c r="J35" s="29" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="21" t="inlineStr">
+        <is>
+          <t>Lợi ích cổ đông không kiểm soát</t>
+        </is>
+      </c>
+      <c r="B36" s="25">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Lợi ích cổ đông không kiểm soát",balance_sheet!$A:$A,0),MATCH(B$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C36" s="25">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Lợi ích cổ đông không kiểm soát",balance_sheet!$A:$A,0),MATCH(C$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D36" s="25">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Lợi ích cổ đông không kiểm soát",balance_sheet!$A:$A,0),MATCH(D$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E36" s="25">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Lợi ích cổ đông không kiểm soát",balance_sheet!$A:$A,0),MATCH(E$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F36" s="25">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Lợi ích cổ đông không kiểm soát",balance_sheet!$A:$A,0),MATCH(F$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G36" s="25">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Lợi ích cổ đông không kiểm soát",balance_sheet!$A:$A,0),MATCH(G$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H36" s="25">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Lợi ích cổ đông không kiểm soát",balance_sheet!$A:$A,0),MATCH(H$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I36" s="25">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Lợi ích cổ đông không kiểm soát",balance_sheet!$A:$A,0),MATCH(I$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J36" s="29" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="21" t="inlineStr">
+        <is>
+          <t>Kết quả hoạt động kinh doanh</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="n"/>
+      <c r="C37" s="9" t="n"/>
+      <c r="D37" s="9" t="n"/>
+      <c r="E37" s="9" t="n"/>
+      <c r="F37" s="9" t="n"/>
+      <c r="G37" s="9" t="n"/>
+      <c r="H37" s="9" t="n"/>
+      <c r="I37" s="9" t="n"/>
+      <c r="J37" s="9" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="21" t="inlineStr">
+        <is>
+          <t>Doanh thu thuần về hoạt động kinh doanh</t>
+        </is>
+      </c>
+      <c r="B38" s="25">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần về hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(B$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C38" s="25">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần về hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(C$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D38" s="25">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần về hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(D$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E38" s="25">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần về hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(E$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F38" s="25">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần về hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(F$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G38" s="25">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần về hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(G$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H38" s="25">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần về hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(H$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I38" s="25">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần về hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(I$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J38" s="25" t="n">
+        <v>13227000000000</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="22" t="inlineStr">
+        <is>
+          <t>CHI PHÍ HOẠT ĐỘNG</t>
+        </is>
+      </c>
+      <c r="B39" s="23">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(B$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C39" s="23">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(C$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D39" s="23">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(D$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E39" s="23">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(E$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F39" s="23">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(F$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G39" s="23">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(G$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H39" s="23">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(H$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I39" s="23">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(I$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J39" s="9" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="21" t="inlineStr">
+        <is>
+          <t>LỢI NHUẬN GỘP</t>
+        </is>
+      </c>
+      <c r="B40" s="25">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN GỘP",income_statement!$A:$A,0),MATCH(B$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C40" s="25">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN GỘP",income_statement!$A:$A,0),MATCH(C$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D40" s="25">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN GỘP",income_statement!$A:$A,0),MATCH(D$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E40" s="25">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN GỘP",income_statement!$A:$A,0),MATCH(E$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F40" s="25">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN GỘP",income_statement!$A:$A,0),MATCH(F$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G40" s="25">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN GỘP",income_statement!$A:$A,0),MATCH(G$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H40" s="25">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN GỘP",income_statement!$A:$A,0),MATCH(H$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I40" s="25">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN GỘP",income_statement!$A:$A,0),MATCH(I$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J40" s="29" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="22" t="inlineStr">
+        <is>
+          <t>CHI PHÍ BÁN HÀNG</t>
+        </is>
+      </c>
+      <c r="B41" s="23">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ BÁN HÀNG",income_statement!$A:$A,0),MATCH(B$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C41" s="23">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ BÁN HÀNG",income_statement!$A:$A,0),MATCH(C$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D41" s="23">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ BÁN HÀNG",income_statement!$A:$A,0),MATCH(D$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E41" s="23">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ BÁN HÀNG",income_statement!$A:$A,0),MATCH(E$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F41" s="23">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ BÁN HÀNG",income_statement!$A:$A,0),MATCH(F$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G41" s="23">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ BÁN HÀNG",income_statement!$A:$A,0),MATCH(G$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H41" s="23">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ BÁN HÀNG",income_statement!$A:$A,0),MATCH(H$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I41" s="23">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ BÁN HÀNG",income_statement!$A:$A,0),MATCH(I$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J41" s="9" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="22" t="inlineStr">
+        <is>
+          <t>CHI PHÍ QUẢN LÝ CÔNG TY CHỨNG KHOÁN</t>
+        </is>
+      </c>
+      <c r="B42" s="23">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ QUẢN LÝ CÔNG TY CHỨNG KHOÁN",income_statement!$A:$A,0),MATCH(B$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C42" s="23">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ QUẢN LÝ CÔNG TY CHỨNG KHOÁN",income_statement!$A:$A,0),MATCH(C$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D42" s="23">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ QUẢN LÝ CÔNG TY CHỨNG KHOÁN",income_statement!$A:$A,0),MATCH(D$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E42" s="23">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ QUẢN LÝ CÔNG TY CHỨNG KHOÁN",income_statement!$A:$A,0),MATCH(E$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F42" s="23">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ QUẢN LÝ CÔNG TY CHỨNG KHOÁN",income_statement!$A:$A,0),MATCH(F$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G42" s="23">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ QUẢN LÝ CÔNG TY CHỨNG KHOÁN",income_statement!$A:$A,0),MATCH(G$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H42" s="23">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ QUẢN LÝ CÔNG TY CHỨNG KHOÁN",income_statement!$A:$A,0),MATCH(H$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I42" s="23">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ QUẢN LÝ CÔNG TY CHỨNG KHOÁN",income_statement!$A:$A,0),MATCH(I$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J42" s="9" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="22" t="inlineStr">
+        <is>
+          <t>KẾT QUẢ HOẠT ĐỘNG</t>
+        </is>
+      </c>
+      <c r="B43" s="23">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("KẾT QUẢ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(B$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C43" s="23">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("KẾT QUẢ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(C$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D43" s="23">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("KẾT QUẢ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(D$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E43" s="23">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("KẾT QUẢ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(E$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F43" s="23">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("KẾT QUẢ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(F$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G43" s="23">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("KẾT QUẢ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(G$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H43" s="23">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("KẾT QUẢ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(H$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I43" s="23">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("KẾT QUẢ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(I$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J43" s="9" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="22" t="inlineStr">
+        <is>
+          <t>Chi phí lãi vay</t>
+        </is>
+      </c>
+      <c r="B44" s="23">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(B$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C44" s="23">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(C$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D44" s="23">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(D$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E44" s="23">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(E$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F44" s="23">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(F$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G44" s="23">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(G$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H44" s="23">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(H$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I44" s="23">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(I$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J44" s="9" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="21" t="inlineStr">
+        <is>
+          <t>LỢI NHUẬN KẾ TOÁN SAU THUẾ</t>
+        </is>
+      </c>
+      <c r="B45" s="25">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN KẾ TOÁN SAU THUẾ",income_statement!$A:$A,0),MATCH(B$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C45" s="25">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN KẾ TOÁN SAU THUẾ",income_statement!$A:$A,0),MATCH(C$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D45" s="25">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN KẾ TOÁN SAU THUẾ",income_statement!$A:$A,0),MATCH(D$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E45" s="25">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN KẾ TOÁN SAU THUẾ",income_statement!$A:$A,0),MATCH(E$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F45" s="25">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN KẾ TOÁN SAU THUẾ",income_statement!$A:$A,0),MATCH(F$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G45" s="25">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN KẾ TOÁN SAU THUẾ",income_statement!$A:$A,0),MATCH(G$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H45" s="25">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN KẾ TOÁN SAU THUẾ",income_statement!$A:$A,0),MATCH(H$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I45" s="25">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN KẾ TOÁN SAU THUẾ",income_statement!$A:$A,0),MATCH(I$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J45" s="25" t="n">
+        <v>7535000000000</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="21" t="inlineStr">
+        <is>
+          <t>Lợi nhuận sau thuế phân bổ cho chủ sở hữu</t>
+        </is>
+      </c>
+      <c r="B46" s="25">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận sau thuế phân bổ cho chủ sở hữu",income_statement!$A:$A,0),MATCH(B$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C46" s="25">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận sau thuế phân bổ cho chủ sở hữu",income_statement!$A:$A,0),MATCH(C$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D46" s="25">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận sau thuế phân bổ cho chủ sở hữu",income_statement!$A:$A,0),MATCH(D$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E46" s="25">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận sau thuế phân bổ cho chủ sở hữu",income_statement!$A:$A,0),MATCH(E$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F46" s="25">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận sau thuế phân bổ cho chủ sở hữu",income_statement!$A:$A,0),MATCH(F$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G46" s="25">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận sau thuế phân bổ cho chủ sở hữu",income_statement!$A:$A,0),MATCH(G$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H46" s="25">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận sau thuế phân bổ cho chủ sở hữu",income_statement!$A:$A,0),MATCH(H$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I46" s="25">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận sau thuế phân bổ cho chủ sở hữu",income_statement!$A:$A,0),MATCH(I$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J46" s="25" t="n">
+        <v>7535000000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="B2:I2">
+    <cfRule type="cellIs" priority="13" operator="lessThan" dxfId="0">
+      <formula>0.15</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="14" operator="greaterThanOrEqual" dxfId="1">
+      <formula>0.15</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B4:I5">
+    <cfRule type="cellIs" priority="11" operator="lessThan" dxfId="0">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="12" operator="greaterThan" dxfId="1">
+      <formula>0.15</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B6:I6">
+    <cfRule type="cellIs" priority="6" operator="lessThanOrEqual" dxfId="0">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="7" operator="between" dxfId="2">
+      <formula>0.3</formula>
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="8" operator="greaterThanOrEqual" dxfId="1">
+      <formula>0.3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B7:I7">
+    <cfRule type="cellIs" priority="5" operator="greaterThanOrEqual" dxfId="1">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B8:I8">
+    <cfRule type="cellIs" priority="10" operator="lessThanOrEqual" dxfId="1">
+      <formula>0.5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B11:I11">
+    <cfRule type="cellIs" priority="9" operator="lessThanOrEqual" dxfId="1">
+      <formula>0.5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B14:I14">
+    <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
+      <formula>0.7</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="lessThanOrEqual" dxfId="1">
+      <formula>0.3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B17:I17">
+    <cfRule type="cellIs" priority="3" operator="notBetween" dxfId="0">
+      <formula>0.02</formula>
+      <formula>0.3</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="between" dxfId="1">
+      <formula>0.02</formula>
+      <formula>0.3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8.21875" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="20.44140625" customWidth="1" min="7" max="7"/>
+    <col width="9.33203125" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="30" t="n"/>
+      <c r="B1" s="30" t="inlineStr">
+        <is>
+          <t>Q4/2025</t>
+        </is>
+      </c>
+      <c r="C1" s="30" t="inlineStr">
+        <is>
+          <t>Q1/2026</t>
+        </is>
+      </c>
+      <c r="D1" s="30" t="inlineStr">
+        <is>
+          <t>Q2/2026</t>
+        </is>
+      </c>
+      <c r="E1" s="30" t="inlineStr">
+        <is>
+          <t>Q3/2026</t>
+        </is>
+      </c>
+      <c r="F1" s="30" t="inlineStr">
+        <is>
+          <t>Q4/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="14.25" customHeight="1">
+      <c r="A2" s="30" t="inlineStr">
+        <is>
+          <t>Số CP</t>
+        </is>
+      </c>
+      <c r="B2" s="31" t="n">
+        <v>2774453325</v>
+      </c>
+      <c r="C2" s="31" t="n">
+        <v>2774453325</v>
+      </c>
+      <c r="D2" s="31" t="n">
+        <v>2774453325</v>
+      </c>
+      <c r="E2" s="31" t="n">
+        <v>2774453325</v>
+      </c>
+      <c r="F2" s="31" t="n">
+        <v>2774453325</v>
+      </c>
+    </row>
+    <row r="3" ht="14.25" customHeight="1">
+      <c r="A3" s="30" t="inlineStr">
+        <is>
+          <t>Thị giá</t>
+        </is>
+      </c>
+      <c r="B3" s="31" t="n">
+        <v>40800</v>
+      </c>
+      <c r="C3" s="31" t="n">
+        <v>40800</v>
+      </c>
+      <c r="D3" s="31" t="n">
+        <v>40800</v>
+      </c>
+      <c r="E3" s="31" t="n">
+        <v>40800</v>
+      </c>
+      <c r="F3" s="31" t="n">
+        <v>40800</v>
+      </c>
+    </row>
+    <row r="4" ht="14.25" customHeight="1">
+      <c r="A4" s="30" t="inlineStr">
+        <is>
+          <t>Vốn hoá</t>
+        </is>
+      </c>
+      <c r="B4" s="31">
+        <f>B2*B3</f>
+        <v/>
+      </c>
+      <c r="C4" s="31">
+        <f>C2*C3</f>
+        <v/>
+      </c>
+      <c r="D4" s="31">
+        <f>D2*D3</f>
+        <v/>
+      </c>
+      <c r="E4" s="31">
+        <f>E2*E3</f>
+        <v/>
+      </c>
+      <c r="F4" s="31">
+        <f>F2*F3</f>
+        <v/>
+      </c>
+      <c r="G4" s="32" t="n"/>
+    </row>
+    <row r="5" ht="14.25" customHeight="1"/>
+    <row r="6" ht="14.25" customHeight="1">
+      <c r="A6" s="30" t="inlineStr">
+        <is>
+          <t>VCSH</t>
+        </is>
+      </c>
+      <c r="B6" s="31">
+        <f>chi_so_tai_chinh!I34</f>
+        <v/>
+      </c>
+      <c r="C6" s="31" t="n">
+        <v>45782000000000</v>
+      </c>
+      <c r="D6" s="31">
+        <f>B$6*(($F$6/$B$6)^(2/4))</f>
+        <v/>
+      </c>
+      <c r="E6" s="31">
+        <f>B$6*(($F$6/$B$6)^(3/4))</f>
+        <v/>
+      </c>
+      <c r="F6" s="31">
+        <f>chi_so_tai_chinh!J34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="14.25" customHeight="1">
+      <c r="A7" s="30" t="inlineStr">
+        <is>
+          <t>LICĐKKS</t>
+        </is>
+      </c>
+      <c r="B7" s="31">
+        <f>chi_so_tai_chinh!I36</f>
+        <v/>
+      </c>
+      <c r="C7" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="31">
+        <f>[1]CĐKT!K157*1000000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="14.25" customHeight="1">
+      <c r="A8" s="30" t="inlineStr">
+        <is>
+          <t>BV</t>
+        </is>
+      </c>
+      <c r="B8" s="33">
+        <f>B6-B7</f>
+        <v/>
+      </c>
+      <c r="C8" s="33">
+        <f>C6-C7</f>
+        <v/>
+      </c>
+      <c r="D8" s="33">
+        <f>D6-D7</f>
+        <v/>
+      </c>
+      <c r="E8" s="33">
+        <f>E6-E7</f>
+        <v/>
+      </c>
+      <c r="F8" s="33">
+        <f>F6-F7</f>
+        <v/>
+      </c>
+      <c r="G8" s="34" t="n"/>
+      <c r="H8" s="34" t="n"/>
+      <c r="I8" s="34" t="n"/>
+      <c r="J8" s="34" t="n"/>
+      <c r="K8" s="34" t="n"/>
+      <c r="L8" s="34" t="n"/>
+      <c r="M8" s="34" t="n"/>
+    </row>
+    <row r="9" ht="14.25" customHeight="1">
+      <c r="A9" s="35" t="inlineStr">
+        <is>
+          <t>BVPS</t>
+        </is>
+      </c>
+      <c r="B9" s="36">
+        <f>B8/B2</f>
+        <v/>
+      </c>
+      <c r="C9" s="36">
+        <f>C8/C2</f>
+        <v/>
+      </c>
+      <c r="D9" s="36">
+        <f>D8/D2</f>
+        <v/>
+      </c>
+      <c r="E9" s="36">
+        <f>E8/E2</f>
+        <v/>
+      </c>
+      <c r="F9" s="36">
+        <f>F8/F2</f>
+        <v/>
+      </c>
+      <c r="H9" s="34" t="n"/>
+      <c r="I9" s="34" t="n"/>
+      <c r="J9" s="34" t="n"/>
+      <c r="K9" s="34" t="n"/>
+      <c r="L9" s="34" t="n"/>
+      <c r="M9" s="34" t="n"/>
+    </row>
+    <row r="10" ht="14.25" customHeight="1">
+      <c r="A10" s="35" t="inlineStr">
+        <is>
+          <t>PB</t>
+        </is>
+      </c>
+      <c r="B10" s="37">
+        <f>B3/B9</f>
+        <v/>
+      </c>
+      <c r="C10" s="37">
+        <f>C3/C9</f>
+        <v/>
+      </c>
+      <c r="D10" s="37">
+        <f>D3/D9</f>
+        <v/>
+      </c>
+      <c r="E10" s="37">
+        <f>E3/E9</f>
+        <v/>
+      </c>
+      <c r="F10" s="37">
+        <f>F3/F9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="14.25" customHeight="1"/>
+    <row r="12" ht="14.25" customHeight="1"/>
+    <row r="13" ht="14.25" customHeight="1"/>
+    <row r="14" ht="14.25" customHeight="1"/>
+    <row r="15" ht="14.25" customHeight="1"/>
+    <row r="16" ht="14.25" customHeight="1"/>
+    <row r="17" ht="14.25" customHeight="1"/>
+    <row r="18" ht="14.25" customHeight="1"/>
+    <row r="19" ht="14.25" customHeight="1"/>
+    <row r="20" ht="14.25" customHeight="1"/>
+    <row r="21" ht="14.25" customHeight="1"/>
+    <row r="22" ht="14.25" customHeight="1"/>
+    <row r="23" ht="14.25" customHeight="1"/>
+    <row r="24" ht="14.25" customHeight="1"/>
+    <row r="25" ht="14.25" customHeight="1"/>
+    <row r="26" ht="14.25" customHeight="1"/>
+    <row r="27" ht="14.25" customHeight="1"/>
+    <row r="28" ht="14.25" customHeight="1"/>
+    <row r="29" ht="14.25" customHeight="1"/>
+    <row r="30" ht="14.25" customHeight="1"/>
+    <row r="31" ht="14.25" customHeight="1"/>
+    <row r="32" ht="14.25" customHeight="1"/>
+    <row r="33" ht="14.25" customHeight="1"/>
+    <row r="34" ht="14.25" customHeight="1"/>
+    <row r="35" ht="14.25" customHeight="1"/>
+    <row r="36" ht="14.25" customHeight="1"/>
+    <row r="37" ht="14.25" customHeight="1"/>
+    <row r="38" ht="14.25" customHeight="1"/>
+    <row r="39" ht="14.25" customHeight="1"/>
+    <row r="40" ht="14.25" customHeight="1"/>
+    <row r="41" ht="14.25" customHeight="1"/>
+    <row r="42" ht="14.25" customHeight="1"/>
+    <row r="43" ht="14.25" customHeight="1"/>
+    <row r="44" ht="14.25" customHeight="1"/>
+    <row r="45" ht="14.25" customHeight="1"/>
+    <row r="46" ht="14.25" customHeight="1"/>
+    <row r="47" ht="14.25" customHeight="1"/>
+    <row r="48" ht="14.25" customHeight="1"/>
+    <row r="49" ht="14.25" customHeight="1"/>
+    <row r="50" ht="14.25" customHeight="1"/>
+    <row r="51" ht="14.25" customHeight="1"/>
+    <row r="52" ht="14.25" customHeight="1"/>
+    <row r="53" ht="14.25" customHeight="1"/>
+    <row r="54" ht="14.25" customHeight="1"/>
+    <row r="55" ht="14.25" customHeight="1"/>
+    <row r="56" ht="14.25" customHeight="1"/>
+    <row r="57" ht="14.25" customHeight="1"/>
+    <row r="58" ht="14.25" customHeight="1"/>
+    <row r="59" ht="14.25" customHeight="1"/>
+    <row r="60" ht="14.25" customHeight="1"/>
+    <row r="61" ht="14.25" customHeight="1"/>
+    <row r="62" ht="14.25" customHeight="1"/>
+    <row r="63" ht="14.25" customHeight="1"/>
+    <row r="64" ht="14.25" customHeight="1"/>
+    <row r="65" ht="14.25" customHeight="1"/>
+    <row r="66" ht="14.25" customHeight="1"/>
+    <row r="67" ht="14.25" customHeight="1"/>
+    <row r="68" ht="14.25" customHeight="1"/>
+    <row r="69" ht="14.25" customHeight="1"/>
+    <row r="70" ht="14.25" customHeight="1"/>
+    <row r="71" ht="14.25" customHeight="1"/>
+    <row r="72" ht="14.25" customHeight="1"/>
+    <row r="73" ht="14.25" customHeight="1"/>
+    <row r="74" ht="14.25" customHeight="1"/>
+    <row r="75" ht="14.25" customHeight="1"/>
+    <row r="76" ht="14.25" customHeight="1"/>
+    <row r="77" ht="14.25" customHeight="1"/>
+    <row r="78" ht="14.25" customHeight="1"/>
+    <row r="79" ht="14.25" customHeight="1"/>
+    <row r="80" ht="14.25" customHeight="1"/>
+    <row r="81" ht="14.25" customHeight="1"/>
+    <row r="82" ht="14.25" customHeight="1"/>
+    <row r="83" ht="14.25" customHeight="1"/>
+    <row r="84" ht="14.25" customHeight="1"/>
+    <row r="85" ht="14.25" customHeight="1"/>
+    <row r="86" ht="14.25" customHeight="1"/>
+    <row r="87" ht="14.25" customHeight="1"/>
+    <row r="88" ht="14.25" customHeight="1"/>
+    <row r="89" ht="14.25" customHeight="1"/>
+    <row r="90" ht="14.25" customHeight="1"/>
+    <row r="91" ht="14.25" customHeight="1"/>
+    <row r="92" ht="14.25" customHeight="1"/>
+    <row r="93" ht="14.25" customHeight="1"/>
+    <row r="94" ht="14.25" customHeight="1"/>
+    <row r="95" ht="14.25" customHeight="1"/>
+    <row r="96" ht="14.25" customHeight="1"/>
+    <row r="97" ht="14.25" customHeight="1"/>
+    <row r="98" ht="14.25" customHeight="1"/>
+    <row r="99" ht="14.25" customHeight="1"/>
+    <row r="100" ht="14.25" customHeight="1"/>
+    <row r="101" ht="14.25" customHeight="1"/>
+    <row r="102" ht="14.25" customHeight="1"/>
+    <row r="103" ht="14.25" customHeight="1"/>
+    <row r="104" ht="14.25" customHeight="1"/>
+    <row r="105" ht="14.25" customHeight="1"/>
+    <row r="106" ht="14.25" customHeight="1"/>
+    <row r="107" ht="14.25" customHeight="1"/>
+    <row r="108" ht="14.25" customHeight="1"/>
+    <row r="109" ht="14.25" customHeight="1"/>
+    <row r="110" ht="14.25" customHeight="1"/>
+    <row r="111" ht="14.25" customHeight="1"/>
+    <row r="112" ht="14.25" customHeight="1"/>
+    <row r="113" ht="14.25" customHeight="1"/>
+    <row r="114" ht="14.25" customHeight="1"/>
+    <row r="115" ht="14.25" customHeight="1"/>
+    <row r="116" ht="14.25" customHeight="1"/>
+    <row r="117" ht="14.25" customHeight="1"/>
+    <row r="118" ht="14.25" customHeight="1"/>
+    <row r="119" ht="14.25" customHeight="1"/>
+    <row r="120" ht="14.25" customHeight="1"/>
+    <row r="121" ht="14.25" customHeight="1"/>
+    <row r="122" ht="14.25" customHeight="1"/>
+    <row r="123" ht="14.25" customHeight="1"/>
+    <row r="124" ht="14.25" customHeight="1"/>
+    <row r="125" ht="14.25" customHeight="1"/>
+    <row r="126" ht="14.25" customHeight="1"/>
+    <row r="127" ht="14.25" customHeight="1"/>
+    <row r="128" ht="14.25" customHeight="1"/>
+    <row r="129" ht="14.25" customHeight="1"/>
+    <row r="130" ht="14.25" customHeight="1"/>
+    <row r="131" ht="14.25" customHeight="1"/>
+    <row r="132" ht="14.25" customHeight="1"/>
+    <row r="133" ht="14.25" customHeight="1"/>
+    <row r="134" ht="14.25" customHeight="1"/>
+    <row r="135" ht="14.25" customHeight="1"/>
+    <row r="136" ht="14.25" customHeight="1"/>
+    <row r="137" ht="14.25" customHeight="1"/>
+    <row r="138" ht="14.25" customHeight="1"/>
+    <row r="139" ht="14.25" customHeight="1"/>
+    <row r="140" ht="14.25" customHeight="1"/>
+    <row r="141" ht="14.25" customHeight="1"/>
+    <row r="142" ht="14.25" customHeight="1"/>
+    <row r="143" ht="14.25" customHeight="1"/>
+    <row r="144" ht="14.25" customHeight="1"/>
+    <row r="145" ht="14.25" customHeight="1"/>
+    <row r="146" ht="14.25" customHeight="1"/>
+    <row r="147" ht="14.25" customHeight="1"/>
+    <row r="148" ht="14.25" customHeight="1"/>
+    <row r="149" ht="14.25" customHeight="1"/>
+    <row r="150" ht="14.25" customHeight="1"/>
+    <row r="151" ht="14.25" customHeight="1"/>
+    <row r="152" ht="14.25" customHeight="1"/>
+    <row r="153" ht="14.25" customHeight="1"/>
+    <row r="154" ht="14.25" customHeight="1"/>
+    <row r="155" ht="14.25" customHeight="1"/>
+    <row r="156" ht="14.25" customHeight="1"/>
+    <row r="157" ht="14.25" customHeight="1"/>
+    <row r="158" ht="14.25" customHeight="1"/>
+    <row r="159" ht="14.25" customHeight="1"/>
+    <row r="160" ht="14.25" customHeight="1"/>
+    <row r="161" ht="14.25" customHeight="1"/>
+    <row r="162" ht="14.25" customHeight="1"/>
+    <row r="163" ht="14.25" customHeight="1"/>
+    <row r="164" ht="14.25" customHeight="1"/>
+    <row r="165" ht="14.25" customHeight="1"/>
+    <row r="166" ht="14.25" customHeight="1"/>
+    <row r="167" ht="14.25" customHeight="1"/>
+    <row r="168" ht="14.25" customHeight="1"/>
+    <row r="169" ht="14.25" customHeight="1"/>
+    <row r="170" ht="14.25" customHeight="1"/>
+    <row r="171" ht="14.25" customHeight="1"/>
+    <row r="172" ht="14.25" customHeight="1"/>
+    <row r="173" ht="14.25" customHeight="1"/>
+    <row r="174" ht="14.25" customHeight="1"/>
+    <row r="175" ht="14.25" customHeight="1"/>
+    <row r="176" ht="14.25" customHeight="1"/>
+    <row r="177" ht="14.25" customHeight="1"/>
+    <row r="178" ht="14.25" customHeight="1"/>
+    <row r="179" ht="14.25" customHeight="1"/>
+    <row r="180" ht="14.25" customHeight="1"/>
+    <row r="181" ht="14.25" customHeight="1"/>
+    <row r="182" ht="14.25" customHeight="1"/>
+    <row r="183" ht="14.25" customHeight="1"/>
+    <row r="184" ht="14.25" customHeight="1"/>
+    <row r="185" ht="14.25" customHeight="1"/>
+    <row r="186" ht="14.25" customHeight="1"/>
+    <row r="187" ht="14.25" customHeight="1"/>
+    <row r="188" ht="14.25" customHeight="1"/>
+    <row r="189" ht="14.25" customHeight="1"/>
+    <row r="190" ht="14.25" customHeight="1"/>
+    <row r="191" ht="14.25" customHeight="1"/>
+    <row r="192" ht="14.25" customHeight="1"/>
+    <row r="193" ht="14.25" customHeight="1"/>
+    <row r="194" ht="14.25" customHeight="1"/>
+    <row r="195" ht="14.25" customHeight="1"/>
+    <row r="196" ht="14.25" customHeight="1"/>
+    <row r="197" ht="14.25" customHeight="1"/>
+    <row r="198" ht="14.25" customHeight="1"/>
+    <row r="199" ht="14.25" customHeight="1"/>
+    <row r="200" ht="14.25" customHeight="1"/>
+    <row r="201" ht="14.25" customHeight="1"/>
+    <row r="202" ht="14.25" customHeight="1"/>
+    <row r="203" ht="14.25" customHeight="1"/>
+    <row r="204" ht="14.25" customHeight="1"/>
+    <row r="205" ht="14.25" customHeight="1"/>
+    <row r="206" ht="14.25" customHeight="1"/>
+    <row r="207" ht="14.25" customHeight="1"/>
+    <row r="208" ht="14.25" customHeight="1"/>
+    <row r="209" ht="14.25" customHeight="1"/>
+    <row r="210" ht="14.25" customHeight="1"/>
+    <row r="211" ht="14.25" customHeight="1"/>
+    <row r="212" ht="14.25" customHeight="1"/>
+    <row r="213" ht="14.25" customHeight="1"/>
+    <row r="214" ht="14.25" customHeight="1"/>
+    <row r="215" ht="14.25" customHeight="1"/>
+    <row r="216" ht="14.25" customHeight="1"/>
+    <row r="217" ht="14.25" customHeight="1"/>
+    <row r="218" ht="14.25" customHeight="1"/>
+    <row r="219" ht="14.25" customHeight="1"/>
+    <row r="220" ht="14.25" customHeight="1"/>
+    <row r="221" ht="14.25" customHeight="1"/>
+    <row r="222" ht="14.25" customHeight="1"/>
+    <row r="223" ht="14.25" customHeight="1"/>
+    <row r="224" ht="14.25" customHeight="1"/>
+    <row r="225" ht="14.25" customHeight="1"/>
+    <row r="226" ht="14.25" customHeight="1"/>
+    <row r="227" ht="14.25" customHeight="1"/>
+    <row r="228" ht="14.25" customHeight="1"/>
+    <row r="229" ht="14.25" customHeight="1"/>
+    <row r="230" ht="14.25" customHeight="1"/>
+    <row r="231" ht="14.25" customHeight="1"/>
+    <row r="232" ht="14.25" customHeight="1"/>
+    <row r="233" ht="14.25" customHeight="1"/>
+    <row r="234" ht="14.25" customHeight="1"/>
+    <row r="235" ht="14.25" customHeight="1"/>
+    <row r="236" ht="14.25" customHeight="1"/>
+    <row r="237" ht="14.25" customHeight="1"/>
+    <row r="238" ht="14.25" customHeight="1"/>
+    <row r="239" ht="14.25" customHeight="1"/>
+    <row r="240" ht="14.25" customHeight="1"/>
+    <row r="241" ht="14.25" customHeight="1"/>
+    <row r="242" ht="14.25" customHeight="1"/>
+    <row r="243" ht="14.25" customHeight="1"/>
+    <row r="244" ht="14.25" customHeight="1"/>
+    <row r="245" ht="14.25" customHeight="1"/>
+    <row r="246" ht="14.25" customHeight="1"/>
+    <row r="247" ht="14.25" customHeight="1"/>
+    <row r="248" ht="14.25" customHeight="1"/>
+    <row r="249" ht="14.25" customHeight="1"/>
+    <row r="250" ht="14.25" customHeight="1"/>
+    <row r="251" ht="14.25" customHeight="1"/>
+    <row r="252" ht="14.25" customHeight="1"/>
+    <row r="253" ht="14.25" customHeight="1"/>
+    <row r="254" ht="14.25" customHeight="1"/>
+    <row r="255" ht="14.25" customHeight="1"/>
+    <row r="256" ht="14.25" customHeight="1"/>
+    <row r="257" ht="14.25" customHeight="1"/>
+    <row r="258" ht="14.25" customHeight="1"/>
+    <row r="259" ht="14.25" customHeight="1"/>
+    <row r="260" ht="14.25" customHeight="1"/>
+    <row r="261" ht="14.25" customHeight="1"/>
+    <row r="262" ht="14.25" customHeight="1"/>
+    <row r="263" ht="14.25" customHeight="1"/>
+    <row r="264" ht="14.25" customHeight="1"/>
+    <row r="265" ht="14.25" customHeight="1"/>
+    <row r="266" ht="14.25" customHeight="1"/>
+    <row r="267" ht="14.25" customHeight="1"/>
+    <row r="268" ht="14.25" customHeight="1"/>
+    <row r="269" ht="14.25" customHeight="1"/>
+    <row r="270" ht="14.25" customHeight="1"/>
+    <row r="271" ht="14.25" customHeight="1"/>
+    <row r="272" ht="14.25" customHeight="1"/>
+    <row r="273" ht="14.25" customHeight="1"/>
+    <row r="274" ht="14.25" customHeight="1"/>
+    <row r="275" ht="14.25" customHeight="1"/>
+    <row r="276" ht="14.25" customHeight="1"/>
+    <row r="277" ht="14.25" customHeight="1"/>
+    <row r="278" ht="14.25" customHeight="1"/>
+    <row r="279" ht="14.25" customHeight="1"/>
+    <row r="280" ht="14.25" customHeight="1"/>
+    <row r="281" ht="14.25" customHeight="1"/>
+    <row r="282" ht="14.25" customHeight="1"/>
+    <row r="283" ht="14.25" customHeight="1"/>
+    <row r="284" ht="14.25" customHeight="1"/>
+    <row r="285" ht="14.25" customHeight="1"/>
+    <row r="286" ht="14.25" customHeight="1"/>
+    <row r="287" ht="14.25" customHeight="1"/>
+    <row r="288" ht="14.25" customHeight="1"/>
+    <row r="289" ht="14.25" customHeight="1"/>
+    <row r="290" ht="14.25" customHeight="1"/>
+    <row r="291" ht="14.25" customHeight="1"/>
+    <row r="292" ht="14.25" customHeight="1"/>
+    <row r="293" ht="14.25" customHeight="1"/>
+    <row r="294" ht="14.25" customHeight="1"/>
+    <row r="295" ht="14.25" customHeight="1"/>
+    <row r="296" ht="14.25" customHeight="1"/>
+    <row r="297" ht="14.25" customHeight="1"/>
+    <row r="298" ht="14.25" customHeight="1"/>
+    <row r="299" ht="14.25" customHeight="1"/>
+    <row r="300" ht="14.25" customHeight="1"/>
+    <row r="301" ht="14.25" customHeight="1"/>
+    <row r="302" ht="14.25" customHeight="1"/>
+    <row r="303" ht="14.25" customHeight="1"/>
+    <row r="304" ht="14.25" customHeight="1"/>
+    <row r="305" ht="14.25" customHeight="1"/>
+    <row r="306" ht="14.25" customHeight="1"/>
+    <row r="307" ht="14.25" customHeight="1"/>
+    <row r="308" ht="14.25" customHeight="1"/>
+    <row r="309" ht="14.25" customHeight="1"/>
+    <row r="310" ht="14.25" customHeight="1"/>
+    <row r="311" ht="14.25" customHeight="1"/>
+    <row r="312" ht="14.25" customHeight="1"/>
+    <row r="313" ht="14.25" customHeight="1"/>
+    <row r="314" ht="14.25" customHeight="1"/>
+    <row r="315" ht="14.25" customHeight="1"/>
+    <row r="316" ht="14.25" customHeight="1"/>
+    <row r="317" ht="14.25" customHeight="1"/>
+    <row r="318" ht="14.25" customHeight="1"/>
+    <row r="319" ht="14.25" customHeight="1"/>
+    <row r="320" ht="14.25" customHeight="1"/>
+    <row r="321" ht="14.25" customHeight="1"/>
+    <row r="322" ht="14.25" customHeight="1"/>
+    <row r="323" ht="14.25" customHeight="1"/>
+    <row r="324" ht="14.25" customHeight="1"/>
+    <row r="325" ht="14.25" customHeight="1"/>
+    <row r="326" ht="14.25" customHeight="1"/>
+    <row r="327" ht="14.25" customHeight="1"/>
+    <row r="328" ht="14.25" customHeight="1"/>
+    <row r="329" ht="14.25" customHeight="1"/>
+    <row r="330" ht="14.25" customHeight="1"/>
+    <row r="331" ht="14.25" customHeight="1"/>
+    <row r="332" ht="14.25" customHeight="1"/>
+    <row r="333" ht="14.25" customHeight="1"/>
+    <row r="334" ht="14.25" customHeight="1"/>
+    <row r="335" ht="14.25" customHeight="1"/>
+    <row r="336" ht="14.25" customHeight="1"/>
+    <row r="337" ht="14.25" customHeight="1"/>
+    <row r="338" ht="14.25" customHeight="1"/>
+    <row r="339" ht="14.25" customHeight="1"/>
+    <row r="340" ht="14.25" customHeight="1"/>
+    <row r="341" ht="14.25" customHeight="1"/>
+    <row r="342" ht="14.25" customHeight="1"/>
+    <row r="343" ht="14.25" customHeight="1"/>
+    <row r="344" ht="14.25" customHeight="1"/>
+    <row r="345" ht="14.25" customHeight="1"/>
+    <row r="346" ht="14.25" customHeight="1"/>
+    <row r="347" ht="14.25" customHeight="1"/>
+    <row r="348" ht="14.25" customHeight="1"/>
+    <row r="349" ht="14.25" customHeight="1"/>
+    <row r="350" ht="14.25" customHeight="1"/>
+    <row r="351" ht="14.25" customHeight="1"/>
+    <row r="352" ht="14.25" customHeight="1"/>
+    <row r="353" ht="14.25" customHeight="1"/>
+    <row r="354" ht="14.25" customHeight="1"/>
+    <row r="355" ht="14.25" customHeight="1"/>
+    <row r="356" ht="14.25" customHeight="1"/>
+    <row r="357" ht="14.25" customHeight="1"/>
+    <row r="358" ht="14.25" customHeight="1"/>
+    <row r="359" ht="14.25" customHeight="1"/>
+    <row r="360" ht="14.25" customHeight="1"/>
+    <row r="361" ht="14.25" customHeight="1"/>
+    <row r="362" ht="14.25" customHeight="1"/>
+    <row r="363" ht="14.25" customHeight="1"/>
+    <row r="364" ht="14.25" customHeight="1"/>
+    <row r="365" ht="14.25" customHeight="1"/>
+    <row r="366" ht="14.25" customHeight="1"/>
+    <row r="367" ht="14.25" customHeight="1"/>
+    <row r="368" ht="14.25" customHeight="1"/>
+    <row r="369" ht="14.25" customHeight="1"/>
+    <row r="370" ht="14.25" customHeight="1"/>
+    <row r="371" ht="14.25" customHeight="1"/>
+    <row r="372" ht="14.25" customHeight="1"/>
+    <row r="373" ht="14.25" customHeight="1"/>
+    <row r="374" ht="14.25" customHeight="1"/>
+    <row r="375" ht="14.25" customHeight="1"/>
+    <row r="376" ht="14.25" customHeight="1"/>
+    <row r="377" ht="14.25" customHeight="1"/>
+    <row r="378" ht="14.25" customHeight="1"/>
+    <row r="379" ht="14.25" customHeight="1"/>
+    <row r="380" ht="14.25" customHeight="1"/>
+    <row r="381" ht="14.25" customHeight="1"/>
+    <row r="382" ht="14.25" customHeight="1"/>
+    <row r="383" ht="14.25" customHeight="1"/>
+    <row r="384" ht="14.25" customHeight="1"/>
+    <row r="385" ht="14.25" customHeight="1"/>
+    <row r="386" ht="14.25" customHeight="1"/>
+    <row r="387" ht="14.25" customHeight="1"/>
+    <row r="388" ht="14.25" customHeight="1"/>
+    <row r="389" ht="14.25" customHeight="1"/>
+    <row r="390" ht="14.25" customHeight="1"/>
+    <row r="391" ht="14.25" customHeight="1"/>
+    <row r="392" ht="14.25" customHeight="1"/>
+    <row r="393" ht="14.25" customHeight="1"/>
+    <row r="394" ht="14.25" customHeight="1"/>
+    <row r="395" ht="14.25" customHeight="1"/>
+    <row r="396" ht="14.25" customHeight="1"/>
+    <row r="397" ht="14.25" customHeight="1"/>
+    <row r="398" ht="14.25" customHeight="1"/>
+    <row r="399" ht="14.25" customHeight="1"/>
+    <row r="400" ht="14.25" customHeight="1"/>
+    <row r="401" ht="14.25" customHeight="1"/>
+    <row r="402" ht="14.25" customHeight="1"/>
+    <row r="403" ht="14.25" customHeight="1"/>
+    <row r="404" ht="14.25" customHeight="1"/>
+    <row r="405" ht="14.25" customHeight="1"/>
+    <row r="406" ht="14.25" customHeight="1"/>
+    <row r="407" ht="14.25" customHeight="1"/>
+    <row r="408" ht="14.25" customHeight="1"/>
+    <row r="409" ht="14.25" customHeight="1"/>
+    <row r="410" ht="14.25" customHeight="1"/>
+    <row r="411" ht="14.25" customHeight="1"/>
+    <row r="412" ht="14.25" customHeight="1"/>
+    <row r="413" ht="14.25" customHeight="1"/>
+    <row r="414" ht="14.25" customHeight="1"/>
+    <row r="415" ht="14.25" customHeight="1"/>
+    <row r="416" ht="14.25" customHeight="1"/>
+    <row r="417" ht="14.25" customHeight="1"/>
+    <row r="418" ht="14.25" customHeight="1"/>
+    <row r="419" ht="14.25" customHeight="1"/>
+    <row r="420" ht="14.25" customHeight="1"/>
+    <row r="421" ht="14.25" customHeight="1"/>
+    <row r="422" ht="14.25" customHeight="1"/>
+    <row r="423" ht="14.25" customHeight="1"/>
+    <row r="424" ht="14.25" customHeight="1"/>
+    <row r="425" ht="14.25" customHeight="1"/>
+    <row r="426" ht="14.25" customHeight="1"/>
+    <row r="427" ht="14.25" customHeight="1"/>
+    <row r="428" ht="14.25" customHeight="1"/>
+    <row r="429" ht="14.25" customHeight="1"/>
+    <row r="430" ht="14.25" customHeight="1"/>
+    <row r="431" ht="14.25" customHeight="1"/>
+    <row r="432" ht="14.25" customHeight="1"/>
+    <row r="433" ht="14.25" customHeight="1"/>
+    <row r="434" ht="14.25" customHeight="1"/>
+    <row r="435" ht="14.25" customHeight="1"/>
+    <row r="436" ht="14.25" customHeight="1"/>
+    <row r="437" ht="14.25" customHeight="1"/>
+    <row r="438" ht="14.25" customHeight="1"/>
+    <row r="439" ht="14.25" customHeight="1"/>
+    <row r="440" ht="14.25" customHeight="1"/>
+    <row r="441" ht="14.25" customHeight="1"/>
+    <row r="442" ht="14.25" customHeight="1"/>
+    <row r="443" ht="14.25" customHeight="1"/>
+    <row r="444" ht="14.25" customHeight="1"/>
+    <row r="445" ht="14.25" customHeight="1"/>
+    <row r="446" ht="14.25" customHeight="1"/>
+    <row r="447" ht="14.25" customHeight="1"/>
+    <row r="448" ht="14.25" customHeight="1"/>
+    <row r="449" ht="14.25" customHeight="1"/>
+    <row r="450" ht="14.25" customHeight="1"/>
+    <row r="451" ht="14.25" customHeight="1"/>
+    <row r="452" ht="14.25" customHeight="1"/>
+    <row r="453" ht="14.25" customHeight="1"/>
+    <row r="454" ht="14.25" customHeight="1"/>
+    <row r="455" ht="14.25" customHeight="1"/>
+    <row r="456" ht="14.25" customHeight="1"/>
+    <row r="457" ht="14.25" customHeight="1"/>
+    <row r="458" ht="14.25" customHeight="1"/>
+    <row r="459" ht="14.25" customHeight="1"/>
+    <row r="460" ht="14.25" customHeight="1"/>
+    <row r="461" ht="14.25" customHeight="1"/>
+    <row r="462" ht="14.25" customHeight="1"/>
+    <row r="463" ht="14.25" customHeight="1"/>
+    <row r="464" ht="14.25" customHeight="1"/>
+    <row r="465" ht="14.25" customHeight="1"/>
+    <row r="466" ht="14.25" customHeight="1"/>
+    <row r="467" ht="14.25" customHeight="1"/>
+    <row r="468" ht="14.25" customHeight="1"/>
+    <row r="469" ht="14.25" customHeight="1"/>
+    <row r="470" ht="14.25" customHeight="1"/>
+    <row r="471" ht="14.25" customHeight="1"/>
+    <row r="472" ht="14.25" customHeight="1"/>
+    <row r="473" ht="14.25" customHeight="1"/>
+    <row r="474" ht="14.25" customHeight="1"/>
+    <row r="475" ht="14.25" customHeight="1"/>
+    <row r="476" ht="14.25" customHeight="1"/>
+    <row r="477" ht="14.25" customHeight="1"/>
+    <row r="478" ht="14.25" customHeight="1"/>
+    <row r="479" ht="14.25" customHeight="1"/>
+    <row r="480" ht="14.25" customHeight="1"/>
+    <row r="481" ht="14.25" customHeight="1"/>
+    <row r="482" ht="14.25" customHeight="1"/>
+    <row r="483" ht="14.25" customHeight="1"/>
+    <row r="484" ht="14.25" customHeight="1"/>
+    <row r="485" ht="14.25" customHeight="1"/>
+    <row r="486" ht="14.25" customHeight="1"/>
+    <row r="487" ht="14.25" customHeight="1"/>
+    <row r="488" ht="14.25" customHeight="1"/>
+    <row r="489" ht="14.25" customHeight="1"/>
+    <row r="490" ht="14.25" customHeight="1"/>
+    <row r="491" ht="14.25" customHeight="1"/>
+    <row r="492" ht="14.25" customHeight="1"/>
+    <row r="493" ht="14.25" customHeight="1"/>
+    <row r="494" ht="14.25" customHeight="1"/>
+    <row r="495" ht="14.25" customHeight="1"/>
+    <row r="496" ht="14.25" customHeight="1"/>
+    <row r="497" ht="14.25" customHeight="1"/>
+    <row r="498" ht="14.25" customHeight="1"/>
+    <row r="499" ht="14.25" customHeight="1"/>
+    <row r="500" ht="14.25" customHeight="1"/>
+    <row r="501" ht="14.25" customHeight="1"/>
+    <row r="502" ht="14.25" customHeight="1"/>
+    <row r="503" ht="14.25" customHeight="1"/>
+    <row r="504" ht="14.25" customHeight="1"/>
+    <row r="505" ht="14.25" customHeight="1"/>
+    <row r="506" ht="14.25" customHeight="1"/>
+    <row r="507" ht="14.25" customHeight="1"/>
+    <row r="508" ht="14.25" customHeight="1"/>
+    <row r="509" ht="14.25" customHeight="1"/>
+    <row r="510" ht="14.25" customHeight="1"/>
+    <row r="511" ht="14.25" customHeight="1"/>
+    <row r="512" ht="14.25" customHeight="1"/>
+    <row r="513" ht="14.25" customHeight="1"/>
+    <row r="514" ht="14.25" customHeight="1"/>
+    <row r="515" ht="14.25" customHeight="1"/>
+    <row r="516" ht="14.25" customHeight="1"/>
+    <row r="517" ht="14.25" customHeight="1"/>
+    <row r="518" ht="14.25" customHeight="1"/>
+    <row r="519" ht="14.25" customHeight="1"/>
+    <row r="520" ht="14.25" customHeight="1"/>
+    <row r="521" ht="14.25" customHeight="1"/>
+    <row r="522" ht="14.25" customHeight="1"/>
+    <row r="523" ht="14.25" customHeight="1"/>
+    <row r="524" ht="14.25" customHeight="1"/>
+    <row r="525" ht="14.25" customHeight="1"/>
+    <row r="526" ht="14.25" customHeight="1"/>
+    <row r="527" ht="14.25" customHeight="1"/>
+    <row r="528" ht="14.25" customHeight="1"/>
+    <row r="529" ht="14.25" customHeight="1"/>
+    <row r="530" ht="14.25" customHeight="1"/>
+    <row r="531" ht="14.25" customHeight="1"/>
+    <row r="532" ht="14.25" customHeight="1"/>
+    <row r="533" ht="14.25" customHeight="1"/>
+    <row r="534" ht="14.25" customHeight="1"/>
+    <row r="535" ht="14.25" customHeight="1"/>
+    <row r="536" ht="14.25" customHeight="1"/>
+    <row r="537" ht="14.25" customHeight="1"/>
+    <row r="538" ht="14.25" customHeight="1"/>
+    <row r="539" ht="14.25" customHeight="1"/>
+    <row r="540" ht="14.25" customHeight="1"/>
+    <row r="541" ht="14.25" customHeight="1"/>
+    <row r="542" ht="14.25" customHeight="1"/>
+    <row r="543" ht="14.25" customHeight="1"/>
+    <row r="544" ht="14.25" customHeight="1"/>
+    <row r="545" ht="14.25" customHeight="1"/>
+    <row r="546" ht="14.25" customHeight="1"/>
+    <row r="547" ht="14.25" customHeight="1"/>
+    <row r="548" ht="14.25" customHeight="1"/>
+    <row r="549" ht="14.25" customHeight="1"/>
+    <row r="550" ht="14.25" customHeight="1"/>
+    <row r="551" ht="14.25" customHeight="1"/>
+    <row r="552" ht="14.25" customHeight="1"/>
+    <row r="553" ht="14.25" customHeight="1"/>
+    <row r="554" ht="14.25" customHeight="1"/>
+    <row r="555" ht="14.25" customHeight="1"/>
+    <row r="556" ht="14.25" customHeight="1"/>
+    <row r="557" ht="14.25" customHeight="1"/>
+    <row r="558" ht="14.25" customHeight="1"/>
+    <row r="559" ht="14.25" customHeight="1"/>
+    <row r="560" ht="14.25" customHeight="1"/>
+    <row r="561" ht="14.25" customHeight="1"/>
+    <row r="562" ht="14.25" customHeight="1"/>
+    <row r="563" ht="14.25" customHeight="1"/>
+    <row r="564" ht="14.25" customHeight="1"/>
+    <row r="565" ht="14.25" customHeight="1"/>
+    <row r="566" ht="14.25" customHeight="1"/>
+    <row r="567" ht="14.25" customHeight="1"/>
+    <row r="568" ht="14.25" customHeight="1"/>
+    <row r="569" ht="14.25" customHeight="1"/>
+    <row r="570" ht="14.25" customHeight="1"/>
+    <row r="571" ht="14.25" customHeight="1"/>
+    <row r="572" ht="14.25" customHeight="1"/>
+    <row r="573" ht="14.25" customHeight="1"/>
+    <row r="574" ht="14.25" customHeight="1"/>
+    <row r="575" ht="14.25" customHeight="1"/>
+    <row r="576" ht="14.25" customHeight="1"/>
+    <row r="577" ht="14.25" customHeight="1"/>
+    <row r="578" ht="14.25" customHeight="1"/>
+    <row r="579" ht="14.25" customHeight="1"/>
+    <row r="580" ht="14.25" customHeight="1"/>
+    <row r="581" ht="14.25" customHeight="1"/>
+    <row r="582" ht="14.25" customHeight="1"/>
+    <row r="583" ht="14.25" customHeight="1"/>
+    <row r="584" ht="14.25" customHeight="1"/>
+    <row r="585" ht="14.25" customHeight="1"/>
+    <row r="586" ht="14.25" customHeight="1"/>
+    <row r="587" ht="14.25" customHeight="1"/>
+    <row r="588" ht="14.25" customHeight="1"/>
+    <row r="589" ht="14.25" customHeight="1"/>
+    <row r="590" ht="14.25" customHeight="1"/>
+    <row r="591" ht="14.25" customHeight="1"/>
+    <row r="592" ht="14.25" customHeight="1"/>
+    <row r="593" ht="14.25" customHeight="1"/>
+    <row r="594" ht="14.25" customHeight="1"/>
+    <row r="595" ht="14.25" customHeight="1"/>
+    <row r="596" ht="14.25" customHeight="1"/>
+    <row r="597" ht="14.25" customHeight="1"/>
+    <row r="598" ht="14.25" customHeight="1"/>
+    <row r="599" ht="14.25" customHeight="1"/>
+    <row r="600" ht="14.25" customHeight="1"/>
+    <row r="601" ht="14.25" customHeight="1"/>
+    <row r="602" ht="14.25" customHeight="1"/>
+    <row r="603" ht="14.25" customHeight="1"/>
+    <row r="604" ht="14.25" customHeight="1"/>
+    <row r="605" ht="14.25" customHeight="1"/>
+    <row r="606" ht="14.25" customHeight="1"/>
+    <row r="607" ht="14.25" customHeight="1"/>
+    <row r="608" ht="14.25" customHeight="1"/>
+    <row r="609" ht="14.25" customHeight="1"/>
+    <row r="610" ht="14.25" customHeight="1"/>
+    <row r="611" ht="14.25" customHeight="1"/>
+    <row r="612" ht="14.25" customHeight="1"/>
+    <row r="613" ht="14.25" customHeight="1"/>
+    <row r="614" ht="14.25" customHeight="1"/>
+    <row r="615" ht="14.25" customHeight="1"/>
+    <row r="616" ht="14.25" customHeight="1"/>
+    <row r="617" ht="14.25" customHeight="1"/>
+    <row r="618" ht="14.25" customHeight="1"/>
+    <row r="619" ht="14.25" customHeight="1"/>
+    <row r="620" ht="14.25" customHeight="1"/>
+    <row r="621" ht="14.25" customHeight="1"/>
+    <row r="622" ht="14.25" customHeight="1"/>
+    <row r="623" ht="14.25" customHeight="1"/>
+    <row r="624" ht="14.25" customHeight="1"/>
+    <row r="625" ht="14.25" customHeight="1"/>
+    <row r="626" ht="14.25" customHeight="1"/>
+    <row r="627" ht="14.25" customHeight="1"/>
+    <row r="628" ht="14.25" customHeight="1"/>
+    <row r="629" ht="14.25" customHeight="1"/>
+    <row r="630" ht="14.25" customHeight="1"/>
+    <row r="631" ht="14.25" customHeight="1"/>
+    <row r="632" ht="14.25" customHeight="1"/>
+    <row r="633" ht="14.25" customHeight="1"/>
+    <row r="634" ht="14.25" customHeight="1"/>
+    <row r="635" ht="14.25" customHeight="1"/>
+    <row r="636" ht="14.25" customHeight="1"/>
+    <row r="637" ht="14.25" customHeight="1"/>
+    <row r="638" ht="14.25" customHeight="1"/>
+    <row r="639" ht="14.25" customHeight="1"/>
+    <row r="640" ht="14.25" customHeight="1"/>
+    <row r="641" ht="14.25" customHeight="1"/>
+    <row r="642" ht="14.25" customHeight="1"/>
+    <row r="643" ht="14.25" customHeight="1"/>
+    <row r="644" ht="14.25" customHeight="1"/>
+    <row r="645" ht="14.25" customHeight="1"/>
+    <row r="646" ht="14.25" customHeight="1"/>
+    <row r="647" ht="14.25" customHeight="1"/>
+    <row r="648" ht="14.25" customHeight="1"/>
+    <row r="649" ht="14.25" customHeight="1"/>
+    <row r="650" ht="14.25" customHeight="1"/>
+    <row r="651" ht="14.25" customHeight="1"/>
+    <row r="652" ht="14.25" customHeight="1"/>
+    <row r="653" ht="14.25" customHeight="1"/>
+    <row r="654" ht="14.25" customHeight="1"/>
+    <row r="655" ht="14.25" customHeight="1"/>
+    <row r="656" ht="14.25" customHeight="1"/>
+    <row r="657" ht="14.25" customHeight="1"/>
+    <row r="658" ht="14.25" customHeight="1"/>
+    <row r="659" ht="14.25" customHeight="1"/>
+    <row r="660" ht="14.25" customHeight="1"/>
+    <row r="661" ht="14.25" customHeight="1"/>
+    <row r="662" ht="14.25" customHeight="1"/>
+    <row r="663" ht="14.25" customHeight="1"/>
+    <row r="664" ht="14.25" customHeight="1"/>
+    <row r="665" ht="14.25" customHeight="1"/>
+    <row r="666" ht="14.25" customHeight="1"/>
+    <row r="667" ht="14.25" customHeight="1"/>
+    <row r="668" ht="14.25" customHeight="1"/>
+    <row r="669" ht="14.25" customHeight="1"/>
+    <row r="670" ht="14.25" customHeight="1"/>
+    <row r="671" ht="14.25" customHeight="1"/>
+    <row r="672" ht="14.25" customHeight="1"/>
+    <row r="673" ht="14.25" customHeight="1"/>
+    <row r="674" ht="14.25" customHeight="1"/>
+    <row r="675" ht="14.25" customHeight="1"/>
+    <row r="676" ht="14.25" customHeight="1"/>
+    <row r="677" ht="14.25" customHeight="1"/>
+    <row r="678" ht="14.25" customHeight="1"/>
+    <row r="679" ht="14.25" customHeight="1"/>
+    <row r="680" ht="14.25" customHeight="1"/>
+    <row r="681" ht="14.25" customHeight="1"/>
+    <row r="682" ht="14.25" customHeight="1"/>
+    <row r="683" ht="14.25" customHeight="1"/>
+    <row r="684" ht="14.25" customHeight="1"/>
+    <row r="685" ht="14.25" customHeight="1"/>
+    <row r="686" ht="14.25" customHeight="1"/>
+    <row r="687" ht="14.25" customHeight="1"/>
+    <row r="688" ht="14.25" customHeight="1"/>
+    <row r="689" ht="14.25" customHeight="1"/>
+    <row r="690" ht="14.25" customHeight="1"/>
+    <row r="691" ht="14.25" customHeight="1"/>
+    <row r="692" ht="14.25" customHeight="1"/>
+    <row r="693" ht="14.25" customHeight="1"/>
+    <row r="694" ht="14.25" customHeight="1"/>
+    <row r="695" ht="14.25" customHeight="1"/>
+    <row r="696" ht="14.25" customHeight="1"/>
+    <row r="697" ht="14.25" customHeight="1"/>
+    <row r="698" ht="14.25" customHeight="1"/>
+    <row r="699" ht="14.25" customHeight="1"/>
+    <row r="700" ht="14.25" customHeight="1"/>
+    <row r="701" ht="14.25" customHeight="1"/>
+    <row r="702" ht="14.25" customHeight="1"/>
+    <row r="703" ht="14.25" customHeight="1"/>
+    <row r="704" ht="14.25" customHeight="1"/>
+    <row r="705" ht="14.25" customHeight="1"/>
+    <row r="706" ht="14.25" customHeight="1"/>
+    <row r="707" ht="14.25" customHeight="1"/>
+    <row r="708" ht="14.25" customHeight="1"/>
+    <row r="709" ht="14.25" customHeight="1"/>
+    <row r="710" ht="14.25" customHeight="1"/>
+    <row r="711" ht="14.25" customHeight="1"/>
+    <row r="712" ht="14.25" customHeight="1"/>
+    <row r="713" ht="14.25" customHeight="1"/>
+    <row r="714" ht="14.25" customHeight="1"/>
+    <row r="715" ht="14.25" customHeight="1"/>
+    <row r="716" ht="14.25" customHeight="1"/>
+    <row r="717" ht="14.25" customHeight="1"/>
+    <row r="718" ht="14.25" customHeight="1"/>
+    <row r="719" ht="14.25" customHeight="1"/>
+    <row r="720" ht="14.25" customHeight="1"/>
+    <row r="721" ht="14.25" customHeight="1"/>
+    <row r="722" ht="14.25" customHeight="1"/>
+    <row r="723" ht="14.25" customHeight="1"/>
+    <row r="724" ht="14.25" customHeight="1"/>
+    <row r="725" ht="14.25" customHeight="1"/>
+    <row r="726" ht="14.25" customHeight="1"/>
+    <row r="727" ht="14.25" customHeight="1"/>
+    <row r="728" ht="14.25" customHeight="1"/>
+    <row r="729" ht="14.25" customHeight="1"/>
+    <row r="730" ht="14.25" customHeight="1"/>
+    <row r="731" ht="14.25" customHeight="1"/>
+    <row r="732" ht="14.25" customHeight="1"/>
+    <row r="733" ht="14.25" customHeight="1"/>
+    <row r="734" ht="14.25" customHeight="1"/>
+    <row r="735" ht="14.25" customHeight="1"/>
+    <row r="736" ht="14.25" customHeight="1"/>
+    <row r="737" ht="14.25" customHeight="1"/>
+    <row r="738" ht="14.25" customHeight="1"/>
+    <row r="739" ht="14.25" customHeight="1"/>
+    <row r="740" ht="14.25" customHeight="1"/>
+    <row r="741" ht="14.25" customHeight="1"/>
+    <row r="742" ht="14.25" customHeight="1"/>
+    <row r="743" ht="14.25" customHeight="1"/>
+    <row r="744" ht="14.25" customHeight="1"/>
+    <row r="745" ht="14.25" customHeight="1"/>
+    <row r="746" ht="14.25" customHeight="1"/>
+    <row r="747" ht="14.25" customHeight="1"/>
+    <row r="748" ht="14.25" customHeight="1"/>
+    <row r="749" ht="14.25" customHeight="1"/>
+    <row r="750" ht="14.25" customHeight="1"/>
+    <row r="751" ht="14.25" customHeight="1"/>
+    <row r="752" ht="14.25" customHeight="1"/>
+    <row r="753" ht="14.25" customHeight="1"/>
+    <row r="754" ht="14.25" customHeight="1"/>
+    <row r="755" ht="14.25" customHeight="1"/>
+    <row r="756" ht="14.25" customHeight="1"/>
+    <row r="757" ht="14.25" customHeight="1"/>
+    <row r="758" ht="14.25" customHeight="1"/>
+    <row r="759" ht="14.25" customHeight="1"/>
+    <row r="760" ht="14.25" customHeight="1"/>
+    <row r="761" ht="14.25" customHeight="1"/>
+    <row r="762" ht="14.25" customHeight="1"/>
+    <row r="763" ht="14.25" customHeight="1"/>
+    <row r="764" ht="14.25" customHeight="1"/>
+    <row r="765" ht="14.25" customHeight="1"/>
+    <row r="766" ht="14.25" customHeight="1"/>
+    <row r="767" ht="14.25" customHeight="1"/>
+    <row r="768" ht="14.25" customHeight="1"/>
+    <row r="769" ht="14.25" customHeight="1"/>
+    <row r="770" ht="14.25" customHeight="1"/>
+    <row r="771" ht="14.25" customHeight="1"/>
+    <row r="772" ht="14.25" customHeight="1"/>
+    <row r="773" ht="14.25" customHeight="1"/>
+    <row r="774" ht="14.25" customHeight="1"/>
+    <row r="775" ht="14.25" customHeight="1"/>
+    <row r="776" ht="14.25" customHeight="1"/>
+    <row r="777" ht="14.25" customHeight="1"/>
+    <row r="778" ht="14.25" customHeight="1"/>
+    <row r="779" ht="14.25" customHeight="1"/>
+    <row r="780" ht="14.25" customHeight="1"/>
+    <row r="781" ht="14.25" customHeight="1"/>
+    <row r="782" ht="14.25" customHeight="1"/>
+    <row r="783" ht="14.25" customHeight="1"/>
+    <row r="784" ht="14.25" customHeight="1"/>
+    <row r="785" ht="14.25" customHeight="1"/>
+    <row r="786" ht="14.25" customHeight="1"/>
+    <row r="787" ht="14.25" customHeight="1"/>
+    <row r="788" ht="14.25" customHeight="1"/>
+    <row r="789" ht="14.25" customHeight="1"/>
+    <row r="790" ht="14.25" customHeight="1"/>
+    <row r="791" ht="14.25" customHeight="1"/>
+    <row r="792" ht="14.25" customHeight="1"/>
+    <row r="793" ht="14.25" customHeight="1"/>
+    <row r="794" ht="14.25" customHeight="1"/>
+    <row r="795" ht="14.25" customHeight="1"/>
+    <row r="796" ht="14.25" customHeight="1"/>
+    <row r="797" ht="14.25" customHeight="1"/>
+    <row r="798" ht="14.25" customHeight="1"/>
+    <row r="799" ht="14.25" customHeight="1"/>
+    <row r="800" ht="14.25" customHeight="1"/>
+    <row r="801" ht="14.25" customHeight="1"/>
+    <row r="802" ht="14.25" customHeight="1"/>
+    <row r="803" ht="14.25" customHeight="1"/>
+    <row r="804" ht="14.25" customHeight="1"/>
+    <row r="805" ht="14.25" customHeight="1"/>
+    <row r="806" ht="14.25" customHeight="1"/>
+    <row r="807" ht="14.25" customHeight="1"/>
+    <row r="808" ht="14.25" customHeight="1"/>
+    <row r="809" ht="14.25" customHeight="1"/>
+    <row r="810" ht="14.25" customHeight="1"/>
+    <row r="811" ht="14.25" customHeight="1"/>
+    <row r="812" ht="14.25" customHeight="1"/>
+    <row r="813" ht="14.25" customHeight="1"/>
+    <row r="814" ht="14.25" customHeight="1"/>
+    <row r="815" ht="14.25" customHeight="1"/>
+    <row r="816" ht="14.25" customHeight="1"/>
+    <row r="817" ht="14.25" customHeight="1"/>
+    <row r="818" ht="14.25" customHeight="1"/>
+    <row r="819" ht="14.25" customHeight="1"/>
+    <row r="820" ht="14.25" customHeight="1"/>
+    <row r="821" ht="14.25" customHeight="1"/>
+    <row r="822" ht="14.25" customHeight="1"/>
+    <row r="823" ht="14.25" customHeight="1"/>
+    <row r="824" ht="14.25" customHeight="1"/>
+    <row r="825" ht="14.25" customHeight="1"/>
+    <row r="826" ht="14.25" customHeight="1"/>
+    <row r="827" ht="14.25" customHeight="1"/>
+    <row r="828" ht="14.25" customHeight="1"/>
+    <row r="829" ht="14.25" customHeight="1"/>
+    <row r="830" ht="14.25" customHeight="1"/>
+    <row r="831" ht="14.25" customHeight="1"/>
+    <row r="832" ht="14.25" customHeight="1"/>
+    <row r="833" ht="14.25" customHeight="1"/>
+    <row r="834" ht="14.25" customHeight="1"/>
+    <row r="835" ht="14.25" customHeight="1"/>
+    <row r="836" ht="14.25" customHeight="1"/>
+    <row r="837" ht="14.25" customHeight="1"/>
+    <row r="838" ht="14.25" customHeight="1"/>
+    <row r="839" ht="14.25" customHeight="1"/>
+    <row r="840" ht="14.25" customHeight="1"/>
+    <row r="841" ht="14.25" customHeight="1"/>
+    <row r="842" ht="14.25" customHeight="1"/>
+    <row r="843" ht="14.25" customHeight="1"/>
+    <row r="844" ht="14.25" customHeight="1"/>
+    <row r="845" ht="14.25" customHeight="1"/>
+    <row r="846" ht="14.25" customHeight="1"/>
+    <row r="847" ht="14.25" customHeight="1"/>
+    <row r="848" ht="14.25" customHeight="1"/>
+    <row r="849" ht="14.25" customHeight="1"/>
+    <row r="850" ht="14.25" customHeight="1"/>
+    <row r="851" ht="14.25" customHeight="1"/>
+    <row r="852" ht="14.25" customHeight="1"/>
+    <row r="853" ht="14.25" customHeight="1"/>
+    <row r="854" ht="14.25" customHeight="1"/>
+    <row r="855" ht="14.25" customHeight="1"/>
+    <row r="856" ht="14.25" customHeight="1"/>
+    <row r="857" ht="14.25" customHeight="1"/>
+    <row r="858" ht="14.25" customHeight="1"/>
+    <row r="859" ht="14.25" customHeight="1"/>
+    <row r="860" ht="14.25" customHeight="1"/>
+    <row r="861" ht="14.25" customHeight="1"/>
+    <row r="862" ht="14.25" customHeight="1"/>
+    <row r="863" ht="14.25" customHeight="1"/>
+    <row r="864" ht="14.25" customHeight="1"/>
+    <row r="865" ht="14.25" customHeight="1"/>
+    <row r="866" ht="14.25" customHeight="1"/>
+    <row r="867" ht="14.25" customHeight="1"/>
+    <row r="868" ht="14.25" customHeight="1"/>
+    <row r="869" ht="14.25" customHeight="1"/>
+    <row r="870" ht="14.25" customHeight="1"/>
+    <row r="871" ht="14.25" customHeight="1"/>
+    <row r="872" ht="14.25" customHeight="1"/>
+    <row r="873" ht="14.25" customHeight="1"/>
+    <row r="874" ht="14.25" customHeight="1"/>
+    <row r="875" ht="14.25" customHeight="1"/>
+    <row r="876" ht="14.25" customHeight="1"/>
+    <row r="877" ht="14.25" customHeight="1"/>
+    <row r="878" ht="14.25" customHeight="1"/>
+    <row r="879" ht="14.25" customHeight="1"/>
+    <row r="880" ht="14.25" customHeight="1"/>
+    <row r="881" ht="14.25" customHeight="1"/>
+    <row r="882" ht="14.25" customHeight="1"/>
+    <row r="883" ht="14.25" customHeight="1"/>
+    <row r="884" ht="14.25" customHeight="1"/>
+    <row r="885" ht="14.25" customHeight="1"/>
+    <row r="886" ht="14.25" customHeight="1"/>
+    <row r="887" ht="14.25" customHeight="1"/>
+    <row r="888" ht="14.25" customHeight="1"/>
+    <row r="889" ht="14.25" customHeight="1"/>
+    <row r="890" ht="14.25" customHeight="1"/>
+    <row r="891" ht="14.25" customHeight="1"/>
+    <row r="892" ht="14.25" customHeight="1"/>
+    <row r="893" ht="14.25" customHeight="1"/>
+    <row r="894" ht="14.25" customHeight="1"/>
+    <row r="895" ht="14.25" customHeight="1"/>
+    <row r="896" ht="14.25" customHeight="1"/>
+    <row r="897" ht="14.25" customHeight="1"/>
+    <row r="898" ht="14.25" customHeight="1"/>
+    <row r="899" ht="14.25" customHeight="1"/>
+    <row r="900" ht="14.25" customHeight="1"/>
+    <row r="901" ht="14.25" customHeight="1"/>
+    <row r="902" ht="14.25" customHeight="1"/>
+    <row r="903" ht="14.25" customHeight="1"/>
+    <row r="904" ht="14.25" customHeight="1"/>
+    <row r="905" ht="14.25" customHeight="1"/>
+    <row r="906" ht="14.25" customHeight="1"/>
+    <row r="907" ht="14.25" customHeight="1"/>
+    <row r="908" ht="14.25" customHeight="1"/>
+    <row r="909" ht="14.25" customHeight="1"/>
+    <row r="910" ht="14.25" customHeight="1"/>
+    <row r="911" ht="14.25" customHeight="1"/>
+    <row r="912" ht="14.25" customHeight="1"/>
+    <row r="913" ht="14.25" customHeight="1"/>
+    <row r="914" ht="14.25" customHeight="1"/>
+    <row r="915" ht="14.25" customHeight="1"/>
+    <row r="916" ht="14.25" customHeight="1"/>
+    <row r="917" ht="14.25" customHeight="1"/>
+    <row r="918" ht="14.25" customHeight="1"/>
+    <row r="919" ht="14.25" customHeight="1"/>
+    <row r="920" ht="14.25" customHeight="1"/>
+    <row r="921" ht="14.25" customHeight="1"/>
+    <row r="922" ht="14.25" customHeight="1"/>
+    <row r="923" ht="14.25" customHeight="1"/>
+    <row r="924" ht="14.25" customHeight="1"/>
+    <row r="925" ht="14.25" customHeight="1"/>
+    <row r="926" ht="14.25" customHeight="1"/>
+    <row r="927" ht="14.25" customHeight="1"/>
+    <row r="928" ht="14.25" customHeight="1"/>
+    <row r="929" ht="14.25" customHeight="1"/>
+    <row r="930" ht="14.25" customHeight="1"/>
+    <row r="931" ht="14.25" customHeight="1"/>
+    <row r="932" ht="14.25" customHeight="1"/>
+    <row r="933" ht="14.25" customHeight="1"/>
+    <row r="934" ht="14.25" customHeight="1"/>
+    <row r="935" ht="14.25" customHeight="1"/>
+    <row r="936" ht="14.25" customHeight="1"/>
+    <row r="937" ht="14.25" customHeight="1"/>
+    <row r="938" ht="14.25" customHeight="1"/>
+    <row r="939" ht="14.25" customHeight="1"/>
+    <row r="940" ht="14.25" customHeight="1"/>
+    <row r="941" ht="14.25" customHeight="1"/>
+    <row r="942" ht="14.25" customHeight="1"/>
+    <row r="943" ht="14.25" customHeight="1"/>
+    <row r="944" ht="14.25" customHeight="1"/>
+    <row r="945" ht="14.25" customHeight="1"/>
+    <row r="946" ht="14.25" customHeight="1"/>
+    <row r="947" ht="14.25" customHeight="1"/>
+    <row r="948" ht="14.25" customHeight="1"/>
+    <row r="949" ht="14.25" customHeight="1"/>
+    <row r="950" ht="14.25" customHeight="1"/>
+    <row r="951" ht="14.25" customHeight="1"/>
+    <row r="952" ht="14.25" customHeight="1"/>
+    <row r="953" ht="14.25" customHeight="1"/>
+    <row r="954" ht="14.25" customHeight="1"/>
+    <row r="955" ht="14.25" customHeight="1"/>
+    <row r="956" ht="14.25" customHeight="1"/>
+    <row r="957" ht="14.25" customHeight="1"/>
+    <row r="958" ht="14.25" customHeight="1"/>
+    <row r="959" ht="14.25" customHeight="1"/>
+    <row r="960" ht="14.25" customHeight="1"/>
+    <row r="961" ht="14.25" customHeight="1"/>
+    <row r="962" ht="14.25" customHeight="1"/>
+    <row r="963" ht="14.25" customHeight="1"/>
+    <row r="964" ht="14.25" customHeight="1"/>
+    <row r="965" ht="14.25" customHeight="1"/>
+    <row r="966" ht="14.25" customHeight="1"/>
+    <row r="967" ht="14.25" customHeight="1"/>
+    <row r="968" ht="14.25" customHeight="1"/>
+    <row r="969" ht="14.25" customHeight="1"/>
+    <row r="970" ht="14.25" customHeight="1"/>
+    <row r="971" ht="14.25" customHeight="1"/>
+    <row r="972" ht="14.25" customHeight="1"/>
+    <row r="973" ht="14.25" customHeight="1"/>
+    <row r="974" ht="14.25" customHeight="1"/>
+    <row r="975" ht="14.25" customHeight="1"/>
+    <row r="976" ht="14.25" customHeight="1"/>
+    <row r="977" ht="14.25" customHeight="1"/>
+    <row r="978" ht="14.25" customHeight="1"/>
+    <row r="979" ht="14.25" customHeight="1"/>
+    <row r="980" ht="14.25" customHeight="1"/>
+    <row r="981" ht="14.25" customHeight="1"/>
+    <row r="982" ht="14.25" customHeight="1"/>
+    <row r="983" ht="14.25" customHeight="1"/>
+    <row r="984" ht="14.25" customHeight="1"/>
+    <row r="985" ht="14.25" customHeight="1"/>
+    <row r="986" ht="14.25" customHeight="1"/>
+    <row r="987" ht="14.25" customHeight="1"/>
+    <row r="988" ht="14.25" customHeight="1"/>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42.88671875" customWidth="1" min="1" max="1"/>
+    <col width="10.109375" customWidth="1" min="2" max="2"/>
+    <col width="11.109375" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>Chỉ tiêu</t>
         </is>
       </c>
-      <c r="B3" s="9">
-        <f>'balance_sheet'!B1</f>
-        <v/>
-      </c>
-      <c r="C3" s="9">
-        <f>'balance_sheet'!C1</f>
-        <v/>
-      </c>
-      <c r="D3" s="9">
-        <f>'balance_sheet'!D1</f>
-        <v/>
-      </c>
-      <c r="E3" s="9">
-        <f>'balance_sheet'!E1</f>
-        <v/>
-      </c>
-      <c r="F3" s="9">
-        <f>'balance_sheet'!F1</f>
-        <v/>
-      </c>
-      <c r="G3" s="9">
-        <f>'balance_sheet'!G1</f>
-        <v/>
-      </c>
-      <c r="H3" s="9">
-        <f>'balance_sheet'!H1</f>
-        <v/>
-      </c>
-      <c r="I3" s="9">
-        <f>'balance_sheet'!I1</f>
-        <v/>
-      </c>
+      <c r="B1" s="30" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C1" s="30" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="30" t="inlineStr">
+        <is>
+          <t>Doanh thu kế hoạch</t>
+        </is>
+      </c>
+      <c r="B2" s="31" t="n">
+        <v>9323</v>
+      </c>
+      <c r="C2" s="31" t="n">
+        <v>13227</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="30" t="inlineStr">
+        <is>
+          <t>Doanh thu thuần về bán hàng và cung cấp dịch vụ</t>
+        </is>
+      </c>
+      <c r="B3" s="31" t="n">
+        <v>11217.42651465</v>
+      </c>
+      <c r="C3" s="31" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
-        <is>
-          <t>1. Khả năng sinh lời</t>
-        </is>
-      </c>
+      <c r="A4" s="30" t="inlineStr">
+        <is>
+          <t>%thực hiện</t>
+        </is>
+      </c>
+      <c r="B4" s="38">
+        <f>B3/B2</f>
+        <v/>
+      </c>
+      <c r="C4" s="38" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
-        <is>
-          <t>ROE (LNST CĐ Cty mẹ / VCSH bình quân)</t>
-        </is>
-      </c>
-      <c r="B5" s="12" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C5" s="13">
-        <f>IFERROR(C$47/((C$32+B$32)/2),"n/a")</f>
-        <v/>
-      </c>
-      <c r="D5" s="13">
-        <f>IFERROR(D$47/((D$32+C$32)/2),"n/a")</f>
-        <v/>
-      </c>
-      <c r="E5" s="13">
-        <f>IFERROR(E$47/((E$32+D$32)/2),"n/a")</f>
-        <v/>
-      </c>
-      <c r="F5" s="13">
-        <f>IFERROR(F$47/((F$32+E$32)/2),"n/a")</f>
-        <v/>
-      </c>
-      <c r="G5" s="13">
-        <f>IFERROR(G$47/((G$32+F$32)/2),"n/a")</f>
-        <v/>
-      </c>
-      <c r="H5" s="13">
-        <f>IFERROR(H$47/((H$32+G$32)/2),"n/a")</f>
-        <v/>
-      </c>
-      <c r="I5" s="13">
-        <f>IFERROR(I$47/((I$32+H$32)/2),"n/a")</f>
-        <v/>
+      <c r="A5" s="30" t="inlineStr">
+        <is>
+          <t>Lợi nhuận trước thuế kế hoạch</t>
+        </is>
+      </c>
+      <c r="B5" s="31" t="n">
+        <v>5765</v>
+      </c>
+      <c r="C5" s="31" t="n">
+        <v>7535</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
-        <is>
-          <t>ROA (LNST / Tổng tài sản bình quân)</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C6" s="13">
-        <f>IFERROR(C$46/((C$33+B$33)/2),"n/a")</f>
-        <v/>
-      </c>
-      <c r="D6" s="13">
-        <f>IFERROR(D$46/((D$33+C$33)/2),"n/a")</f>
-        <v/>
-      </c>
-      <c r="E6" s="13">
-        <f>IFERROR(E$46/((E$33+D$33)/2),"n/a")</f>
-        <v/>
-      </c>
-      <c r="F6" s="13">
-        <f>IFERROR(F$46/((F$33+E$33)/2),"n/a")</f>
-        <v/>
-      </c>
-      <c r="G6" s="13">
-        <f>IFERROR(G$46/((G$33+F$33)/2),"n/a")</f>
-        <v/>
-      </c>
-      <c r="H6" s="13">
-        <f>IFERROR(H$46/((H$33+G$33)/2),"n/a")</f>
-        <v/>
-      </c>
-      <c r="I6" s="13">
-        <f>IFERROR(I$46/((I$33+H$33)/2),"n/a")</f>
-        <v/>
-      </c>
+      <c r="A6" s="30" t="inlineStr">
+        <is>
+          <t>Lợi nhuận trước thuế thu nhập doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="B6" s="31" t="n">
+        <v>7109</v>
+      </c>
+      <c r="C6" s="31" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>Tăng trưởng LN Cổ đông Cty mẹ</t>
-        </is>
-      </c>
-      <c r="B7" s="12" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C7" s="13">
-        <f>IFERROR((C$47-B$47)/ABS(B$47),"n/a")</f>
-        <v/>
-      </c>
-      <c r="D7" s="13">
-        <f>IFERROR((D$47-C$47)/ABS(C$47),"n/a")</f>
-        <v/>
-      </c>
-      <c r="E7" s="13">
-        <f>IFERROR((E$47-D$47)/ABS(D$47),"n/a")</f>
-        <v/>
-      </c>
-      <c r="F7" s="13">
-        <f>IFERROR((F$47-E$47)/ABS(E$47),"n/a")</f>
-        <v/>
-      </c>
-      <c r="G7" s="13">
-        <f>IFERROR((G$47-F$47)/ABS(F$47),"n/a")</f>
-        <v/>
-      </c>
-      <c r="H7" s="13">
-        <f>IFERROR((H$47-G$47)/ABS(G$47),"n/a")</f>
-        <v/>
-      </c>
-      <c r="I7" s="13">
-        <f>IFERROR((I$47-H$47)/ABS(H$47),"n/a")</f>
-        <v/>
-      </c>
+      <c r="A7" s="30" t="inlineStr">
+        <is>
+          <t>%thực hiện</t>
+        </is>
+      </c>
+      <c r="B7" s="38">
+        <f>B6/B5</f>
+        <v/>
+      </c>
+      <c r="C7" s="38" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="inlineStr">
-        <is>
-          <t>Tăng trưởng Doanh thu thuần</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C8" s="13">
-        <f>IFERROR((C$39-B$39)/ABS(B$39),"n/a")</f>
-        <v/>
-      </c>
-      <c r="D8" s="13">
-        <f>IFERROR((D$39-C$39)/ABS(C$39),"n/a")</f>
-        <v/>
-      </c>
-      <c r="E8" s="13">
-        <f>IFERROR((E$39-D$39)/ABS(D$39),"n/a")</f>
-        <v/>
-      </c>
-      <c r="F8" s="13">
-        <f>IFERROR((F$39-E$39)/ABS(E$39),"n/a")</f>
-        <v/>
-      </c>
-      <c r="G8" s="13">
-        <f>IFERROR((G$39-F$39)/ABS(F$39),"n/a")</f>
-        <v/>
-      </c>
-      <c r="H8" s="13">
-        <f>IFERROR((H$39-G$39)/ABS(G$39),"n/a")</f>
-        <v/>
-      </c>
-      <c r="I8" s="13">
-        <f>IFERROR((I$39-H$39)/ABS(H$39),"n/a")</f>
-        <v/>
-      </c>
+      <c r="A8" s="39" t="n"/>
+      <c r="B8" s="39" t="n"/>
+      <c r="C8" s="39" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>2. Biên lợi nhuận</t>
-        </is>
-      </c>
+      <c r="A9" s="30" t="inlineStr">
+        <is>
+          <t>Trung vị %thực hiện DT</t>
+        </is>
+      </c>
+      <c r="B9" s="38">
+        <f>MEDIAN(B4:C4)</f>
+        <v/>
+      </c>
+      <c r="C9" s="39" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
-        <is>
-          <t>Biên lợi nhuận gộp</t>
-        </is>
-      </c>
-      <c r="B10" s="13">
-        <f>IFERROR(B$41/B$39,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C10" s="13">
-        <f>IFERROR(C$41/C$39,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D10" s="13">
-        <f>IFERROR(D$41/D$39,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E10" s="13">
-        <f>IFERROR(E$41/E$39,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F10" s="13">
-        <f>IFERROR(F$41/F$39,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G10" s="13">
-        <f>IFERROR(G$41/G$39,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H10" s="13">
-        <f>IFERROR(H$41/H$39,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I10" s="13">
-        <f>IFERROR(I$41/I$39,"n/a")</f>
-        <v/>
-      </c>
+      <c r="A10" s="30" t="inlineStr">
+        <is>
+          <t>Trung vị %thực hiện LNST</t>
+        </is>
+      </c>
+      <c r="B10" s="38">
+        <f>MEDIAN(B7:C7)</f>
+        <v/>
+      </c>
+      <c r="C10" s="39" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>Biên lợi nhuận ròng</t>
-        </is>
-      </c>
-      <c r="B11" s="13">
-        <f>IFERROR(B$46/B$39,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C11" s="13">
-        <f>IFERROR(C$46/C$39,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D11" s="13">
-        <f>IFERROR(D$46/D$39,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E11" s="13">
-        <f>IFERROR(E$46/E$39,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F11" s="13">
-        <f>IFERROR(F$46/F$39,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G11" s="13">
-        <f>IFERROR(G$46/G$39,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H11" s="13">
-        <f>IFERROR(H$46/H$39,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I11" s="13">
-        <f>IFERROR(I$46/I$39,"n/a")</f>
-        <v/>
-      </c>
+      <c r="A11" s="39" t="n"/>
+      <c r="B11" s="39" t="n"/>
+      <c r="C11" s="39" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr">
-        <is>
-          <t>3. Đòn bẩy tài chính</t>
-        </is>
-      </c>
+      <c r="A12" s="30" t="inlineStr">
+        <is>
+          <t>Tỷ lệ hoàn thành DT trên 95%</t>
+        </is>
+      </c>
+      <c r="B12" s="38">
+        <f>COUNTIF(B4:C4,"&gt;=95%")/COUNT(B4:C4)</f>
+        <v/>
+      </c>
+      <c r="C12" s="39" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>D/E (Nợ vay / Vốn chủ sở hữu)</t>
-        </is>
-      </c>
-      <c r="B13" s="14">
-        <f>IFERROR((B$37+B$38)/B$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C13" s="14">
-        <f>IFERROR((C$37+C$38)/C$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D13" s="14">
-        <f>IFERROR((D$37+D$38)/D$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E13" s="14">
-        <f>IFERROR((E$37+E$38)/E$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F13" s="14">
-        <f>IFERROR((F$37+F$38)/F$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G13" s="14">
-        <f>IFERROR((G$37+G$38)/G$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H13" s="14">
-        <f>IFERROR((H$37+H$38)/H$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I13" s="14">
-        <f>IFERROR((I$37+I$38)/I$32,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     - Nợ vay dài hạn/Vốn chủ sở hữu</t>
-        </is>
-      </c>
-      <c r="B14" s="14">
-        <f>IFERROR(B$38/B$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C14" s="14">
-        <f>IFERROR(C$38/C$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D14" s="14">
-        <f>IFERROR(D$38/D$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E14" s="14">
-        <f>IFERROR(E$38/E$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F14" s="14">
-        <f>IFERROR(F$38/F$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G14" s="14">
-        <f>IFERROR(G$38/G$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H14" s="14">
-        <f>IFERROR(H$38/H$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I14" s="14">
-        <f>IFERROR(I$38/I$32,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     - Nợ vay ngắn hạn/Vốn chủ sở hữu</t>
-        </is>
-      </c>
-      <c r="B15" s="14">
-        <f>IFERROR(B$37/B$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C15" s="14">
-        <f>IFERROR(C$37/C$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D15" s="14">
-        <f>IFERROR(D$37/D$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E15" s="14">
-        <f>IFERROR(E$37/E$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F15" s="14">
-        <f>IFERROR(F$37/F$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G15" s="14">
-        <f>IFERROR(G$37/G$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H15" s="14">
-        <f>IFERROR(H$37/H$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I15" s="14">
-        <f>IFERROR(I$37/I$32,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="11" t="inlineStr">
-        <is>
-          <t>Nợ phải trả/Vốn chủ sở hữu</t>
-        </is>
-      </c>
-      <c r="B16" s="14">
-        <f>IFERROR(B$34/B$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C16" s="14">
-        <f>IFERROR(C$34/C$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D16" s="14">
-        <f>IFERROR(D$34/D$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E16" s="14">
-        <f>IFERROR(E$34/E$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F16" s="14">
-        <f>IFERROR(F$34/F$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G16" s="14">
-        <f>IFERROR(G$34/G$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H16" s="14">
-        <f>IFERROR(H$34/H$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I16" s="14">
-        <f>IFERROR(I$34/I$32,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     - Nợ dài hạn/Vốn chủ sở hữu</t>
-        </is>
-      </c>
-      <c r="B17" s="14">
-        <f>IFERROR(B$36/B$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C17" s="14">
-        <f>IFERROR(C$36/C$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D17" s="14">
-        <f>IFERROR(D$36/D$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E17" s="14">
-        <f>IFERROR(E$36/E$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F17" s="14">
-        <f>IFERROR(F$36/F$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G17" s="14">
-        <f>IFERROR(G$36/G$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H17" s="14">
-        <f>IFERROR(H$36/H$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I17" s="14">
-        <f>IFERROR(I$36/I$32,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     - Nợ ngắn hạn/Vốn chủ sở hữu</t>
-        </is>
-      </c>
-      <c r="B18" s="14">
-        <f>IFERROR(B$35/B$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C18" s="14">
-        <f>IFERROR(C$35/C$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D18" s="14">
-        <f>IFERROR(D$35/D$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E18" s="14">
-        <f>IFERROR(E$35/E$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F18" s="14">
-        <f>IFERROR(F$35/F$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G18" s="14">
-        <f>IFERROR(G$35/G$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H18" s="14">
-        <f>IFERROR(H$35/H$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I18" s="14">
-        <f>IFERROR(I$35/I$32,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>4. Chi phí &amp; khả năng trả lãi</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="11" t="inlineStr">
-        <is>
-          <t>Chi phí bán hàng, quản lý/LN gộp</t>
-        </is>
-      </c>
-      <c r="B20" s="13">
-        <f>IFERROR((ABS(B$42)+ABS(B$43))/B$41,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C20" s="13">
-        <f>IFERROR((ABS(C$42)+ABS(C$43))/C$41,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D20" s="13">
-        <f>IFERROR((ABS(D$42)+ABS(D$43))/D$41,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E20" s="13">
-        <f>IFERROR((ABS(E$42)+ABS(E$43))/E$41,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F20" s="13">
-        <f>IFERROR((ABS(F$42)+ABS(F$43))/F$41,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G20" s="13">
-        <f>IFERROR((ABS(G$42)+ABS(G$43))/G$41,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H20" s="13">
-        <f>IFERROR((ABS(H$42)+ABS(H$43))/H$41,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I20" s="13">
-        <f>IFERROR((ABS(I$42)+ABS(I$43))/I$41,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="11" t="inlineStr">
-        <is>
-          <t>Chi phí lãi vay/LN từ hoạt động kinh doanh</t>
-        </is>
-      </c>
-      <c r="B21" s="13">
-        <f>IFERROR(ABS(B$45)/B$44,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C21" s="13">
-        <f>IFERROR(ABS(C$45)/C$44,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D21" s="13">
-        <f>IFERROR(ABS(D$45)/D$44,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E21" s="13">
-        <f>IFERROR(ABS(E$45)/E$44,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F21" s="13">
-        <f>IFERROR(ABS(F$45)/F$44,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G21" s="13">
-        <f>IFERROR(ABS(G$45)/G$44,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H21" s="13">
-        <f>IFERROR(ABS(H$45)/H$44,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I21" s="13">
-        <f>IFERROR(ABS(I$45)/I$44,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t>5. Chu kỳ hoạt động vốn lưu động</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="11" t="inlineStr">
-        <is>
-          <t>Số ngày phải trả (DPO)</t>
-        </is>
-      </c>
-      <c r="B23" s="12" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C23" s="15">
-        <f>IFERROR(((C$49+B$49)/2)/ABS(C$40)*365,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D23" s="15">
-        <f>IFERROR(((D$49+C$49)/2)/ABS(D$40)*365,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E23" s="15">
-        <f>IFERROR(((E$49+D$49)/2)/ABS(E$40)*365,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F23" s="15">
-        <f>IFERROR(((F$49+E$49)/2)/ABS(F$40)*365,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G23" s="15">
-        <f>IFERROR(((G$49+F$49)/2)/ABS(G$40)*365,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H23" s="15">
-        <f>IFERROR(((H$49+G$49)/2)/ABS(H$40)*365,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I23" s="15">
-        <f>IFERROR(((I$49+H$49)/2)/ABS(I$40)*365,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="11" t="inlineStr">
-        <is>
-          <t>Số ngày phải thu (DSO)</t>
-        </is>
-      </c>
-      <c r="B24" s="12" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C24" s="15">
-        <f>IFERROR(((C$48+B$48)/2)/C$39*365,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D24" s="15">
-        <f>IFERROR(((D$48+C$48)/2)/D$39*365,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E24" s="15">
-        <f>IFERROR(((E$48+D$48)/2)/E$39*365,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F24" s="15">
-        <f>IFERROR(((F$48+E$48)/2)/F$39*365,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G24" s="15">
-        <f>IFERROR(((G$48+F$48)/2)/G$39*365,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H24" s="15">
-        <f>IFERROR(((H$48+G$48)/2)/H$39*365,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I24" s="15">
-        <f>IFERROR(((I$48+H$48)/2)/I$39*365,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="11" t="inlineStr">
-        <is>
-          <t>Số ngày tồn kho (DIO)</t>
-        </is>
-      </c>
-      <c r="B25" s="12" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C25" s="15">
-        <f>IFERROR(((C$50+B$50)/2)/ABS(C$40)*365,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D25" s="15">
-        <f>IFERROR(((D$50+C$50)/2)/ABS(D$40)*365,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E25" s="15">
-        <f>IFERROR(((E$50+D$50)/2)/ABS(E$40)*365,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F25" s="15">
-        <f>IFERROR(((F$50+E$50)/2)/ABS(F$40)*365,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G25" s="15">
-        <f>IFERROR(((G$50+F$50)/2)/ABS(G$40)*365,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H25" s="15">
-        <f>IFERROR(((H$50+G$50)/2)/ABS(H$40)*365,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I25" s="15">
-        <f>IFERROR(((I$50+H$50)/2)/ABS(I$40)*365,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="10" t="inlineStr">
-        <is>
-          <t>6. Cơ cấu tài sản</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="11" t="inlineStr">
-        <is>
-          <t>Tiền và tương đương tiền/Tài sản</t>
-        </is>
-      </c>
-      <c r="B27" s="13">
-        <f>IFERROR(B$51/B$33,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C27" s="13">
-        <f>IFERROR(C$51/C$33,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D27" s="13">
-        <f>IFERROR(D$51/D$33,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E27" s="13">
-        <f>IFERROR(E$51/E$33,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F27" s="13">
-        <f>IFERROR(F$51/F$33,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G27" s="13">
-        <f>IFERROR(G$51/G$33,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H27" s="13">
-        <f>IFERROR(H$51/H$33,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I27" s="13">
-        <f>IFERROR(I$51/I$33,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="11" t="inlineStr">
-        <is>
-          <t>Hàng tồn kho/Tài sản</t>
-        </is>
-      </c>
-      <c r="B28" s="13">
-        <f>IFERROR(B$50/B$33,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C28" s="13">
-        <f>IFERROR(C$50/C$33,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D28" s="13">
-        <f>IFERROR(D$50/D$33,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E28" s="13">
-        <f>IFERROR(E$50/E$33,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F28" s="13">
-        <f>IFERROR(F$50/F$33,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G28" s="13">
-        <f>IFERROR(G$50/G$33,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H28" s="13">
-        <f>IFERROR(H$50/H$33,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I28" s="13">
-        <f>IFERROR(I$50/I$33,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>II. DỮ LIỆU TRÍCH XUẤT (tự động dò theo tên khoản mục)</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="n"/>
-      <c r="C30" s="7" t="n"/>
-      <c r="D30" s="7" t="n"/>
-      <c r="E30" s="7" t="n"/>
-      <c r="F30" s="7" t="n"/>
-      <c r="G30" s="7" t="n"/>
-      <c r="H30" s="7" t="n"/>
-      <c r="I30" s="7" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="8" t="inlineStr">
-        <is>
-          <t>Khoản mục</t>
-        </is>
-      </c>
-      <c r="B31" s="9">
-        <f>'balance_sheet'!B1</f>
-        <v/>
-      </c>
-      <c r="C31" s="9">
-        <f>'balance_sheet'!C1</f>
-        <v/>
-      </c>
-      <c r="D31" s="9">
-        <f>'balance_sheet'!D1</f>
-        <v/>
-      </c>
-      <c r="E31" s="9">
-        <f>'balance_sheet'!E1</f>
-        <v/>
-      </c>
-      <c r="F31" s="9">
-        <f>'balance_sheet'!F1</f>
-        <v/>
-      </c>
-      <c r="G31" s="9">
-        <f>'balance_sheet'!G1</f>
-        <v/>
-      </c>
-      <c r="H31" s="9">
-        <f>'balance_sheet'!H1</f>
-        <v/>
-      </c>
-      <c r="I31" s="9">
-        <f>'balance_sheet'!I1</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>Vốn chủ sở hữu</t>
-        </is>
-      </c>
-      <c r="B32" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C32" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D32" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E32" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F32" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G32" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H32" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I32" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>TỔNG CỘNG TÀI SẢN</t>
-        </is>
-      </c>
-      <c r="B33" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C33" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D33" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E33" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F33" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G33" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H33" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I33" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>NỢ PHẢI TRẢ</t>
-        </is>
-      </c>
-      <c r="B34" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C34" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D34" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E34" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F34" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G34" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H34" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I34" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>Nợ phải trả ngắn hạn</t>
-        </is>
-      </c>
-      <c r="B35" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả ngắn hạn",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C35" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả ngắn hạn",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D35" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả ngắn hạn",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E35" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả ngắn hạn",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F35" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả ngắn hạn",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G35" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả ngắn hạn",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H35" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả ngắn hạn",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I35" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả ngắn hạn",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>Nợ phải trả dài hạn</t>
-        </is>
-      </c>
-      <c r="B36" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả dài hạn",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C36" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả dài hạn",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D36" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả dài hạn",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E36" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả dài hạn",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F36" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả dài hạn",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G36" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả dài hạn",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H36" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả dài hạn",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I36" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả dài hạn",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>Vay ngắn hạn</t>
-        </is>
-      </c>
-      <c r="B37" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C37" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D37" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E37" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F37" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G37" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H37" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I37" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>Vay dài hạn</t>
-        </is>
-      </c>
-      <c r="B38" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C38" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D38" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E38" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F38" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G38" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H38" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I38" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>Doanh thu thuần về hoạt động kinh doanh</t>
-        </is>
-      </c>
-      <c r="B39" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần về hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C39" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần về hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D39" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần về hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E39" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần về hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F39" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần về hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G39" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần về hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H39" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần về hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I39" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần về hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>CHI PHÍ HOẠT ĐỘNG</t>
-        </is>
-      </c>
-      <c r="B40" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C40" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D40" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E40" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F40" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G40" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H40" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I40" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>LỢI NHUẬN GỘP</t>
-        </is>
-      </c>
-      <c r="B41" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN GỘP",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C41" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN GỘP",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D41" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN GỘP",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E41" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN GỘP",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F41" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN GỘP",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G41" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN GỘP",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H41" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN GỘP",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I41" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN GỘP",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>CHI PHÍ BÁN HÀNG</t>
-        </is>
-      </c>
-      <c r="B42" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ BÁN HÀNG",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C42" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ BÁN HÀNG",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D42" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ BÁN HÀNG",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E42" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ BÁN HÀNG",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F42" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ BÁN HÀNG",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G42" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ BÁN HÀNG",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H42" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ BÁN HÀNG",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I42" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ BÁN HÀNG",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>CHI PHÍ QUẢN LÝ CÔNG TY CHỨNG KHOÁN</t>
-        </is>
-      </c>
-      <c r="B43" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ QUẢN LÝ CÔNG TY CHỨNG KHOÁN",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C43" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ QUẢN LÝ CÔNG TY CHỨNG KHOÁN",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D43" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ QUẢN LÝ CÔNG TY CHỨNG KHOÁN",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E43" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ QUẢN LÝ CÔNG TY CHỨNG KHOÁN",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F43" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ QUẢN LÝ CÔNG TY CHỨNG KHOÁN",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G43" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ QUẢN LÝ CÔNG TY CHỨNG KHOÁN",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H43" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ QUẢN LÝ CÔNG TY CHỨNG KHOÁN",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I43" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ QUẢN LÝ CÔNG TY CHỨNG KHOÁN",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>KẾT QUẢ HOẠT ĐỘNG</t>
-        </is>
-      </c>
-      <c r="B44" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("KẾT QUẢ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C44" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("KẾT QUẢ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D44" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("KẾT QUẢ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E44" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("KẾT QUẢ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F44" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("KẾT QUẢ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G44" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("KẾT QUẢ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H44" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("KẾT QUẢ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I44" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("KẾT QUẢ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>Chi phí lãi vay</t>
-        </is>
-      </c>
-      <c r="B45" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C45" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D45" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E45" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F45" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G45" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H45" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I45" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>LỢI NHUẬN KẾ TOÁN SAU THUẾ</t>
-        </is>
-      </c>
-      <c r="B46" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN KẾ TOÁN SAU THUẾ",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C46" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN KẾ TOÁN SAU THUẾ",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D46" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN KẾ TOÁN SAU THUẾ",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E46" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN KẾ TOÁN SAU THUẾ",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F46" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN KẾ TOÁN SAU THUẾ",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G46" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN KẾ TOÁN SAU THUẾ",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H46" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN KẾ TOÁN SAU THUẾ",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I46" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN KẾ TOÁN SAU THUẾ",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>Lợi nhuận sau thuế phân bổ cho chủ sở hữu</t>
-        </is>
-      </c>
-      <c r="B47" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận sau thuế phân bổ cho chủ sở hữu",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C47" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận sau thuế phân bổ cho chủ sở hữu",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D47" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận sau thuế phân bổ cho chủ sở hữu",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E47" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận sau thuế phân bổ cho chủ sở hữu",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F47" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận sau thuế phân bổ cho chủ sở hữu",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G47" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận sau thuế phân bổ cho chủ sở hữu",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H47" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận sau thuế phân bổ cho chủ sở hữu",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I47" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận sau thuế phân bổ cho chủ sở hữu",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>Phải thu khách hàng</t>
-        </is>
-      </c>
-      <c r="B48" s="12" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C48" s="12" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="D48" s="12" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="E48" s="12" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="F48" s="12" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="G48" s="12" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="H48" s="12" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="I48" s="12" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>Phải trả người bán ngắn hạn</t>
-        </is>
-      </c>
-      <c r="B49" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán ngắn hạn",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C49" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán ngắn hạn",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D49" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán ngắn hạn",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E49" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán ngắn hạn",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F49" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán ngắn hạn",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G49" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán ngắn hạn",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H49" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán ngắn hạn",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I49" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán ngắn hạn",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t>Hàng tồn kho, ròng</t>
-        </is>
-      </c>
-      <c r="B50" s="12" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C50" s="12" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="D50" s="12" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="E50" s="12" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="F50" s="12" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="G50" s="12" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="H50" s="12" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="I50" s="12" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>Tiền và tương đương tiền</t>
-        </is>
-      </c>
-      <c r="B51" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C51" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D51" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E51" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F51" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G51" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H51" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I51" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
+      <c r="A13" s="30" t="inlineStr">
+        <is>
+          <t>Tỷ lệ hoàn thành LNST trên 95%</t>
+        </is>
+      </c>
+      <c r="B13" s="38">
+        <f>COUNTIF(B7:C7,"&gt;=95%")/COUNT(B7:C7)</f>
+        <v/>
+      </c>
+      <c r="C13" s="39" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:I1"/>
-  </mergeCells>
+  <conditionalFormatting sqref="B9:B10">
+    <cfRule type="cellIs" priority="4" operator="lessThanOrEqual" dxfId="0" stopIfTrue="1">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="5" operator="greaterThanOrEqual" dxfId="1" stopIfTrue="1">
+      <formula>0.95</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="6" operator="between" dxfId="2">
+      <formula>0.9</formula>
+      <formula>0.95</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B12:B13">
+    <cfRule type="cellIs" priority="2" operator="lessThan" dxfId="0">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="greaterThanOrEqual" dxfId="1">
+      <formula>0.8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B4:C4 B7:C7">
+    <cfRule type="cellIs" priority="7" operator="greaterThanOrEqual" dxfId="3">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/financials/TCX/TCX.xlsx
+++ b/financials/TCX/TCX.xlsx
@@ -11,6 +11,8 @@
     <sheet name="income_statement" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="cash_flow" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="chi_so_tai_chinh" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Dự báo tăng trưởng" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Hiệu quả thực hiện kế hoạch" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,22 +21,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
-    <numFmt numFmtId="166" formatCode="0.00&quot;x&quot;"/>
-    <numFmt numFmtId="167" formatCode="#,##0 &quot;ngày&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0;\(#,##0\);&quot;-&quot;"/>
+    <numFmt numFmtId="167" formatCode="#,##0;\(#,##0\);\-"/>
+    <numFmt numFmtId="168" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <name val="Tahoma"/>
@@ -47,48 +47,83 @@
     </font>
     <font>
       <name val="Tahoma"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <name val="Tahoma"/>
+      <family val="2"/>
       <b val="1"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Tahoma"/>
+      <family val="2"/>
       <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <name val="Tahoma"/>
-      <b val="1"/>
-      <i val="1"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Tahoma"/>
-      <b val="1"/>
+      <family val="2"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Tahoma"/>
+      <family val="2"/>
       <i val="1"/>
-      <color rgb="00808080"/>
+      <color rgb="FF808080"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Tahoma"/>
-      <color rgb="00000000"/>
+      <family val="2"/>
+      <color rgb="FF008000"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Tahoma"/>
-      <color rgb="00008000"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF008000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF7030A0"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <color rgb="FF7030A0"/>
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -102,7 +137,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
+        <fgColor theme="5" tint="0.7999816888943144"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.7999816888943144"/>
+        <bgColor theme="7" tint="0.5999938962981048"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.7999816888943144"/>
+        <bgColor theme="7" tint="0.7999816888943144"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.5999938962981048"/>
+        <bgColor theme="7" tint="0.5999938962981048"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9E1F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -113,12 +172,6 @@
       <top/>
       <bottom/>
       <diagonal/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
     </border>
     <border>
       <left style="thin">
@@ -134,38 +187,109 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="3" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="5" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="6" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="5" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="5" fillId="6" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="6" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="10" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="43" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="13" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="14" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="14" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="4">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="9"/>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -14076,1727 +14200,3227 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:J46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="56" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
-    <col width="3" customWidth="1" min="10" max="10"/>
+    <col width="13.125" customWidth="1" min="2" max="2"/>
+    <col width="20.5" customWidth="1" min="9" max="9"/>
+    <col width="19.375" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
+    <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>CHỈ SỐ TÀI CHÍNH — TCX</t>
-        </is>
+          <t>Chỉ tiêu</t>
+        </is>
+      </c>
+      <c r="B1" s="6">
+        <f>balance_sheet!B1</f>
+        <v/>
+      </c>
+      <c r="C1" s="6">
+        <f>balance_sheet!C1</f>
+        <v/>
+      </c>
+      <c r="D1" s="6">
+        <f>balance_sheet!D1</f>
+        <v/>
+      </c>
+      <c r="E1" s="6">
+        <f>balance_sheet!E1</f>
+        <v/>
+      </c>
+      <c r="F1" s="6">
+        <f>balance_sheet!F1</f>
+        <v/>
+      </c>
+      <c r="G1" s="6">
+        <f>balance_sheet!G1</f>
+        <v/>
+      </c>
+      <c r="H1" s="6">
+        <f>balance_sheet!H1</f>
+        <v/>
+      </c>
+      <c r="I1" s="6">
+        <f>balance_sheet!I1</f>
+        <v/>
+      </c>
+      <c r="J1" s="6" t="n">
+        <v>2026</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>I. CHỈ SỐ TÀI CHÍNH</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="n"/>
-      <c r="C2" s="7" t="n"/>
-      <c r="D2" s="7" t="n"/>
-      <c r="E2" s="7" t="n"/>
-      <c r="F2" s="7" t="n"/>
-      <c r="G2" s="7" t="n"/>
-      <c r="H2" s="7" t="n"/>
-      <c r="I2" s="7" t="n"/>
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>ROE</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C2" s="8">
+        <f>IFERROR(C$46/((C$34+B$34)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="D2" s="8">
+        <f>IFERROR(D$46/((D$34+C$34)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="E2" s="8">
+        <f>IFERROR(E$46/((E$34+D$34)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="F2" s="8">
+        <f>IFERROR(F$46/((F$34+E$34)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="G2" s="8">
+        <f>IFERROR(G$46/((G$34+F$34)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="H2" s="8">
+        <f>IFERROR(H$46/((H$34+G$34)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="I2" s="8">
+        <f>IFERROR(I$46/((I$34+H$34)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="J2" s="9" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>ROA</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C3" s="10">
+        <f>IFERROR(C$45/((C$26+B$26)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="D3" s="10">
+        <f>IFERROR(D$45/((D$26+C$26)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="E3" s="10">
+        <f>IFERROR(E$45/((E$26+D$26)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="F3" s="10">
+        <f>IFERROR(F$45/((F$26+E$26)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="G3" s="10">
+        <f>IFERROR(G$45/((G$26+F$26)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="H3" s="10">
+        <f>IFERROR(H$45/((H$26+G$26)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="I3" s="10">
+        <f>IFERROR(I$45/((I$26+H$26)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="J3" s="9" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Tăng trưởng LN Cổ đông Cty mẹ</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C4" s="8">
+        <f>IFERROR((C$46-B$46)/ABS(B$46),"n/a")</f>
+        <v/>
+      </c>
+      <c r="D4" s="8">
+        <f>IFERROR((D$46-C$46)/ABS(C$46),"n/a")</f>
+        <v/>
+      </c>
+      <c r="E4" s="8">
+        <f>IFERROR((E$46-D$46)/ABS(D$46),"n/a")</f>
+        <v/>
+      </c>
+      <c r="F4" s="8">
+        <f>IFERROR((F$46-E$46)/ABS(E$46),"n/a")</f>
+        <v/>
+      </c>
+      <c r="G4" s="8">
+        <f>IFERROR((G$46-F$46)/ABS(F$46),"n/a")</f>
+        <v/>
+      </c>
+      <c r="H4" s="8">
+        <f>IFERROR((H$46-G$46)/ABS(G$46),"n/a")</f>
+        <v/>
+      </c>
+      <c r="I4" s="8">
+        <f>IFERROR((I$46-H$46)/ABS(H$46),"n/a")</f>
+        <v/>
+      </c>
+      <c r="J4" s="9" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Tăng trưởng Doanh thu thuần</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C5" s="8">
+        <f>IFERROR((C$38-B$38)/ABS(B$38),"n/a")</f>
+        <v/>
+      </c>
+      <c r="D5" s="8">
+        <f>IFERROR((D$38-C$38)/ABS(C$38),"n/a")</f>
+        <v/>
+      </c>
+      <c r="E5" s="8">
+        <f>IFERROR((E$38-D$38)/ABS(D$38),"n/a")</f>
+        <v/>
+      </c>
+      <c r="F5" s="8">
+        <f>IFERROR((F$38-E$38)/ABS(E$38),"n/a")</f>
+        <v/>
+      </c>
+      <c r="G5" s="8">
+        <f>IFERROR((G$38-F$38)/ABS(F$38),"n/a")</f>
+        <v/>
+      </c>
+      <c r="H5" s="8">
+        <f>IFERROR((H$38-G$38)/ABS(G$38),"n/a")</f>
+        <v/>
+      </c>
+      <c r="I5" s="8">
+        <f>IFERROR((I$38-H$38)/ABS(H$38),"n/a")</f>
+        <v/>
+      </c>
+      <c r="J5" s="9" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Biên lợi nhuận gộp</t>
+        </is>
+      </c>
+      <c r="B6" s="8">
+        <f>IFERROR(B$40/B$38,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C6" s="8">
+        <f>IFERROR(C$40/C$38,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D6" s="8">
+        <f>IFERROR(D$40/D$38,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E6" s="8">
+        <f>IFERROR(E$40/E$38,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F6" s="8">
+        <f>IFERROR(F$40/F$38,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G6" s="8">
+        <f>IFERROR(G$40/G$38,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H6" s="8">
+        <f>IFERROR(H$40/H$38,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I6" s="8">
+        <f>IFERROR(I$40/I$38,"n/a")</f>
+        <v/>
+      </c>
+      <c r="J6" s="9" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Biên lợi nhuận ròng</t>
+        </is>
+      </c>
+      <c r="B7" s="11">
+        <f>IFERROR(B$45/B$38,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C7" s="11">
+        <f>IFERROR(C$45/C$38,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D7" s="11">
+        <f>IFERROR(D$45/D$38,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E7" s="11">
+        <f>IFERROR(E$45/E$38,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F7" s="11">
+        <f>IFERROR(F$45/F$38,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G7" s="11">
+        <f>IFERROR(G$45/G$38,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H7" s="11">
+        <f>IFERROR(H$45/H$38,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I7" s="11">
+        <f>IFERROR(I$45/I$38,"n/a")</f>
+        <v/>
+      </c>
+      <c r="J7" s="9" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>D/E (Nợ vay / Vốn chủ sở hữu)</t>
+        </is>
+      </c>
+      <c r="B8" s="8">
+        <f>IFERROR((B$29+B$31)/B$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C8" s="8">
+        <f>IFERROR((C$29+C$31)/C$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D8" s="8">
+        <f>IFERROR((D$29+D$31)/D$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E8" s="8">
+        <f>IFERROR((E$29+E$31)/E$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F8" s="8">
+        <f>IFERROR((F$29+F$31)/F$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G8" s="8">
+        <f>IFERROR((G$29+G$31)/G$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H8" s="8">
+        <f>IFERROR((H$29+H$31)/H$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I8" s="8">
+        <f>IFERROR((I$29+I$31)/I$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="J8" s="9" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     - Nợ vay dài hạn/Vốn chủ sở hữu</t>
+        </is>
+      </c>
+      <c r="B9" s="10">
+        <f>IFERROR(B$31/B$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C9" s="10">
+        <f>IFERROR(C$31/C$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D9" s="10">
+        <f>IFERROR(D$31/D$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E9" s="10">
+        <f>IFERROR(E$31/E$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F9" s="10">
+        <f>IFERROR(F$31/F$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G9" s="10">
+        <f>IFERROR(G$31/G$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H9" s="10">
+        <f>IFERROR(H$31/H$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I9" s="10">
+        <f>IFERROR(I$31/I$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="J9" s="9" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     - Nợ vay ngắn hạn/Vốn chủ sở hữu</t>
+        </is>
+      </c>
+      <c r="B10" s="10">
+        <f>IFERROR(B$29/B$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C10" s="10">
+        <f>IFERROR(C$29/C$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D10" s="10">
+        <f>IFERROR(D$29/D$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E10" s="10">
+        <f>IFERROR(E$29/E$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F10" s="10">
+        <f>IFERROR(F$29/F$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G10" s="10">
+        <f>IFERROR(G$29/G$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H10" s="10">
+        <f>IFERROR(H$29/H$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I10" s="10">
+        <f>IFERROR(I$29/I$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="J10" s="9" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Nợ phải trả/Vốn chủ sở hữu</t>
+        </is>
+      </c>
+      <c r="B11" s="11">
+        <f>IFERROR(B$33/B$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C11" s="11">
+        <f>IFERROR(C$33/C$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D11" s="11">
+        <f>IFERROR(D$33/D$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E11" s="11">
+        <f>IFERROR(E$33/E$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F11" s="11">
+        <f>IFERROR(F$33/F$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G11" s="11">
+        <f>IFERROR(G$33/G$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H11" s="11">
+        <f>IFERROR(H$33/H$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I11" s="11">
+        <f>IFERROR(I$33/I$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="J11" s="9" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     - Nợ dài hạn/Vốn chủ sở hữu</t>
+        </is>
+      </c>
+      <c r="B12" s="10">
+        <f>IFERROR(B$32/B$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C12" s="10">
+        <f>IFERROR(C$32/C$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D12" s="10">
+        <f>IFERROR(D$32/D$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E12" s="10">
+        <f>IFERROR(E$32/E$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F12" s="10">
+        <f>IFERROR(F$32/F$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G12" s="10">
+        <f>IFERROR(G$32/G$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H12" s="10">
+        <f>IFERROR(H$32/H$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I12" s="10">
+        <f>IFERROR(I$32/I$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="J12" s="9" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     - Nợ ngắn hạn/Vốn chủ sở hữu</t>
+        </is>
+      </c>
+      <c r="B13" s="10">
+        <f>IFERROR(B$30/B$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C13" s="10">
+        <f>IFERROR(C$30/C$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D13" s="10">
+        <f>IFERROR(D$30/D$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E13" s="10">
+        <f>IFERROR(E$30/E$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F13" s="10">
+        <f>IFERROR(F$30/F$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G13" s="10">
+        <f>IFERROR(G$30/G$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H13" s="10">
+        <f>IFERROR(H$30/H$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I13" s="10">
+        <f>IFERROR(I$30/I$34,"n/a")</f>
+        <v/>
+      </c>
+      <c r="J13" s="9" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Chi phí bán hàng, quản lý/LN gộp</t>
+        </is>
+      </c>
+      <c r="B14" s="13">
+        <f>IFERROR((ABS(B$41)+ABS(B$42))/B$40,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C14" s="13">
+        <f>IFERROR((ABS(C$41)+ABS(C$42))/C$40,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D14" s="13">
+        <f>IFERROR((ABS(D$41)+ABS(D$42))/D$40,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E14" s="13">
+        <f>IFERROR((ABS(E$41)+ABS(E$42))/E$40,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F14" s="13">
+        <f>IFERROR((ABS(F$41)+ABS(F$42))/F$40,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G14" s="13">
+        <f>IFERROR((ABS(G$41)+ABS(G$42))/G$40,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H14" s="13">
+        <f>IFERROR((ABS(H$41)+ABS(H$42))/H$40,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I14" s="13">
+        <f>IFERROR((ABS(I$41)+ABS(I$42))/I$40,"n/a")</f>
+        <v/>
+      </c>
+      <c r="J14" s="9" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Chi phí lãi vay/LN từ hoạt động kinh doanh</t>
+        </is>
+      </c>
+      <c r="B15" s="14">
+        <f>IFERROR(ABS(B$44)/B$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C15" s="14">
+        <f>IFERROR(ABS(C$44)/C$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D15" s="14">
+        <f>IFERROR(ABS(D$44)/D$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E15" s="14">
+        <f>IFERROR(ABS(E$44)/E$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F15" s="14">
+        <f>IFERROR(ABS(F$44)/F$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G15" s="14">
+        <f>IFERROR(ABS(G$44)/G$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H15" s="14">
+        <f>IFERROR(ABS(H$44)/H$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I15" s="14">
+        <f>IFERROR(ABS(I$44)/I$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="J15" s="9" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Số ngày phải trả (DPO)</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C16" s="16">
+        <f>IFERROR(((C$28+B$28)/2)/ABS(C$39)*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D16" s="16">
+        <f>IFERROR(((D$28+C$28)/2)/ABS(D$39)*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E16" s="16">
+        <f>IFERROR(((E$28+D$28)/2)/ABS(E$39)*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F16" s="16">
+        <f>IFERROR(((F$28+E$28)/2)/ABS(F$39)*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G16" s="16">
+        <f>IFERROR(((G$28+F$28)/2)/ABS(G$39)*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H16" s="16">
+        <f>IFERROR(((H$28+G$28)/2)/ABS(H$39)*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I16" s="16">
+        <f>IFERROR(((I$28+H$28)/2)/ABS(I$39)*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="J16" s="9" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Tiền và tương đương tiền/Tài sản</t>
+        </is>
+      </c>
+      <c r="B17" s="8">
+        <f>IFERROR(B$23/B$26,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C17" s="8">
+        <f>IFERROR(C$23/C$26,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D17" s="8">
+        <f>IFERROR(D$23/D$26,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E17" s="8">
+        <f>IFERROR(E$23/E$26,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F17" s="8">
+        <f>IFERROR(F$23/F$26,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G17" s="8">
+        <f>IFERROR(G$23/G$26,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H17" s="8">
+        <f>IFERROR(H$23/H$26,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I17" s="8">
+        <f>IFERROR(I$23/I$26,"n/a")</f>
+        <v/>
+      </c>
+      <c r="J17" s="9" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="n"/>
+      <c r="B18" s="9" t="n"/>
+      <c r="C18" s="9" t="n"/>
+      <c r="D18" s="9" t="n"/>
+      <c r="E18" s="9" t="n"/>
+      <c r="F18" s="9" t="n"/>
+      <c r="G18" s="9" t="n"/>
+      <c r="H18" s="9" t="n"/>
+      <c r="I18" s="9" t="n"/>
+      <c r="J18" s="9" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t>II. DỮ LIỆU TRÍCH XUẤT (tự động dò theo tên khoản mục)</t>
+        </is>
+      </c>
+      <c r="B19" s="18" t="n"/>
+      <c r="C19" s="18" t="n"/>
+      <c r="D19" s="18" t="n"/>
+      <c r="E19" s="18" t="n"/>
+      <c r="F19" s="18" t="n"/>
+      <c r="G19" s="18" t="n"/>
+      <c r="H19" s="18" t="n"/>
+      <c r="I19" s="18" t="n"/>
+      <c r="J19" s="9" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>Khoản mục</t>
+        </is>
+      </c>
+      <c r="B20" s="20">
+        <f>balance_sheet!B1</f>
+        <v/>
+      </c>
+      <c r="C20" s="20">
+        <f>balance_sheet!C1</f>
+        <v/>
+      </c>
+      <c r="D20" s="20">
+        <f>balance_sheet!D1</f>
+        <v/>
+      </c>
+      <c r="E20" s="20">
+        <f>balance_sheet!E1</f>
+        <v/>
+      </c>
+      <c r="F20" s="20">
+        <f>balance_sheet!F1</f>
+        <v/>
+      </c>
+      <c r="G20" s="20">
+        <f>balance_sheet!G1</f>
+        <v/>
+      </c>
+      <c r="H20" s="20">
+        <f>balance_sheet!H1</f>
+        <v/>
+      </c>
+      <c r="I20" s="20">
+        <f>balance_sheet!I1</f>
+        <v/>
+      </c>
+      <c r="J20" s="9" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="21" t="inlineStr">
+        <is>
+          <t>CĐKT</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="n"/>
+      <c r="C21" s="20" t="n"/>
+      <c r="D21" s="20" t="n"/>
+      <c r="E21" s="20" t="n"/>
+      <c r="F21" s="20" t="n"/>
+      <c r="G21" s="20" t="n"/>
+      <c r="H21" s="20" t="n"/>
+      <c r="I21" s="20" t="n"/>
+      <c r="J21" s="9" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="21" t="inlineStr">
+        <is>
+          <t>Tài sản</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="n"/>
+      <c r="C22" s="20" t="n"/>
+      <c r="D22" s="20" t="n"/>
+      <c r="E22" s="20" t="n"/>
+      <c r="F22" s="20" t="n"/>
+      <c r="G22" s="20" t="n"/>
+      <c r="H22" s="20" t="n"/>
+      <c r="I22" s="20" t="n"/>
+      <c r="J22" s="9" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="22" t="inlineStr">
+        <is>
+          <t>Tiền và tương đương tiền</t>
+        </is>
+      </c>
+      <c r="B23" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(B$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C23" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(C$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D23" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(D$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E23" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(E$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F23" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(F$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G23" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(G$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H23" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(H$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I23" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(I$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J23" s="9" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="22" t="inlineStr">
+        <is>
+          <t>Phải thu khách hàng</t>
+        </is>
+      </c>
+      <c r="B24" s="24" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C24" s="24" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D24" s="24" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="E24" s="24" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F24" s="24" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G24" s="24" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H24" s="24" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I24" s="24" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J24" s="9" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="22" t="inlineStr">
+        <is>
+          <t>Hàng tồn kho, ròng</t>
+        </is>
+      </c>
+      <c r="B25" s="24" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C25" s="24" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D25" s="24" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="E25" s="24" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F25" s="24" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G25" s="24" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H25" s="24" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I25" s="24" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J25" s="9" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="22" t="inlineStr">
+        <is>
+          <t>TỔNG CỘNG TÀI SẢN</t>
+        </is>
+      </c>
+      <c r="B26" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(B$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C26" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(C$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D26" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(D$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E26" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(E$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F26" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(F$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G26" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(G$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H26" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(H$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I26" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(I$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J26" s="9" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="21" t="inlineStr">
+        <is>
+          <t>Nguồn vốn</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="n"/>
+      <c r="C27" s="20" t="n"/>
+      <c r="D27" s="20" t="n"/>
+      <c r="E27" s="20" t="n"/>
+      <c r="F27" s="20" t="n"/>
+      <c r="G27" s="20" t="n"/>
+      <c r="H27" s="20" t="n"/>
+      <c r="I27" s="20" t="n"/>
+      <c r="J27" s="9" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="22" t="inlineStr">
+        <is>
+          <t>Phải trả người bán ngắn hạn</t>
+        </is>
+      </c>
+      <c r="B28" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán ngắn hạn",balance_sheet!$A:$A,0),MATCH(B$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C28" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán ngắn hạn",balance_sheet!$A:$A,0),MATCH(C$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D28" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán ngắn hạn",balance_sheet!$A:$A,0),MATCH(D$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E28" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán ngắn hạn",balance_sheet!$A:$A,0),MATCH(E$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F28" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán ngắn hạn",balance_sheet!$A:$A,0),MATCH(F$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G28" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán ngắn hạn",balance_sheet!$A:$A,0),MATCH(G$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H28" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán ngắn hạn",balance_sheet!$A:$A,0),MATCH(H$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I28" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán ngắn hạn",balance_sheet!$A:$A,0),MATCH(I$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J28" s="9" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="22" t="inlineStr">
+        <is>
+          <t>Vay ngắn hạn</t>
+        </is>
+      </c>
+      <c r="B29" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(B$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C29" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(C$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D29" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(D$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E29" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(E$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F29" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(F$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G29" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(G$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H29" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(H$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I29" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(I$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J29" s="9" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="22" t="inlineStr">
+        <is>
+          <t>Nợ phải trả ngắn hạn</t>
+        </is>
+      </c>
+      <c r="B30" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả ngắn hạn",balance_sheet!$A:$A,0),MATCH(B$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C30" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả ngắn hạn",balance_sheet!$A:$A,0),MATCH(C$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D30" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả ngắn hạn",balance_sheet!$A:$A,0),MATCH(D$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E30" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả ngắn hạn",balance_sheet!$A:$A,0),MATCH(E$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F30" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả ngắn hạn",balance_sheet!$A:$A,0),MATCH(F$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G30" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả ngắn hạn",balance_sheet!$A:$A,0),MATCH(G$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H30" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả ngắn hạn",balance_sheet!$A:$A,0),MATCH(H$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I30" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả ngắn hạn",balance_sheet!$A:$A,0),MATCH(I$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J30" s="9" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="22" t="inlineStr">
+        <is>
+          <t>Vay dài hạn</t>
+        </is>
+      </c>
+      <c r="B31" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(B$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C31" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(C$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D31" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(D$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E31" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(E$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F31" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(F$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G31" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(G$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H31" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(H$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I31" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(I$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J31" s="9" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="22" t="inlineStr">
+        <is>
+          <t>Nợ phải trả dài hạn</t>
+        </is>
+      </c>
+      <c r="B32" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả dài hạn",balance_sheet!$A:$A,0),MATCH(B$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C32" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả dài hạn",balance_sheet!$A:$A,0),MATCH(C$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D32" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả dài hạn",balance_sheet!$A:$A,0),MATCH(D$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E32" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả dài hạn",balance_sheet!$A:$A,0),MATCH(E$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F32" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả dài hạn",balance_sheet!$A:$A,0),MATCH(F$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G32" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả dài hạn",balance_sheet!$A:$A,0),MATCH(G$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H32" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả dài hạn",balance_sheet!$A:$A,0),MATCH(H$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I32" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả dài hạn",balance_sheet!$A:$A,0),MATCH(I$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J32" s="9" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="22" t="inlineStr">
+        <is>
+          <t>NỢ PHẢI TRẢ</t>
+        </is>
+      </c>
+      <c r="B33" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(B$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C33" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(C$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D33" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(D$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E33" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(E$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F33" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(F$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G33" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(G$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H33" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(H$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I33" s="23">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(I$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J33" s="9" t="n"/>
+    </row>
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" s="21" t="inlineStr">
+        <is>
+          <t>Vốn chủ sở hữu</t>
+        </is>
+      </c>
+      <c r="B34" s="25">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(B$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C34" s="25">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(C$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D34" s="25">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(D$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E34" s="25">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(E$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F34" s="25">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(F$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G34" s="25">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(G$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H34" s="25">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(H$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I34" s="25">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(I$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J34" s="25">
+        <f>I34+J46*0.7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" ht="15" customHeight="1">
+      <c r="A35" s="26" t="inlineStr">
+        <is>
+          <t>Tăng VCSH/LN cổ đông cty mẹ</t>
+        </is>
+      </c>
+      <c r="B35" s="27" t="n"/>
+      <c r="C35" s="28">
+        <f>(C34-B34)/C46</f>
+        <v/>
+      </c>
+      <c r="D35" s="28">
+        <f>(D34-C34)/D46</f>
+        <v/>
+      </c>
+      <c r="E35" s="28">
+        <f>(E34-D34)/E46</f>
+        <v/>
+      </c>
+      <c r="F35" s="28">
+        <f>(F34-E34)/F46</f>
+        <v/>
+      </c>
+      <c r="G35" s="28">
+        <f>(G34-F34)/G46</f>
+        <v/>
+      </c>
+      <c r="H35" s="28">
+        <f>(H34-G34)/H46</f>
+        <v/>
+      </c>
+      <c r="I35" s="28">
+        <f>(I34-H34)/I46</f>
+        <v/>
+      </c>
+      <c r="J35" s="29" t="n"/>
+    </row>
+    <row r="36" ht="15" customHeight="1">
+      <c r="A36" s="21" t="inlineStr">
+        <is>
+          <t>Lợi ích cổ đông không kiểm soát</t>
+        </is>
+      </c>
+      <c r="B36" s="25">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Lợi ích cổ đông không kiểm soát",balance_sheet!$A:$A,0),MATCH(B$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C36" s="25">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Lợi ích cổ đông không kiểm soát",balance_sheet!$A:$A,0),MATCH(C$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D36" s="25">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Lợi ích cổ đông không kiểm soát",balance_sheet!$A:$A,0),MATCH(D$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E36" s="25">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Lợi ích cổ đông không kiểm soát",balance_sheet!$A:$A,0),MATCH(E$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F36" s="25">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Lợi ích cổ đông không kiểm soát",balance_sheet!$A:$A,0),MATCH(F$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G36" s="25">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Lợi ích cổ đông không kiểm soát",balance_sheet!$A:$A,0),MATCH(G$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H36" s="25">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Lợi ích cổ đông không kiểm soát",balance_sheet!$A:$A,0),MATCH(H$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I36" s="25">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Lợi ích cổ đông không kiểm soát",balance_sheet!$A:$A,0),MATCH(I$20,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J36" s="29" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="21" t="inlineStr">
+        <is>
+          <t>Kết quả hoạt động kinh doanh</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="n"/>
+      <c r="C37" s="9" t="n"/>
+      <c r="D37" s="9" t="n"/>
+      <c r="E37" s="9" t="n"/>
+      <c r="F37" s="9" t="n"/>
+      <c r="G37" s="9" t="n"/>
+      <c r="H37" s="9" t="n"/>
+      <c r="I37" s="9" t="n"/>
+      <c r="J37" s="9" t="n"/>
+    </row>
+    <row r="38" ht="15" customHeight="1">
+      <c r="A38" s="21" t="inlineStr">
+        <is>
+          <t>Doanh thu thuần về hoạt động kinh doanh</t>
+        </is>
+      </c>
+      <c r="B38" s="25">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần về hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(B$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C38" s="25">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần về hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(C$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D38" s="25">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần về hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(D$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E38" s="25">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần về hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(E$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F38" s="25">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần về hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(F$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G38" s="25">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần về hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(G$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H38" s="25">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần về hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(H$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I38" s="25">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần về hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(I$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J38" s="25" t="n">
+        <v>13227000000000</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="22" t="inlineStr">
+        <is>
+          <t>CHI PHÍ HOẠT ĐỘNG</t>
+        </is>
+      </c>
+      <c r="B39" s="23">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(B$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C39" s="23">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(C$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D39" s="23">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(D$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E39" s="23">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(E$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F39" s="23">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(F$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G39" s="23">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(G$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H39" s="23">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(H$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I39" s="23">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(I$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J39" s="9" t="n"/>
+    </row>
+    <row r="40" ht="15" customHeight="1">
+      <c r="A40" s="21" t="inlineStr">
+        <is>
+          <t>LỢI NHUẬN GỘP</t>
+        </is>
+      </c>
+      <c r="B40" s="25">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN GỘP",income_statement!$A:$A,0),MATCH(B$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C40" s="25">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN GỘP",income_statement!$A:$A,0),MATCH(C$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D40" s="25">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN GỘP",income_statement!$A:$A,0),MATCH(D$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E40" s="25">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN GỘP",income_statement!$A:$A,0),MATCH(E$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F40" s="25">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN GỘP",income_statement!$A:$A,0),MATCH(F$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G40" s="25">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN GỘP",income_statement!$A:$A,0),MATCH(G$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H40" s="25">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN GỘP",income_statement!$A:$A,0),MATCH(H$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I40" s="25">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN GỘP",income_statement!$A:$A,0),MATCH(I$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J40" s="29" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="22" t="inlineStr">
+        <is>
+          <t>CHI PHÍ BÁN HÀNG</t>
+        </is>
+      </c>
+      <c r="B41" s="23">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ BÁN HÀNG",income_statement!$A:$A,0),MATCH(B$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C41" s="23">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ BÁN HÀNG",income_statement!$A:$A,0),MATCH(C$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D41" s="23">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ BÁN HÀNG",income_statement!$A:$A,0),MATCH(D$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E41" s="23">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ BÁN HÀNG",income_statement!$A:$A,0),MATCH(E$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F41" s="23">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ BÁN HÀNG",income_statement!$A:$A,0),MATCH(F$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G41" s="23">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ BÁN HÀNG",income_statement!$A:$A,0),MATCH(G$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H41" s="23">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ BÁN HÀNG",income_statement!$A:$A,0),MATCH(H$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I41" s="23">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ BÁN HÀNG",income_statement!$A:$A,0),MATCH(I$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J41" s="9" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="22" t="inlineStr">
+        <is>
+          <t>CHI PHÍ QUẢN LÝ CÔNG TY CHỨNG KHOÁN</t>
+        </is>
+      </c>
+      <c r="B42" s="23">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ QUẢN LÝ CÔNG TY CHỨNG KHOÁN",income_statement!$A:$A,0),MATCH(B$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C42" s="23">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ QUẢN LÝ CÔNG TY CHỨNG KHOÁN",income_statement!$A:$A,0),MATCH(C$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D42" s="23">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ QUẢN LÝ CÔNG TY CHỨNG KHOÁN",income_statement!$A:$A,0),MATCH(D$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E42" s="23">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ QUẢN LÝ CÔNG TY CHỨNG KHOÁN",income_statement!$A:$A,0),MATCH(E$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F42" s="23">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ QUẢN LÝ CÔNG TY CHỨNG KHOÁN",income_statement!$A:$A,0),MATCH(F$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G42" s="23">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ QUẢN LÝ CÔNG TY CHỨNG KHOÁN",income_statement!$A:$A,0),MATCH(G$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H42" s="23">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ QUẢN LÝ CÔNG TY CHỨNG KHOÁN",income_statement!$A:$A,0),MATCH(H$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I42" s="23">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ QUẢN LÝ CÔNG TY CHỨNG KHOÁN",income_statement!$A:$A,0),MATCH(I$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J42" s="9" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="22" t="inlineStr">
+        <is>
+          <t>KẾT QUẢ HOẠT ĐỘNG</t>
+        </is>
+      </c>
+      <c r="B43" s="23">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("KẾT QUẢ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(B$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C43" s="23">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("KẾT QUẢ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(C$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D43" s="23">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("KẾT QUẢ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(D$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E43" s="23">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("KẾT QUẢ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(E$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F43" s="23">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("KẾT QUẢ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(F$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G43" s="23">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("KẾT QUẢ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(G$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H43" s="23">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("KẾT QUẢ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(H$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I43" s="23">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("KẾT QUẢ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(I$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J43" s="9" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="22" t="inlineStr">
+        <is>
+          <t>Chi phí lãi vay</t>
+        </is>
+      </c>
+      <c r="B44" s="23">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(B$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C44" s="23">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(C$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D44" s="23">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(D$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E44" s="23">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(E$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F44" s="23">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(F$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G44" s="23">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(G$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H44" s="23">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(H$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I44" s="23">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(I$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J44" s="9" t="n"/>
+    </row>
+    <row r="45" ht="15" customHeight="1">
+      <c r="A45" s="21" t="inlineStr">
+        <is>
+          <t>LỢI NHUẬN KẾ TOÁN SAU THUẾ</t>
+        </is>
+      </c>
+      <c r="B45" s="25">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN KẾ TOÁN SAU THUẾ",income_statement!$A:$A,0),MATCH(B$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C45" s="25">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN KẾ TOÁN SAU THUẾ",income_statement!$A:$A,0),MATCH(C$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D45" s="25">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN KẾ TOÁN SAU THUẾ",income_statement!$A:$A,0),MATCH(D$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E45" s="25">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN KẾ TOÁN SAU THUẾ",income_statement!$A:$A,0),MATCH(E$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F45" s="25">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN KẾ TOÁN SAU THUẾ",income_statement!$A:$A,0),MATCH(F$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G45" s="25">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN KẾ TOÁN SAU THUẾ",income_statement!$A:$A,0),MATCH(G$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H45" s="25">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN KẾ TOÁN SAU THUẾ",income_statement!$A:$A,0),MATCH(H$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I45" s="25">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN KẾ TOÁN SAU THUẾ",income_statement!$A:$A,0),MATCH(I$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J45" s="25" t="n">
+        <v>7535000000000</v>
+      </c>
+    </row>
+    <row r="46" ht="15" customHeight="1">
+      <c r="A46" s="21" t="inlineStr">
+        <is>
+          <t>Lợi nhuận sau thuế phân bổ cho chủ sở hữu</t>
+        </is>
+      </c>
+      <c r="B46" s="25">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận sau thuế phân bổ cho chủ sở hữu",income_statement!$A:$A,0),MATCH(B$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C46" s="25">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận sau thuế phân bổ cho chủ sở hữu",income_statement!$A:$A,0),MATCH(C$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D46" s="25">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận sau thuế phân bổ cho chủ sở hữu",income_statement!$A:$A,0),MATCH(D$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E46" s="25">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận sau thuế phân bổ cho chủ sở hữu",income_statement!$A:$A,0),MATCH(E$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F46" s="25">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận sau thuế phân bổ cho chủ sở hữu",income_statement!$A:$A,0),MATCH(F$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G46" s="25">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận sau thuế phân bổ cho chủ sở hữu",income_statement!$A:$A,0),MATCH(G$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H46" s="25">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận sau thuế phân bổ cho chủ sở hữu",income_statement!$A:$A,0),MATCH(H$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I46" s="25">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận sau thuế phân bổ cho chủ sở hữu",income_statement!$A:$A,0),MATCH(I$20,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J46" s="25" t="n">
+        <v>7535000000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="B2:I2">
+    <cfRule type="cellIs" priority="13" operator="lessThan" dxfId="0">
+      <formula>0.15</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="14" operator="greaterThanOrEqual" dxfId="1">
+      <formula>0.15</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B4:I5">
+    <cfRule type="cellIs" priority="11" operator="lessThan" dxfId="0">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="12" operator="greaterThan" dxfId="1">
+      <formula>0.15</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B6:I6">
+    <cfRule type="cellIs" priority="6" operator="lessThanOrEqual" dxfId="0">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="7" operator="between" dxfId="2">
+      <formula>0.3</formula>
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="8" operator="greaterThanOrEqual" dxfId="1">
+      <formula>0.3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B7:I7">
+    <cfRule type="cellIs" priority="5" operator="greaterThanOrEqual" dxfId="1">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B8:I8">
+    <cfRule type="cellIs" priority="10" operator="lessThanOrEqual" dxfId="1">
+      <formula>0.5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B11:I11">
+    <cfRule type="cellIs" priority="9" operator="lessThanOrEqual" dxfId="1">
+      <formula>0.5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B14:I14">
+    <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
+      <formula>0.7</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="lessThanOrEqual" dxfId="1">
+      <formula>0.3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B17:I17">
+    <cfRule type="cellIs" priority="3" operator="notBetween" dxfId="0">
+      <formula>0.02</formula>
+      <formula>0.3</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="between" dxfId="1">
+      <formula>0.02</formula>
+      <formula>0.3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8.25" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="20.5" customWidth="1" min="7" max="7"/>
+    <col width="9.375" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="30" t="n"/>
+      <c r="B1" s="30" t="inlineStr">
+        <is>
+          <t>Q4/2025</t>
+        </is>
+      </c>
+      <c r="C1" s="30" t="inlineStr">
+        <is>
+          <t>Q1/2026</t>
+        </is>
+      </c>
+      <c r="D1" s="30" t="inlineStr">
+        <is>
+          <t>Q2/2026</t>
+        </is>
+      </c>
+      <c r="E1" s="30" t="inlineStr">
+        <is>
+          <t>Q3/2026</t>
+        </is>
+      </c>
+      <c r="F1" s="30" t="inlineStr">
+        <is>
+          <t>Q4/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="14.25" customHeight="1">
+      <c r="A2" s="30" t="inlineStr">
+        <is>
+          <t>Số CP</t>
+        </is>
+      </c>
+      <c r="B2" s="31" t="n">
+        <v>2774453325</v>
+      </c>
+      <c r="C2" s="31" t="n">
+        <v>2774453325</v>
+      </c>
+      <c r="D2" s="31" t="n">
+        <v>2774453325</v>
+      </c>
+      <c r="E2" s="31" t="n">
+        <v>2774453325</v>
+      </c>
+      <c r="F2" s="31" t="n">
+        <v>2774453325</v>
+      </c>
+    </row>
+    <row r="3" ht="14.25" customHeight="1">
+      <c r="A3" s="30" t="inlineStr">
+        <is>
+          <t>Thị giá</t>
+        </is>
+      </c>
+      <c r="B3" s="31" t="n">
+        <v>40800</v>
+      </c>
+      <c r="C3" s="31" t="n">
+        <v>40800</v>
+      </c>
+      <c r="D3" s="31" t="n">
+        <v>40800</v>
+      </c>
+      <c r="E3" s="31" t="n">
+        <v>40800</v>
+      </c>
+      <c r="F3" s="31" t="n">
+        <v>40800</v>
+      </c>
+    </row>
+    <row r="4" ht="14.25" customHeight="1">
+      <c r="A4" s="30" t="inlineStr">
+        <is>
+          <t>Vốn hoá</t>
+        </is>
+      </c>
+      <c r="B4" s="31">
+        <f>B2*B3</f>
+        <v/>
+      </c>
+      <c r="C4" s="31">
+        <f>C2*C3</f>
+        <v/>
+      </c>
+      <c r="D4" s="31">
+        <f>D2*D3</f>
+        <v/>
+      </c>
+      <c r="E4" s="31">
+        <f>E2*E3</f>
+        <v/>
+      </c>
+      <c r="F4" s="31">
+        <f>F2*F3</f>
+        <v/>
+      </c>
+      <c r="G4" s="32" t="n"/>
+    </row>
+    <row r="5" ht="14.25" customHeight="1"/>
+    <row r="6" ht="14.25" customHeight="1">
+      <c r="A6" s="30" t="inlineStr">
+        <is>
+          <t>VCSH</t>
+        </is>
+      </c>
+      <c r="B6" s="31">
+        <f>chi_so_tai_chinh!I34</f>
+        <v/>
+      </c>
+      <c r="C6" s="31" t="n">
+        <v>45782000000000</v>
+      </c>
+      <c r="D6" s="31">
+        <f>B$6*(($F$6/$B$6)^(2/4))</f>
+        <v/>
+      </c>
+      <c r="E6" s="31">
+        <f>B$6*(($F$6/$B$6)^(3/4))</f>
+        <v/>
+      </c>
+      <c r="F6" s="31">
+        <f>chi_so_tai_chinh!J34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="14.25" customHeight="1">
+      <c r="A7" s="30" t="inlineStr">
+        <is>
+          <t>LICĐKKS</t>
+        </is>
+      </c>
+      <c r="B7" s="31">
+        <f>chi_so_tai_chinh!I36</f>
+        <v/>
+      </c>
+      <c r="C7" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" ht="14.25" customHeight="1">
+      <c r="A8" s="30" t="inlineStr">
+        <is>
+          <t>BV</t>
+        </is>
+      </c>
+      <c r="B8" s="33">
+        <f>B6-B7</f>
+        <v/>
+      </c>
+      <c r="C8" s="33">
+        <f>C6-C7</f>
+        <v/>
+      </c>
+      <c r="D8" s="33">
+        <f>D6-D7</f>
+        <v/>
+      </c>
+      <c r="E8" s="33">
+        <f>E6-E7</f>
+        <v/>
+      </c>
+      <c r="F8" s="33">
+        <f>F6-F7</f>
+        <v/>
+      </c>
+      <c r="G8" s="34" t="n"/>
+      <c r="H8" s="34" t="n"/>
+      <c r="I8" s="34" t="n"/>
+      <c r="J8" s="34" t="n"/>
+      <c r="K8" s="34" t="n"/>
+      <c r="L8" s="34" t="n"/>
+      <c r="M8" s="34" t="n"/>
+    </row>
+    <row r="9" ht="14.25" customHeight="1">
+      <c r="A9" s="35" t="inlineStr">
+        <is>
+          <t>BVPS</t>
+        </is>
+      </c>
+      <c r="B9" s="36">
+        <f>B8/B2</f>
+        <v/>
+      </c>
+      <c r="C9" s="36">
+        <f>C8/C2</f>
+        <v/>
+      </c>
+      <c r="D9" s="36">
+        <f>D8/D2</f>
+        <v/>
+      </c>
+      <c r="E9" s="36">
+        <f>E8/E2</f>
+        <v/>
+      </c>
+      <c r="F9" s="36">
+        <f>F8/F2</f>
+        <v/>
+      </c>
+      <c r="H9" s="34" t="n"/>
+      <c r="I9" s="34" t="n"/>
+      <c r="J9" s="34" t="n"/>
+      <c r="K9" s="34" t="n"/>
+      <c r="L9" s="34" t="n"/>
+      <c r="M9" s="34" t="n"/>
+    </row>
+    <row r="10" ht="14.25" customHeight="1">
+      <c r="A10" s="35" t="inlineStr">
+        <is>
+          <t>PB</t>
+        </is>
+      </c>
+      <c r="B10" s="37">
+        <f>B3/B9</f>
+        <v/>
+      </c>
+      <c r="C10" s="37">
+        <f>C3/C9</f>
+        <v/>
+      </c>
+      <c r="D10" s="37">
+        <f>D3/D9</f>
+        <v/>
+      </c>
+      <c r="E10" s="37">
+        <f>E3/E9</f>
+        <v/>
+      </c>
+      <c r="F10" s="37">
+        <f>F3/F9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="14.25" customHeight="1"/>
+    <row r="12" ht="14.25" customHeight="1"/>
+    <row r="13" ht="14.25" customHeight="1"/>
+    <row r="14" ht="14.25" customHeight="1"/>
+    <row r="15" ht="14.25" customHeight="1"/>
+    <row r="16" ht="14.25" customHeight="1"/>
+    <row r="17" ht="14.25" customHeight="1"/>
+    <row r="18" ht="14.25" customHeight="1"/>
+    <row r="19" ht="14.25" customHeight="1"/>
+    <row r="20" ht="14.25" customHeight="1"/>
+    <row r="21" ht="14.25" customHeight="1"/>
+    <row r="22" ht="14.25" customHeight="1"/>
+    <row r="23" ht="14.25" customHeight="1"/>
+    <row r="24" ht="14.25" customHeight="1"/>
+    <row r="25" ht="14.25" customHeight="1"/>
+    <row r="26" ht="14.25" customHeight="1"/>
+    <row r="27" ht="14.25" customHeight="1"/>
+    <row r="28" ht="14.25" customHeight="1"/>
+    <row r="29" ht="14.25" customHeight="1"/>
+    <row r="30" ht="14.25" customHeight="1"/>
+    <row r="31" ht="14.25" customHeight="1"/>
+    <row r="32" ht="14.25" customHeight="1"/>
+    <row r="33" ht="14.25" customHeight="1"/>
+    <row r="34" ht="14.25" customHeight="1"/>
+    <row r="35" ht="14.25" customHeight="1"/>
+    <row r="36" ht="14.25" customHeight="1"/>
+    <row r="37" ht="14.25" customHeight="1"/>
+    <row r="38" ht="14.25" customHeight="1"/>
+    <row r="39" ht="14.25" customHeight="1"/>
+    <row r="40" ht="14.25" customHeight="1"/>
+    <row r="41" ht="14.25" customHeight="1"/>
+    <row r="42" ht="14.25" customHeight="1"/>
+    <row r="43" ht="14.25" customHeight="1"/>
+    <row r="44" ht="14.25" customHeight="1"/>
+    <row r="45" ht="14.25" customHeight="1"/>
+    <row r="46" ht="14.25" customHeight="1"/>
+    <row r="47" ht="14.25" customHeight="1"/>
+    <row r="48" ht="14.25" customHeight="1"/>
+    <row r="49" ht="14.25" customHeight="1"/>
+    <row r="50" ht="14.25" customHeight="1"/>
+    <row r="51" ht="14.25" customHeight="1"/>
+    <row r="52" ht="14.25" customHeight="1"/>
+    <row r="53" ht="14.25" customHeight="1"/>
+    <row r="54" ht="14.25" customHeight="1"/>
+    <row r="55" ht="14.25" customHeight="1"/>
+    <row r="56" ht="14.25" customHeight="1"/>
+    <row r="57" ht="14.25" customHeight="1"/>
+    <row r="58" ht="14.25" customHeight="1"/>
+    <row r="59" ht="14.25" customHeight="1"/>
+    <row r="60" ht="14.25" customHeight="1"/>
+    <row r="61" ht="14.25" customHeight="1"/>
+    <row r="62" ht="14.25" customHeight="1"/>
+    <row r="63" ht="14.25" customHeight="1"/>
+    <row r="64" ht="14.25" customHeight="1"/>
+    <row r="65" ht="14.25" customHeight="1"/>
+    <row r="66" ht="14.25" customHeight="1"/>
+    <row r="67" ht="14.25" customHeight="1"/>
+    <row r="68" ht="14.25" customHeight="1"/>
+    <row r="69" ht="14.25" customHeight="1"/>
+    <row r="70" ht="14.25" customHeight="1"/>
+    <row r="71" ht="14.25" customHeight="1"/>
+    <row r="72" ht="14.25" customHeight="1"/>
+    <row r="73" ht="14.25" customHeight="1"/>
+    <row r="74" ht="14.25" customHeight="1"/>
+    <row r="75" ht="14.25" customHeight="1"/>
+    <row r="76" ht="14.25" customHeight="1"/>
+    <row r="77" ht="14.25" customHeight="1"/>
+    <row r="78" ht="14.25" customHeight="1"/>
+    <row r="79" ht="14.25" customHeight="1"/>
+    <row r="80" ht="14.25" customHeight="1"/>
+    <row r="81" ht="14.25" customHeight="1"/>
+    <row r="82" ht="14.25" customHeight="1"/>
+    <row r="83" ht="14.25" customHeight="1"/>
+    <row r="84" ht="14.25" customHeight="1"/>
+    <row r="85" ht="14.25" customHeight="1"/>
+    <row r="86" ht="14.25" customHeight="1"/>
+    <row r="87" ht="14.25" customHeight="1"/>
+    <row r="88" ht="14.25" customHeight="1"/>
+    <row r="89" ht="14.25" customHeight="1"/>
+    <row r="90" ht="14.25" customHeight="1"/>
+    <row r="91" ht="14.25" customHeight="1"/>
+    <row r="92" ht="14.25" customHeight="1"/>
+    <row r="93" ht="14.25" customHeight="1"/>
+    <row r="94" ht="14.25" customHeight="1"/>
+    <row r="95" ht="14.25" customHeight="1"/>
+    <row r="96" ht="14.25" customHeight="1"/>
+    <row r="97" ht="14.25" customHeight="1"/>
+    <row r="98" ht="14.25" customHeight="1"/>
+    <row r="99" ht="14.25" customHeight="1"/>
+    <row r="100" ht="14.25" customHeight="1"/>
+    <row r="101" ht="14.25" customHeight="1"/>
+    <row r="102" ht="14.25" customHeight="1"/>
+    <row r="103" ht="14.25" customHeight="1"/>
+    <row r="104" ht="14.25" customHeight="1"/>
+    <row r="105" ht="14.25" customHeight="1"/>
+    <row r="106" ht="14.25" customHeight="1"/>
+    <row r="107" ht="14.25" customHeight="1"/>
+    <row r="108" ht="14.25" customHeight="1"/>
+    <row r="109" ht="14.25" customHeight="1"/>
+    <row r="110" ht="14.25" customHeight="1"/>
+    <row r="111" ht="14.25" customHeight="1"/>
+    <row r="112" ht="14.25" customHeight="1"/>
+    <row r="113" ht="14.25" customHeight="1"/>
+    <row r="114" ht="14.25" customHeight="1"/>
+    <row r="115" ht="14.25" customHeight="1"/>
+    <row r="116" ht="14.25" customHeight="1"/>
+    <row r="117" ht="14.25" customHeight="1"/>
+    <row r="118" ht="14.25" customHeight="1"/>
+    <row r="119" ht="14.25" customHeight="1"/>
+    <row r="120" ht="14.25" customHeight="1"/>
+    <row r="121" ht="14.25" customHeight="1"/>
+    <row r="122" ht="14.25" customHeight="1"/>
+    <row r="123" ht="14.25" customHeight="1"/>
+    <row r="124" ht="14.25" customHeight="1"/>
+    <row r="125" ht="14.25" customHeight="1"/>
+    <row r="126" ht="14.25" customHeight="1"/>
+    <row r="127" ht="14.25" customHeight="1"/>
+    <row r="128" ht="14.25" customHeight="1"/>
+    <row r="129" ht="14.25" customHeight="1"/>
+    <row r="130" ht="14.25" customHeight="1"/>
+    <row r="131" ht="14.25" customHeight="1"/>
+    <row r="132" ht="14.25" customHeight="1"/>
+    <row r="133" ht="14.25" customHeight="1"/>
+    <row r="134" ht="14.25" customHeight="1"/>
+    <row r="135" ht="14.25" customHeight="1"/>
+    <row r="136" ht="14.25" customHeight="1"/>
+    <row r="137" ht="14.25" customHeight="1"/>
+    <row r="138" ht="14.25" customHeight="1"/>
+    <row r="139" ht="14.25" customHeight="1"/>
+    <row r="140" ht="14.25" customHeight="1"/>
+    <row r="141" ht="14.25" customHeight="1"/>
+    <row r="142" ht="14.25" customHeight="1"/>
+    <row r="143" ht="14.25" customHeight="1"/>
+    <row r="144" ht="14.25" customHeight="1"/>
+    <row r="145" ht="14.25" customHeight="1"/>
+    <row r="146" ht="14.25" customHeight="1"/>
+    <row r="147" ht="14.25" customHeight="1"/>
+    <row r="148" ht="14.25" customHeight="1"/>
+    <row r="149" ht="14.25" customHeight="1"/>
+    <row r="150" ht="14.25" customHeight="1"/>
+    <row r="151" ht="14.25" customHeight="1"/>
+    <row r="152" ht="14.25" customHeight="1"/>
+    <row r="153" ht="14.25" customHeight="1"/>
+    <row r="154" ht="14.25" customHeight="1"/>
+    <row r="155" ht="14.25" customHeight="1"/>
+    <row r="156" ht="14.25" customHeight="1"/>
+    <row r="157" ht="14.25" customHeight="1"/>
+    <row r="158" ht="14.25" customHeight="1"/>
+    <row r="159" ht="14.25" customHeight="1"/>
+    <row r="160" ht="14.25" customHeight="1"/>
+    <row r="161" ht="14.25" customHeight="1"/>
+    <row r="162" ht="14.25" customHeight="1"/>
+    <row r="163" ht="14.25" customHeight="1"/>
+    <row r="164" ht="14.25" customHeight="1"/>
+    <row r="165" ht="14.25" customHeight="1"/>
+    <row r="166" ht="14.25" customHeight="1"/>
+    <row r="167" ht="14.25" customHeight="1"/>
+    <row r="168" ht="14.25" customHeight="1"/>
+    <row r="169" ht="14.25" customHeight="1"/>
+    <row r="170" ht="14.25" customHeight="1"/>
+    <row r="171" ht="14.25" customHeight="1"/>
+    <row r="172" ht="14.25" customHeight="1"/>
+    <row r="173" ht="14.25" customHeight="1"/>
+    <row r="174" ht="14.25" customHeight="1"/>
+    <row r="175" ht="14.25" customHeight="1"/>
+    <row r="176" ht="14.25" customHeight="1"/>
+    <row r="177" ht="14.25" customHeight="1"/>
+    <row r="178" ht="14.25" customHeight="1"/>
+    <row r="179" ht="14.25" customHeight="1"/>
+    <row r="180" ht="14.25" customHeight="1"/>
+    <row r="181" ht="14.25" customHeight="1"/>
+    <row r="182" ht="14.25" customHeight="1"/>
+    <row r="183" ht="14.25" customHeight="1"/>
+    <row r="184" ht="14.25" customHeight="1"/>
+    <row r="185" ht="14.25" customHeight="1"/>
+    <row r="186" ht="14.25" customHeight="1"/>
+    <row r="187" ht="14.25" customHeight="1"/>
+    <row r="188" ht="14.25" customHeight="1"/>
+    <row r="189" ht="14.25" customHeight="1"/>
+    <row r="190" ht="14.25" customHeight="1"/>
+    <row r="191" ht="14.25" customHeight="1"/>
+    <row r="192" ht="14.25" customHeight="1"/>
+    <row r="193" ht="14.25" customHeight="1"/>
+    <row r="194" ht="14.25" customHeight="1"/>
+    <row r="195" ht="14.25" customHeight="1"/>
+    <row r="196" ht="14.25" customHeight="1"/>
+    <row r="197" ht="14.25" customHeight="1"/>
+    <row r="198" ht="14.25" customHeight="1"/>
+    <row r="199" ht="14.25" customHeight="1"/>
+    <row r="200" ht="14.25" customHeight="1"/>
+    <row r="201" ht="14.25" customHeight="1"/>
+    <row r="202" ht="14.25" customHeight="1"/>
+    <row r="203" ht="14.25" customHeight="1"/>
+    <row r="204" ht="14.25" customHeight="1"/>
+    <row r="205" ht="14.25" customHeight="1"/>
+    <row r="206" ht="14.25" customHeight="1"/>
+    <row r="207" ht="14.25" customHeight="1"/>
+    <row r="208" ht="14.25" customHeight="1"/>
+    <row r="209" ht="14.25" customHeight="1"/>
+    <row r="210" ht="14.25" customHeight="1"/>
+    <row r="211" ht="14.25" customHeight="1"/>
+    <row r="212" ht="14.25" customHeight="1"/>
+    <row r="213" ht="14.25" customHeight="1"/>
+    <row r="214" ht="14.25" customHeight="1"/>
+    <row r="215" ht="14.25" customHeight="1"/>
+    <row r="216" ht="14.25" customHeight="1"/>
+    <row r="217" ht="14.25" customHeight="1"/>
+    <row r="218" ht="14.25" customHeight="1"/>
+    <row r="219" ht="14.25" customHeight="1"/>
+    <row r="220" ht="14.25" customHeight="1"/>
+    <row r="221" ht="14.25" customHeight="1"/>
+    <row r="222" ht="14.25" customHeight="1"/>
+    <row r="223" ht="14.25" customHeight="1"/>
+    <row r="224" ht="14.25" customHeight="1"/>
+    <row r="225" ht="14.25" customHeight="1"/>
+    <row r="226" ht="14.25" customHeight="1"/>
+    <row r="227" ht="14.25" customHeight="1"/>
+    <row r="228" ht="14.25" customHeight="1"/>
+    <row r="229" ht="14.25" customHeight="1"/>
+    <row r="230" ht="14.25" customHeight="1"/>
+    <row r="231" ht="14.25" customHeight="1"/>
+    <row r="232" ht="14.25" customHeight="1"/>
+    <row r="233" ht="14.25" customHeight="1"/>
+    <row r="234" ht="14.25" customHeight="1"/>
+    <row r="235" ht="14.25" customHeight="1"/>
+    <row r="236" ht="14.25" customHeight="1"/>
+    <row r="237" ht="14.25" customHeight="1"/>
+    <row r="238" ht="14.25" customHeight="1"/>
+    <row r="239" ht="14.25" customHeight="1"/>
+    <row r="240" ht="14.25" customHeight="1"/>
+    <row r="241" ht="14.25" customHeight="1"/>
+    <row r="242" ht="14.25" customHeight="1"/>
+    <row r="243" ht="14.25" customHeight="1"/>
+    <row r="244" ht="14.25" customHeight="1"/>
+    <row r="245" ht="14.25" customHeight="1"/>
+    <row r="246" ht="14.25" customHeight="1"/>
+    <row r="247" ht="14.25" customHeight="1"/>
+    <row r="248" ht="14.25" customHeight="1"/>
+    <row r="249" ht="14.25" customHeight="1"/>
+    <row r="250" ht="14.25" customHeight="1"/>
+    <row r="251" ht="14.25" customHeight="1"/>
+    <row r="252" ht="14.25" customHeight="1"/>
+    <row r="253" ht="14.25" customHeight="1"/>
+    <row r="254" ht="14.25" customHeight="1"/>
+    <row r="255" ht="14.25" customHeight="1"/>
+    <row r="256" ht="14.25" customHeight="1"/>
+    <row r="257" ht="14.25" customHeight="1"/>
+    <row r="258" ht="14.25" customHeight="1"/>
+    <row r="259" ht="14.25" customHeight="1"/>
+    <row r="260" ht="14.25" customHeight="1"/>
+    <row r="261" ht="14.25" customHeight="1"/>
+    <row r="262" ht="14.25" customHeight="1"/>
+    <row r="263" ht="14.25" customHeight="1"/>
+    <row r="264" ht="14.25" customHeight="1"/>
+    <row r="265" ht="14.25" customHeight="1"/>
+    <row r="266" ht="14.25" customHeight="1"/>
+    <row r="267" ht="14.25" customHeight="1"/>
+    <row r="268" ht="14.25" customHeight="1"/>
+    <row r="269" ht="14.25" customHeight="1"/>
+    <row r="270" ht="14.25" customHeight="1"/>
+    <row r="271" ht="14.25" customHeight="1"/>
+    <row r="272" ht="14.25" customHeight="1"/>
+    <row r="273" ht="14.25" customHeight="1"/>
+    <row r="274" ht="14.25" customHeight="1"/>
+    <row r="275" ht="14.25" customHeight="1"/>
+    <row r="276" ht="14.25" customHeight="1"/>
+    <row r="277" ht="14.25" customHeight="1"/>
+    <row r="278" ht="14.25" customHeight="1"/>
+    <row r="279" ht="14.25" customHeight="1"/>
+    <row r="280" ht="14.25" customHeight="1"/>
+    <row r="281" ht="14.25" customHeight="1"/>
+    <row r="282" ht="14.25" customHeight="1"/>
+    <row r="283" ht="14.25" customHeight="1"/>
+    <row r="284" ht="14.25" customHeight="1"/>
+    <row r="285" ht="14.25" customHeight="1"/>
+    <row r="286" ht="14.25" customHeight="1"/>
+    <row r="287" ht="14.25" customHeight="1"/>
+    <row r="288" ht="14.25" customHeight="1"/>
+    <row r="289" ht="14.25" customHeight="1"/>
+    <row r="290" ht="14.25" customHeight="1"/>
+    <row r="291" ht="14.25" customHeight="1"/>
+    <row r="292" ht="14.25" customHeight="1"/>
+    <row r="293" ht="14.25" customHeight="1"/>
+    <row r="294" ht="14.25" customHeight="1"/>
+    <row r="295" ht="14.25" customHeight="1"/>
+    <row r="296" ht="14.25" customHeight="1"/>
+    <row r="297" ht="14.25" customHeight="1"/>
+    <row r="298" ht="14.25" customHeight="1"/>
+    <row r="299" ht="14.25" customHeight="1"/>
+    <row r="300" ht="14.25" customHeight="1"/>
+    <row r="301" ht="14.25" customHeight="1"/>
+    <row r="302" ht="14.25" customHeight="1"/>
+    <row r="303" ht="14.25" customHeight="1"/>
+    <row r="304" ht="14.25" customHeight="1"/>
+    <row r="305" ht="14.25" customHeight="1"/>
+    <row r="306" ht="14.25" customHeight="1"/>
+    <row r="307" ht="14.25" customHeight="1"/>
+    <row r="308" ht="14.25" customHeight="1"/>
+    <row r="309" ht="14.25" customHeight="1"/>
+    <row r="310" ht="14.25" customHeight="1"/>
+    <row r="311" ht="14.25" customHeight="1"/>
+    <row r="312" ht="14.25" customHeight="1"/>
+    <row r="313" ht="14.25" customHeight="1"/>
+    <row r="314" ht="14.25" customHeight="1"/>
+    <row r="315" ht="14.25" customHeight="1"/>
+    <row r="316" ht="14.25" customHeight="1"/>
+    <row r="317" ht="14.25" customHeight="1"/>
+    <row r="318" ht="14.25" customHeight="1"/>
+    <row r="319" ht="14.25" customHeight="1"/>
+    <row r="320" ht="14.25" customHeight="1"/>
+    <row r="321" ht="14.25" customHeight="1"/>
+    <row r="322" ht="14.25" customHeight="1"/>
+    <row r="323" ht="14.25" customHeight="1"/>
+    <row r="324" ht="14.25" customHeight="1"/>
+    <row r="325" ht="14.25" customHeight="1"/>
+    <row r="326" ht="14.25" customHeight="1"/>
+    <row r="327" ht="14.25" customHeight="1"/>
+    <row r="328" ht="14.25" customHeight="1"/>
+    <row r="329" ht="14.25" customHeight="1"/>
+    <row r="330" ht="14.25" customHeight="1"/>
+    <row r="331" ht="14.25" customHeight="1"/>
+    <row r="332" ht="14.25" customHeight="1"/>
+    <row r="333" ht="14.25" customHeight="1"/>
+    <row r="334" ht="14.25" customHeight="1"/>
+    <row r="335" ht="14.25" customHeight="1"/>
+    <row r="336" ht="14.25" customHeight="1"/>
+    <row r="337" ht="14.25" customHeight="1"/>
+    <row r="338" ht="14.25" customHeight="1"/>
+    <row r="339" ht="14.25" customHeight="1"/>
+    <row r="340" ht="14.25" customHeight="1"/>
+    <row r="341" ht="14.25" customHeight="1"/>
+    <row r="342" ht="14.25" customHeight="1"/>
+    <row r="343" ht="14.25" customHeight="1"/>
+    <row r="344" ht="14.25" customHeight="1"/>
+    <row r="345" ht="14.25" customHeight="1"/>
+    <row r="346" ht="14.25" customHeight="1"/>
+    <row r="347" ht="14.25" customHeight="1"/>
+    <row r="348" ht="14.25" customHeight="1"/>
+    <row r="349" ht="14.25" customHeight="1"/>
+    <row r="350" ht="14.25" customHeight="1"/>
+    <row r="351" ht="14.25" customHeight="1"/>
+    <row r="352" ht="14.25" customHeight="1"/>
+    <row r="353" ht="14.25" customHeight="1"/>
+    <row r="354" ht="14.25" customHeight="1"/>
+    <row r="355" ht="14.25" customHeight="1"/>
+    <row r="356" ht="14.25" customHeight="1"/>
+    <row r="357" ht="14.25" customHeight="1"/>
+    <row r="358" ht="14.25" customHeight="1"/>
+    <row r="359" ht="14.25" customHeight="1"/>
+    <row r="360" ht="14.25" customHeight="1"/>
+    <row r="361" ht="14.25" customHeight="1"/>
+    <row r="362" ht="14.25" customHeight="1"/>
+    <row r="363" ht="14.25" customHeight="1"/>
+    <row r="364" ht="14.25" customHeight="1"/>
+    <row r="365" ht="14.25" customHeight="1"/>
+    <row r="366" ht="14.25" customHeight="1"/>
+    <row r="367" ht="14.25" customHeight="1"/>
+    <row r="368" ht="14.25" customHeight="1"/>
+    <row r="369" ht="14.25" customHeight="1"/>
+    <row r="370" ht="14.25" customHeight="1"/>
+    <row r="371" ht="14.25" customHeight="1"/>
+    <row r="372" ht="14.25" customHeight="1"/>
+    <row r="373" ht="14.25" customHeight="1"/>
+    <row r="374" ht="14.25" customHeight="1"/>
+    <row r="375" ht="14.25" customHeight="1"/>
+    <row r="376" ht="14.25" customHeight="1"/>
+    <row r="377" ht="14.25" customHeight="1"/>
+    <row r="378" ht="14.25" customHeight="1"/>
+    <row r="379" ht="14.25" customHeight="1"/>
+    <row r="380" ht="14.25" customHeight="1"/>
+    <row r="381" ht="14.25" customHeight="1"/>
+    <row r="382" ht="14.25" customHeight="1"/>
+    <row r="383" ht="14.25" customHeight="1"/>
+    <row r="384" ht="14.25" customHeight="1"/>
+    <row r="385" ht="14.25" customHeight="1"/>
+    <row r="386" ht="14.25" customHeight="1"/>
+    <row r="387" ht="14.25" customHeight="1"/>
+    <row r="388" ht="14.25" customHeight="1"/>
+    <row r="389" ht="14.25" customHeight="1"/>
+    <row r="390" ht="14.25" customHeight="1"/>
+    <row r="391" ht="14.25" customHeight="1"/>
+    <row r="392" ht="14.25" customHeight="1"/>
+    <row r="393" ht="14.25" customHeight="1"/>
+    <row r="394" ht="14.25" customHeight="1"/>
+    <row r="395" ht="14.25" customHeight="1"/>
+    <row r="396" ht="14.25" customHeight="1"/>
+    <row r="397" ht="14.25" customHeight="1"/>
+    <row r="398" ht="14.25" customHeight="1"/>
+    <row r="399" ht="14.25" customHeight="1"/>
+    <row r="400" ht="14.25" customHeight="1"/>
+    <row r="401" ht="14.25" customHeight="1"/>
+    <row r="402" ht="14.25" customHeight="1"/>
+    <row r="403" ht="14.25" customHeight="1"/>
+    <row r="404" ht="14.25" customHeight="1"/>
+    <row r="405" ht="14.25" customHeight="1"/>
+    <row r="406" ht="14.25" customHeight="1"/>
+    <row r="407" ht="14.25" customHeight="1"/>
+    <row r="408" ht="14.25" customHeight="1"/>
+    <row r="409" ht="14.25" customHeight="1"/>
+    <row r="410" ht="14.25" customHeight="1"/>
+    <row r="411" ht="14.25" customHeight="1"/>
+    <row r="412" ht="14.25" customHeight="1"/>
+    <row r="413" ht="14.25" customHeight="1"/>
+    <row r="414" ht="14.25" customHeight="1"/>
+    <row r="415" ht="14.25" customHeight="1"/>
+    <row r="416" ht="14.25" customHeight="1"/>
+    <row r="417" ht="14.25" customHeight="1"/>
+    <row r="418" ht="14.25" customHeight="1"/>
+    <row r="419" ht="14.25" customHeight="1"/>
+    <row r="420" ht="14.25" customHeight="1"/>
+    <row r="421" ht="14.25" customHeight="1"/>
+    <row r="422" ht="14.25" customHeight="1"/>
+    <row r="423" ht="14.25" customHeight="1"/>
+    <row r="424" ht="14.25" customHeight="1"/>
+    <row r="425" ht="14.25" customHeight="1"/>
+    <row r="426" ht="14.25" customHeight="1"/>
+    <row r="427" ht="14.25" customHeight="1"/>
+    <row r="428" ht="14.25" customHeight="1"/>
+    <row r="429" ht="14.25" customHeight="1"/>
+    <row r="430" ht="14.25" customHeight="1"/>
+    <row r="431" ht="14.25" customHeight="1"/>
+    <row r="432" ht="14.25" customHeight="1"/>
+    <row r="433" ht="14.25" customHeight="1"/>
+    <row r="434" ht="14.25" customHeight="1"/>
+    <row r="435" ht="14.25" customHeight="1"/>
+    <row r="436" ht="14.25" customHeight="1"/>
+    <row r="437" ht="14.25" customHeight="1"/>
+    <row r="438" ht="14.25" customHeight="1"/>
+    <row r="439" ht="14.25" customHeight="1"/>
+    <row r="440" ht="14.25" customHeight="1"/>
+    <row r="441" ht="14.25" customHeight="1"/>
+    <row r="442" ht="14.25" customHeight="1"/>
+    <row r="443" ht="14.25" customHeight="1"/>
+    <row r="444" ht="14.25" customHeight="1"/>
+    <row r="445" ht="14.25" customHeight="1"/>
+    <row r="446" ht="14.25" customHeight="1"/>
+    <row r="447" ht="14.25" customHeight="1"/>
+    <row r="448" ht="14.25" customHeight="1"/>
+    <row r="449" ht="14.25" customHeight="1"/>
+    <row r="450" ht="14.25" customHeight="1"/>
+    <row r="451" ht="14.25" customHeight="1"/>
+    <row r="452" ht="14.25" customHeight="1"/>
+    <row r="453" ht="14.25" customHeight="1"/>
+    <row r="454" ht="14.25" customHeight="1"/>
+    <row r="455" ht="14.25" customHeight="1"/>
+    <row r="456" ht="14.25" customHeight="1"/>
+    <row r="457" ht="14.25" customHeight="1"/>
+    <row r="458" ht="14.25" customHeight="1"/>
+    <row r="459" ht="14.25" customHeight="1"/>
+    <row r="460" ht="14.25" customHeight="1"/>
+    <row r="461" ht="14.25" customHeight="1"/>
+    <row r="462" ht="14.25" customHeight="1"/>
+    <row r="463" ht="14.25" customHeight="1"/>
+    <row r="464" ht="14.25" customHeight="1"/>
+    <row r="465" ht="14.25" customHeight="1"/>
+    <row r="466" ht="14.25" customHeight="1"/>
+    <row r="467" ht="14.25" customHeight="1"/>
+    <row r="468" ht="14.25" customHeight="1"/>
+    <row r="469" ht="14.25" customHeight="1"/>
+    <row r="470" ht="14.25" customHeight="1"/>
+    <row r="471" ht="14.25" customHeight="1"/>
+    <row r="472" ht="14.25" customHeight="1"/>
+    <row r="473" ht="14.25" customHeight="1"/>
+    <row r="474" ht="14.25" customHeight="1"/>
+    <row r="475" ht="14.25" customHeight="1"/>
+    <row r="476" ht="14.25" customHeight="1"/>
+    <row r="477" ht="14.25" customHeight="1"/>
+    <row r="478" ht="14.25" customHeight="1"/>
+    <row r="479" ht="14.25" customHeight="1"/>
+    <row r="480" ht="14.25" customHeight="1"/>
+    <row r="481" ht="14.25" customHeight="1"/>
+    <row r="482" ht="14.25" customHeight="1"/>
+    <row r="483" ht="14.25" customHeight="1"/>
+    <row r="484" ht="14.25" customHeight="1"/>
+    <row r="485" ht="14.25" customHeight="1"/>
+    <row r="486" ht="14.25" customHeight="1"/>
+    <row r="487" ht="14.25" customHeight="1"/>
+    <row r="488" ht="14.25" customHeight="1"/>
+    <row r="489" ht="14.25" customHeight="1"/>
+    <row r="490" ht="14.25" customHeight="1"/>
+    <row r="491" ht="14.25" customHeight="1"/>
+    <row r="492" ht="14.25" customHeight="1"/>
+    <row r="493" ht="14.25" customHeight="1"/>
+    <row r="494" ht="14.25" customHeight="1"/>
+    <row r="495" ht="14.25" customHeight="1"/>
+    <row r="496" ht="14.25" customHeight="1"/>
+    <row r="497" ht="14.25" customHeight="1"/>
+    <row r="498" ht="14.25" customHeight="1"/>
+    <row r="499" ht="14.25" customHeight="1"/>
+    <row r="500" ht="14.25" customHeight="1"/>
+    <row r="501" ht="14.25" customHeight="1"/>
+    <row r="502" ht="14.25" customHeight="1"/>
+    <row r="503" ht="14.25" customHeight="1"/>
+    <row r="504" ht="14.25" customHeight="1"/>
+    <row r="505" ht="14.25" customHeight="1"/>
+    <row r="506" ht="14.25" customHeight="1"/>
+    <row r="507" ht="14.25" customHeight="1"/>
+    <row r="508" ht="14.25" customHeight="1"/>
+    <row r="509" ht="14.25" customHeight="1"/>
+    <row r="510" ht="14.25" customHeight="1"/>
+    <row r="511" ht="14.25" customHeight="1"/>
+    <row r="512" ht="14.25" customHeight="1"/>
+    <row r="513" ht="14.25" customHeight="1"/>
+    <row r="514" ht="14.25" customHeight="1"/>
+    <row r="515" ht="14.25" customHeight="1"/>
+    <row r="516" ht="14.25" customHeight="1"/>
+    <row r="517" ht="14.25" customHeight="1"/>
+    <row r="518" ht="14.25" customHeight="1"/>
+    <row r="519" ht="14.25" customHeight="1"/>
+    <row r="520" ht="14.25" customHeight="1"/>
+    <row r="521" ht="14.25" customHeight="1"/>
+    <row r="522" ht="14.25" customHeight="1"/>
+    <row r="523" ht="14.25" customHeight="1"/>
+    <row r="524" ht="14.25" customHeight="1"/>
+    <row r="525" ht="14.25" customHeight="1"/>
+    <row r="526" ht="14.25" customHeight="1"/>
+    <row r="527" ht="14.25" customHeight="1"/>
+    <row r="528" ht="14.25" customHeight="1"/>
+    <row r="529" ht="14.25" customHeight="1"/>
+    <row r="530" ht="14.25" customHeight="1"/>
+    <row r="531" ht="14.25" customHeight="1"/>
+    <row r="532" ht="14.25" customHeight="1"/>
+    <row r="533" ht="14.25" customHeight="1"/>
+    <row r="534" ht="14.25" customHeight="1"/>
+    <row r="535" ht="14.25" customHeight="1"/>
+    <row r="536" ht="14.25" customHeight="1"/>
+    <row r="537" ht="14.25" customHeight="1"/>
+    <row r="538" ht="14.25" customHeight="1"/>
+    <row r="539" ht="14.25" customHeight="1"/>
+    <row r="540" ht="14.25" customHeight="1"/>
+    <row r="541" ht="14.25" customHeight="1"/>
+    <row r="542" ht="14.25" customHeight="1"/>
+    <row r="543" ht="14.25" customHeight="1"/>
+    <row r="544" ht="14.25" customHeight="1"/>
+    <row r="545" ht="14.25" customHeight="1"/>
+    <row r="546" ht="14.25" customHeight="1"/>
+    <row r="547" ht="14.25" customHeight="1"/>
+    <row r="548" ht="14.25" customHeight="1"/>
+    <row r="549" ht="14.25" customHeight="1"/>
+    <row r="550" ht="14.25" customHeight="1"/>
+    <row r="551" ht="14.25" customHeight="1"/>
+    <row r="552" ht="14.25" customHeight="1"/>
+    <row r="553" ht="14.25" customHeight="1"/>
+    <row r="554" ht="14.25" customHeight="1"/>
+    <row r="555" ht="14.25" customHeight="1"/>
+    <row r="556" ht="14.25" customHeight="1"/>
+    <row r="557" ht="14.25" customHeight="1"/>
+    <row r="558" ht="14.25" customHeight="1"/>
+    <row r="559" ht="14.25" customHeight="1"/>
+    <row r="560" ht="14.25" customHeight="1"/>
+    <row r="561" ht="14.25" customHeight="1"/>
+    <row r="562" ht="14.25" customHeight="1"/>
+    <row r="563" ht="14.25" customHeight="1"/>
+    <row r="564" ht="14.25" customHeight="1"/>
+    <row r="565" ht="14.25" customHeight="1"/>
+    <row r="566" ht="14.25" customHeight="1"/>
+    <row r="567" ht="14.25" customHeight="1"/>
+    <row r="568" ht="14.25" customHeight="1"/>
+    <row r="569" ht="14.25" customHeight="1"/>
+    <row r="570" ht="14.25" customHeight="1"/>
+    <row r="571" ht="14.25" customHeight="1"/>
+    <row r="572" ht="14.25" customHeight="1"/>
+    <row r="573" ht="14.25" customHeight="1"/>
+    <row r="574" ht="14.25" customHeight="1"/>
+    <row r="575" ht="14.25" customHeight="1"/>
+    <row r="576" ht="14.25" customHeight="1"/>
+    <row r="577" ht="14.25" customHeight="1"/>
+    <row r="578" ht="14.25" customHeight="1"/>
+    <row r="579" ht="14.25" customHeight="1"/>
+    <row r="580" ht="14.25" customHeight="1"/>
+    <row r="581" ht="14.25" customHeight="1"/>
+    <row r="582" ht="14.25" customHeight="1"/>
+    <row r="583" ht="14.25" customHeight="1"/>
+    <row r="584" ht="14.25" customHeight="1"/>
+    <row r="585" ht="14.25" customHeight="1"/>
+    <row r="586" ht="14.25" customHeight="1"/>
+    <row r="587" ht="14.25" customHeight="1"/>
+    <row r="588" ht="14.25" customHeight="1"/>
+    <row r="589" ht="14.25" customHeight="1"/>
+    <row r="590" ht="14.25" customHeight="1"/>
+    <row r="591" ht="14.25" customHeight="1"/>
+    <row r="592" ht="14.25" customHeight="1"/>
+    <row r="593" ht="14.25" customHeight="1"/>
+    <row r="594" ht="14.25" customHeight="1"/>
+    <row r="595" ht="14.25" customHeight="1"/>
+    <row r="596" ht="14.25" customHeight="1"/>
+    <row r="597" ht="14.25" customHeight="1"/>
+    <row r="598" ht="14.25" customHeight="1"/>
+    <row r="599" ht="14.25" customHeight="1"/>
+    <row r="600" ht="14.25" customHeight="1"/>
+    <row r="601" ht="14.25" customHeight="1"/>
+    <row r="602" ht="14.25" customHeight="1"/>
+    <row r="603" ht="14.25" customHeight="1"/>
+    <row r="604" ht="14.25" customHeight="1"/>
+    <row r="605" ht="14.25" customHeight="1"/>
+    <row r="606" ht="14.25" customHeight="1"/>
+    <row r="607" ht="14.25" customHeight="1"/>
+    <row r="608" ht="14.25" customHeight="1"/>
+    <row r="609" ht="14.25" customHeight="1"/>
+    <row r="610" ht="14.25" customHeight="1"/>
+    <row r="611" ht="14.25" customHeight="1"/>
+    <row r="612" ht="14.25" customHeight="1"/>
+    <row r="613" ht="14.25" customHeight="1"/>
+    <row r="614" ht="14.25" customHeight="1"/>
+    <row r="615" ht="14.25" customHeight="1"/>
+    <row r="616" ht="14.25" customHeight="1"/>
+    <row r="617" ht="14.25" customHeight="1"/>
+    <row r="618" ht="14.25" customHeight="1"/>
+    <row r="619" ht="14.25" customHeight="1"/>
+    <row r="620" ht="14.25" customHeight="1"/>
+    <row r="621" ht="14.25" customHeight="1"/>
+    <row r="622" ht="14.25" customHeight="1"/>
+    <row r="623" ht="14.25" customHeight="1"/>
+    <row r="624" ht="14.25" customHeight="1"/>
+    <row r="625" ht="14.25" customHeight="1"/>
+    <row r="626" ht="14.25" customHeight="1"/>
+    <row r="627" ht="14.25" customHeight="1"/>
+    <row r="628" ht="14.25" customHeight="1"/>
+    <row r="629" ht="14.25" customHeight="1"/>
+    <row r="630" ht="14.25" customHeight="1"/>
+    <row r="631" ht="14.25" customHeight="1"/>
+    <row r="632" ht="14.25" customHeight="1"/>
+    <row r="633" ht="14.25" customHeight="1"/>
+    <row r="634" ht="14.25" customHeight="1"/>
+    <row r="635" ht="14.25" customHeight="1"/>
+    <row r="636" ht="14.25" customHeight="1"/>
+    <row r="637" ht="14.25" customHeight="1"/>
+    <row r="638" ht="14.25" customHeight="1"/>
+    <row r="639" ht="14.25" customHeight="1"/>
+    <row r="640" ht="14.25" customHeight="1"/>
+    <row r="641" ht="14.25" customHeight="1"/>
+    <row r="642" ht="14.25" customHeight="1"/>
+    <row r="643" ht="14.25" customHeight="1"/>
+    <row r="644" ht="14.25" customHeight="1"/>
+    <row r="645" ht="14.25" customHeight="1"/>
+    <row r="646" ht="14.25" customHeight="1"/>
+    <row r="647" ht="14.25" customHeight="1"/>
+    <row r="648" ht="14.25" customHeight="1"/>
+    <row r="649" ht="14.25" customHeight="1"/>
+    <row r="650" ht="14.25" customHeight="1"/>
+    <row r="651" ht="14.25" customHeight="1"/>
+    <row r="652" ht="14.25" customHeight="1"/>
+    <row r="653" ht="14.25" customHeight="1"/>
+    <row r="654" ht="14.25" customHeight="1"/>
+    <row r="655" ht="14.25" customHeight="1"/>
+    <row r="656" ht="14.25" customHeight="1"/>
+    <row r="657" ht="14.25" customHeight="1"/>
+    <row r="658" ht="14.25" customHeight="1"/>
+    <row r="659" ht="14.25" customHeight="1"/>
+    <row r="660" ht="14.25" customHeight="1"/>
+    <row r="661" ht="14.25" customHeight="1"/>
+    <row r="662" ht="14.25" customHeight="1"/>
+    <row r="663" ht="14.25" customHeight="1"/>
+    <row r="664" ht="14.25" customHeight="1"/>
+    <row r="665" ht="14.25" customHeight="1"/>
+    <row r="666" ht="14.25" customHeight="1"/>
+    <row r="667" ht="14.25" customHeight="1"/>
+    <row r="668" ht="14.25" customHeight="1"/>
+    <row r="669" ht="14.25" customHeight="1"/>
+    <row r="670" ht="14.25" customHeight="1"/>
+    <row r="671" ht="14.25" customHeight="1"/>
+    <row r="672" ht="14.25" customHeight="1"/>
+    <row r="673" ht="14.25" customHeight="1"/>
+    <row r="674" ht="14.25" customHeight="1"/>
+    <row r="675" ht="14.25" customHeight="1"/>
+    <row r="676" ht="14.25" customHeight="1"/>
+    <row r="677" ht="14.25" customHeight="1"/>
+    <row r="678" ht="14.25" customHeight="1"/>
+    <row r="679" ht="14.25" customHeight="1"/>
+    <row r="680" ht="14.25" customHeight="1"/>
+    <row r="681" ht="14.25" customHeight="1"/>
+    <row r="682" ht="14.25" customHeight="1"/>
+    <row r="683" ht="14.25" customHeight="1"/>
+    <row r="684" ht="14.25" customHeight="1"/>
+    <row r="685" ht="14.25" customHeight="1"/>
+    <row r="686" ht="14.25" customHeight="1"/>
+    <row r="687" ht="14.25" customHeight="1"/>
+    <row r="688" ht="14.25" customHeight="1"/>
+    <row r="689" ht="14.25" customHeight="1"/>
+    <row r="690" ht="14.25" customHeight="1"/>
+    <row r="691" ht="14.25" customHeight="1"/>
+    <row r="692" ht="14.25" customHeight="1"/>
+    <row r="693" ht="14.25" customHeight="1"/>
+    <row r="694" ht="14.25" customHeight="1"/>
+    <row r="695" ht="14.25" customHeight="1"/>
+    <row r="696" ht="14.25" customHeight="1"/>
+    <row r="697" ht="14.25" customHeight="1"/>
+    <row r="698" ht="14.25" customHeight="1"/>
+    <row r="699" ht="14.25" customHeight="1"/>
+    <row r="700" ht="14.25" customHeight="1"/>
+    <row r="701" ht="14.25" customHeight="1"/>
+    <row r="702" ht="14.25" customHeight="1"/>
+    <row r="703" ht="14.25" customHeight="1"/>
+    <row r="704" ht="14.25" customHeight="1"/>
+    <row r="705" ht="14.25" customHeight="1"/>
+    <row r="706" ht="14.25" customHeight="1"/>
+    <row r="707" ht="14.25" customHeight="1"/>
+    <row r="708" ht="14.25" customHeight="1"/>
+    <row r="709" ht="14.25" customHeight="1"/>
+    <row r="710" ht="14.25" customHeight="1"/>
+    <row r="711" ht="14.25" customHeight="1"/>
+    <row r="712" ht="14.25" customHeight="1"/>
+    <row r="713" ht="14.25" customHeight="1"/>
+    <row r="714" ht="14.25" customHeight="1"/>
+    <row r="715" ht="14.25" customHeight="1"/>
+    <row r="716" ht="14.25" customHeight="1"/>
+    <row r="717" ht="14.25" customHeight="1"/>
+    <row r="718" ht="14.25" customHeight="1"/>
+    <row r="719" ht="14.25" customHeight="1"/>
+    <row r="720" ht="14.25" customHeight="1"/>
+    <row r="721" ht="14.25" customHeight="1"/>
+    <row r="722" ht="14.25" customHeight="1"/>
+    <row r="723" ht="14.25" customHeight="1"/>
+    <row r="724" ht="14.25" customHeight="1"/>
+    <row r="725" ht="14.25" customHeight="1"/>
+    <row r="726" ht="14.25" customHeight="1"/>
+    <row r="727" ht="14.25" customHeight="1"/>
+    <row r="728" ht="14.25" customHeight="1"/>
+    <row r="729" ht="14.25" customHeight="1"/>
+    <row r="730" ht="14.25" customHeight="1"/>
+    <row r="731" ht="14.25" customHeight="1"/>
+    <row r="732" ht="14.25" customHeight="1"/>
+    <row r="733" ht="14.25" customHeight="1"/>
+    <row r="734" ht="14.25" customHeight="1"/>
+    <row r="735" ht="14.25" customHeight="1"/>
+    <row r="736" ht="14.25" customHeight="1"/>
+    <row r="737" ht="14.25" customHeight="1"/>
+    <row r="738" ht="14.25" customHeight="1"/>
+    <row r="739" ht="14.25" customHeight="1"/>
+    <row r="740" ht="14.25" customHeight="1"/>
+    <row r="741" ht="14.25" customHeight="1"/>
+    <row r="742" ht="14.25" customHeight="1"/>
+    <row r="743" ht="14.25" customHeight="1"/>
+    <row r="744" ht="14.25" customHeight="1"/>
+    <row r="745" ht="14.25" customHeight="1"/>
+    <row r="746" ht="14.25" customHeight="1"/>
+    <row r="747" ht="14.25" customHeight="1"/>
+    <row r="748" ht="14.25" customHeight="1"/>
+    <row r="749" ht="14.25" customHeight="1"/>
+    <row r="750" ht="14.25" customHeight="1"/>
+    <row r="751" ht="14.25" customHeight="1"/>
+    <row r="752" ht="14.25" customHeight="1"/>
+    <row r="753" ht="14.25" customHeight="1"/>
+    <row r="754" ht="14.25" customHeight="1"/>
+    <row r="755" ht="14.25" customHeight="1"/>
+    <row r="756" ht="14.25" customHeight="1"/>
+    <row r="757" ht="14.25" customHeight="1"/>
+    <row r="758" ht="14.25" customHeight="1"/>
+    <row r="759" ht="14.25" customHeight="1"/>
+    <row r="760" ht="14.25" customHeight="1"/>
+    <row r="761" ht="14.25" customHeight="1"/>
+    <row r="762" ht="14.25" customHeight="1"/>
+    <row r="763" ht="14.25" customHeight="1"/>
+    <row r="764" ht="14.25" customHeight="1"/>
+    <row r="765" ht="14.25" customHeight="1"/>
+    <row r="766" ht="14.25" customHeight="1"/>
+    <row r="767" ht="14.25" customHeight="1"/>
+    <row r="768" ht="14.25" customHeight="1"/>
+    <row r="769" ht="14.25" customHeight="1"/>
+    <row r="770" ht="14.25" customHeight="1"/>
+    <row r="771" ht="14.25" customHeight="1"/>
+    <row r="772" ht="14.25" customHeight="1"/>
+    <row r="773" ht="14.25" customHeight="1"/>
+    <row r="774" ht="14.25" customHeight="1"/>
+    <row r="775" ht="14.25" customHeight="1"/>
+    <row r="776" ht="14.25" customHeight="1"/>
+    <row r="777" ht="14.25" customHeight="1"/>
+    <row r="778" ht="14.25" customHeight="1"/>
+    <row r="779" ht="14.25" customHeight="1"/>
+    <row r="780" ht="14.25" customHeight="1"/>
+    <row r="781" ht="14.25" customHeight="1"/>
+    <row r="782" ht="14.25" customHeight="1"/>
+    <row r="783" ht="14.25" customHeight="1"/>
+    <row r="784" ht="14.25" customHeight="1"/>
+    <row r="785" ht="14.25" customHeight="1"/>
+    <row r="786" ht="14.25" customHeight="1"/>
+    <row r="787" ht="14.25" customHeight="1"/>
+    <row r="788" ht="14.25" customHeight="1"/>
+    <row r="789" ht="14.25" customHeight="1"/>
+    <row r="790" ht="14.25" customHeight="1"/>
+    <row r="791" ht="14.25" customHeight="1"/>
+    <row r="792" ht="14.25" customHeight="1"/>
+    <row r="793" ht="14.25" customHeight="1"/>
+    <row r="794" ht="14.25" customHeight="1"/>
+    <row r="795" ht="14.25" customHeight="1"/>
+    <row r="796" ht="14.25" customHeight="1"/>
+    <row r="797" ht="14.25" customHeight="1"/>
+    <row r="798" ht="14.25" customHeight="1"/>
+    <row r="799" ht="14.25" customHeight="1"/>
+    <row r="800" ht="14.25" customHeight="1"/>
+    <row r="801" ht="14.25" customHeight="1"/>
+    <row r="802" ht="14.25" customHeight="1"/>
+    <row r="803" ht="14.25" customHeight="1"/>
+    <row r="804" ht="14.25" customHeight="1"/>
+    <row r="805" ht="14.25" customHeight="1"/>
+    <row r="806" ht="14.25" customHeight="1"/>
+    <row r="807" ht="14.25" customHeight="1"/>
+    <row r="808" ht="14.25" customHeight="1"/>
+    <row r="809" ht="14.25" customHeight="1"/>
+    <row r="810" ht="14.25" customHeight="1"/>
+    <row r="811" ht="14.25" customHeight="1"/>
+    <row r="812" ht="14.25" customHeight="1"/>
+    <row r="813" ht="14.25" customHeight="1"/>
+    <row r="814" ht="14.25" customHeight="1"/>
+    <row r="815" ht="14.25" customHeight="1"/>
+    <row r="816" ht="14.25" customHeight="1"/>
+    <row r="817" ht="14.25" customHeight="1"/>
+    <row r="818" ht="14.25" customHeight="1"/>
+    <row r="819" ht="14.25" customHeight="1"/>
+    <row r="820" ht="14.25" customHeight="1"/>
+    <row r="821" ht="14.25" customHeight="1"/>
+    <row r="822" ht="14.25" customHeight="1"/>
+    <row r="823" ht="14.25" customHeight="1"/>
+    <row r="824" ht="14.25" customHeight="1"/>
+    <row r="825" ht="14.25" customHeight="1"/>
+    <row r="826" ht="14.25" customHeight="1"/>
+    <row r="827" ht="14.25" customHeight="1"/>
+    <row r="828" ht="14.25" customHeight="1"/>
+    <row r="829" ht="14.25" customHeight="1"/>
+    <row r="830" ht="14.25" customHeight="1"/>
+    <row r="831" ht="14.25" customHeight="1"/>
+    <row r="832" ht="14.25" customHeight="1"/>
+    <row r="833" ht="14.25" customHeight="1"/>
+    <row r="834" ht="14.25" customHeight="1"/>
+    <row r="835" ht="14.25" customHeight="1"/>
+    <row r="836" ht="14.25" customHeight="1"/>
+    <row r="837" ht="14.25" customHeight="1"/>
+    <row r="838" ht="14.25" customHeight="1"/>
+    <row r="839" ht="14.25" customHeight="1"/>
+    <row r="840" ht="14.25" customHeight="1"/>
+    <row r="841" ht="14.25" customHeight="1"/>
+    <row r="842" ht="14.25" customHeight="1"/>
+    <row r="843" ht="14.25" customHeight="1"/>
+    <row r="844" ht="14.25" customHeight="1"/>
+    <row r="845" ht="14.25" customHeight="1"/>
+    <row r="846" ht="14.25" customHeight="1"/>
+    <row r="847" ht="14.25" customHeight="1"/>
+    <row r="848" ht="14.25" customHeight="1"/>
+    <row r="849" ht="14.25" customHeight="1"/>
+    <row r="850" ht="14.25" customHeight="1"/>
+    <row r="851" ht="14.25" customHeight="1"/>
+    <row r="852" ht="14.25" customHeight="1"/>
+    <row r="853" ht="14.25" customHeight="1"/>
+    <row r="854" ht="14.25" customHeight="1"/>
+    <row r="855" ht="14.25" customHeight="1"/>
+    <row r="856" ht="14.25" customHeight="1"/>
+    <row r="857" ht="14.25" customHeight="1"/>
+    <row r="858" ht="14.25" customHeight="1"/>
+    <row r="859" ht="14.25" customHeight="1"/>
+    <row r="860" ht="14.25" customHeight="1"/>
+    <row r="861" ht="14.25" customHeight="1"/>
+    <row r="862" ht="14.25" customHeight="1"/>
+    <row r="863" ht="14.25" customHeight="1"/>
+    <row r="864" ht="14.25" customHeight="1"/>
+    <row r="865" ht="14.25" customHeight="1"/>
+    <row r="866" ht="14.25" customHeight="1"/>
+    <row r="867" ht="14.25" customHeight="1"/>
+    <row r="868" ht="14.25" customHeight="1"/>
+    <row r="869" ht="14.25" customHeight="1"/>
+    <row r="870" ht="14.25" customHeight="1"/>
+    <row r="871" ht="14.25" customHeight="1"/>
+    <row r="872" ht="14.25" customHeight="1"/>
+    <row r="873" ht="14.25" customHeight="1"/>
+    <row r="874" ht="14.25" customHeight="1"/>
+    <row r="875" ht="14.25" customHeight="1"/>
+    <row r="876" ht="14.25" customHeight="1"/>
+    <row r="877" ht="14.25" customHeight="1"/>
+    <row r="878" ht="14.25" customHeight="1"/>
+    <row r="879" ht="14.25" customHeight="1"/>
+    <row r="880" ht="14.25" customHeight="1"/>
+    <row r="881" ht="14.25" customHeight="1"/>
+    <row r="882" ht="14.25" customHeight="1"/>
+    <row r="883" ht="14.25" customHeight="1"/>
+    <row r="884" ht="14.25" customHeight="1"/>
+    <row r="885" ht="14.25" customHeight="1"/>
+    <row r="886" ht="14.25" customHeight="1"/>
+    <row r="887" ht="14.25" customHeight="1"/>
+    <row r="888" ht="14.25" customHeight="1"/>
+    <row r="889" ht="14.25" customHeight="1"/>
+    <row r="890" ht="14.25" customHeight="1"/>
+    <row r="891" ht="14.25" customHeight="1"/>
+    <row r="892" ht="14.25" customHeight="1"/>
+    <row r="893" ht="14.25" customHeight="1"/>
+    <row r="894" ht="14.25" customHeight="1"/>
+    <row r="895" ht="14.25" customHeight="1"/>
+    <row r="896" ht="14.25" customHeight="1"/>
+    <row r="897" ht="14.25" customHeight="1"/>
+    <row r="898" ht="14.25" customHeight="1"/>
+    <row r="899" ht="14.25" customHeight="1"/>
+    <row r="900" ht="14.25" customHeight="1"/>
+    <row r="901" ht="14.25" customHeight="1"/>
+    <row r="902" ht="14.25" customHeight="1"/>
+    <row r="903" ht="14.25" customHeight="1"/>
+    <row r="904" ht="14.25" customHeight="1"/>
+    <row r="905" ht="14.25" customHeight="1"/>
+    <row r="906" ht="14.25" customHeight="1"/>
+    <row r="907" ht="14.25" customHeight="1"/>
+    <row r="908" ht="14.25" customHeight="1"/>
+    <row r="909" ht="14.25" customHeight="1"/>
+    <row r="910" ht="14.25" customHeight="1"/>
+    <row r="911" ht="14.25" customHeight="1"/>
+    <row r="912" ht="14.25" customHeight="1"/>
+    <row r="913" ht="14.25" customHeight="1"/>
+    <row r="914" ht="14.25" customHeight="1"/>
+    <row r="915" ht="14.25" customHeight="1"/>
+    <row r="916" ht="14.25" customHeight="1"/>
+    <row r="917" ht="14.25" customHeight="1"/>
+    <row r="918" ht="14.25" customHeight="1"/>
+    <row r="919" ht="14.25" customHeight="1"/>
+    <row r="920" ht="14.25" customHeight="1"/>
+    <row r="921" ht="14.25" customHeight="1"/>
+    <row r="922" ht="14.25" customHeight="1"/>
+    <row r="923" ht="14.25" customHeight="1"/>
+    <row r="924" ht="14.25" customHeight="1"/>
+    <row r="925" ht="14.25" customHeight="1"/>
+    <row r="926" ht="14.25" customHeight="1"/>
+    <row r="927" ht="14.25" customHeight="1"/>
+    <row r="928" ht="14.25" customHeight="1"/>
+    <row r="929" ht="14.25" customHeight="1"/>
+    <row r="930" ht="14.25" customHeight="1"/>
+    <row r="931" ht="14.25" customHeight="1"/>
+    <row r="932" ht="14.25" customHeight="1"/>
+    <row r="933" ht="14.25" customHeight="1"/>
+    <row r="934" ht="14.25" customHeight="1"/>
+    <row r="935" ht="14.25" customHeight="1"/>
+    <row r="936" ht="14.25" customHeight="1"/>
+    <row r="937" ht="14.25" customHeight="1"/>
+    <row r="938" ht="14.25" customHeight="1"/>
+    <row r="939" ht="14.25" customHeight="1"/>
+    <row r="940" ht="14.25" customHeight="1"/>
+    <row r="941" ht="14.25" customHeight="1"/>
+    <row r="942" ht="14.25" customHeight="1"/>
+    <row r="943" ht="14.25" customHeight="1"/>
+    <row r="944" ht="14.25" customHeight="1"/>
+    <row r="945" ht="14.25" customHeight="1"/>
+    <row r="946" ht="14.25" customHeight="1"/>
+    <row r="947" ht="14.25" customHeight="1"/>
+    <row r="948" ht="14.25" customHeight="1"/>
+    <row r="949" ht="14.25" customHeight="1"/>
+    <row r="950" ht="14.25" customHeight="1"/>
+    <row r="951" ht="14.25" customHeight="1"/>
+    <row r="952" ht="14.25" customHeight="1"/>
+    <row r="953" ht="14.25" customHeight="1"/>
+    <row r="954" ht="14.25" customHeight="1"/>
+    <row r="955" ht="14.25" customHeight="1"/>
+    <row r="956" ht="14.25" customHeight="1"/>
+    <row r="957" ht="14.25" customHeight="1"/>
+    <row r="958" ht="14.25" customHeight="1"/>
+    <row r="959" ht="14.25" customHeight="1"/>
+    <row r="960" ht="14.25" customHeight="1"/>
+    <row r="961" ht="14.25" customHeight="1"/>
+    <row r="962" ht="14.25" customHeight="1"/>
+    <row r="963" ht="14.25" customHeight="1"/>
+    <row r="964" ht="14.25" customHeight="1"/>
+    <row r="965" ht="14.25" customHeight="1"/>
+    <row r="966" ht="14.25" customHeight="1"/>
+    <row r="967" ht="14.25" customHeight="1"/>
+    <row r="968" ht="14.25" customHeight="1"/>
+    <row r="969" ht="14.25" customHeight="1"/>
+    <row r="970" ht="14.25" customHeight="1"/>
+    <row r="971" ht="14.25" customHeight="1"/>
+    <row r="972" ht="14.25" customHeight="1"/>
+    <row r="973" ht="14.25" customHeight="1"/>
+    <row r="974" ht="14.25" customHeight="1"/>
+    <row r="975" ht="14.25" customHeight="1"/>
+    <row r="976" ht="14.25" customHeight="1"/>
+    <row r="977" ht="14.25" customHeight="1"/>
+    <row r="978" ht="14.25" customHeight="1"/>
+    <row r="979" ht="14.25" customHeight="1"/>
+    <row r="980" ht="14.25" customHeight="1"/>
+    <row r="981" ht="14.25" customHeight="1"/>
+    <row r="982" ht="14.25" customHeight="1"/>
+    <row r="983" ht="14.25" customHeight="1"/>
+    <row r="984" ht="14.25" customHeight="1"/>
+    <row r="985" ht="14.25" customHeight="1"/>
+    <row r="986" ht="14.25" customHeight="1"/>
+    <row r="987" ht="14.25" customHeight="1"/>
+    <row r="988" ht="14.25" customHeight="1"/>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42.875" customWidth="1" min="1" max="1"/>
+    <col width="10.125" customWidth="1" min="2" max="2"/>
+    <col width="11.125" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>Chỉ tiêu</t>
         </is>
       </c>
-      <c r="B3" s="9">
-        <f>'balance_sheet'!B1</f>
-        <v/>
-      </c>
-      <c r="C3" s="9">
-        <f>'balance_sheet'!C1</f>
-        <v/>
-      </c>
-      <c r="D3" s="9">
-        <f>'balance_sheet'!D1</f>
-        <v/>
-      </c>
-      <c r="E3" s="9">
-        <f>'balance_sheet'!E1</f>
-        <v/>
-      </c>
-      <c r="F3" s="9">
-        <f>'balance_sheet'!F1</f>
-        <v/>
-      </c>
-      <c r="G3" s="9">
-        <f>'balance_sheet'!G1</f>
-        <v/>
-      </c>
-      <c r="H3" s="9">
-        <f>'balance_sheet'!H1</f>
-        <v/>
-      </c>
-      <c r="I3" s="9">
-        <f>'balance_sheet'!I1</f>
-        <v/>
-      </c>
+      <c r="B1" s="30" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C1" s="30" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="30" t="inlineStr">
+        <is>
+          <t>Doanh thu kế hoạch</t>
+        </is>
+      </c>
+      <c r="B2" s="31" t="n">
+        <v>9323</v>
+      </c>
+      <c r="C2" s="31" t="n">
+        <v>13227</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="30" t="inlineStr">
+        <is>
+          <t>Doanh thu thuần về bán hàng và cung cấp dịch vụ</t>
+        </is>
+      </c>
+      <c r="B3" s="31" t="n">
+        <v>11217.42651465</v>
+      </c>
+      <c r="C3" s="31" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
-        <is>
-          <t>1. Khả năng sinh lời</t>
-        </is>
-      </c>
+      <c r="A4" s="30" t="inlineStr">
+        <is>
+          <t>%thực hiện</t>
+        </is>
+      </c>
+      <c r="B4" s="38">
+        <f>B3/B2</f>
+        <v/>
+      </c>
+      <c r="C4" s="38" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
-        <is>
-          <t>ROE (LNST CĐ Cty mẹ / VCSH bình quân)</t>
-        </is>
-      </c>
-      <c r="B5" s="12" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C5" s="13">
-        <f>IFERROR(C$47/((C$32+B$32)/2),"n/a")</f>
-        <v/>
-      </c>
-      <c r="D5" s="13">
-        <f>IFERROR(D$47/((D$32+C$32)/2),"n/a")</f>
-        <v/>
-      </c>
-      <c r="E5" s="13">
-        <f>IFERROR(E$47/((E$32+D$32)/2),"n/a")</f>
-        <v/>
-      </c>
-      <c r="F5" s="13">
-        <f>IFERROR(F$47/((F$32+E$32)/2),"n/a")</f>
-        <v/>
-      </c>
-      <c r="G5" s="13">
-        <f>IFERROR(G$47/((G$32+F$32)/2),"n/a")</f>
-        <v/>
-      </c>
-      <c r="H5" s="13">
-        <f>IFERROR(H$47/((H$32+G$32)/2),"n/a")</f>
-        <v/>
-      </c>
-      <c r="I5" s="13">
-        <f>IFERROR(I$47/((I$32+H$32)/2),"n/a")</f>
-        <v/>
+      <c r="A5" s="30" t="inlineStr">
+        <is>
+          <t>Lợi nhuận trước thuế kế hoạch</t>
+        </is>
+      </c>
+      <c r="B5" s="31" t="n">
+        <v>5765</v>
+      </c>
+      <c r="C5" s="31" t="n">
+        <v>7535</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
-        <is>
-          <t>ROA (LNST / Tổng tài sản bình quân)</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C6" s="13">
-        <f>IFERROR(C$46/((C$33+B$33)/2),"n/a")</f>
-        <v/>
-      </c>
-      <c r="D6" s="13">
-        <f>IFERROR(D$46/((D$33+C$33)/2),"n/a")</f>
-        <v/>
-      </c>
-      <c r="E6" s="13">
-        <f>IFERROR(E$46/((E$33+D$33)/2),"n/a")</f>
-        <v/>
-      </c>
-      <c r="F6" s="13">
-        <f>IFERROR(F$46/((F$33+E$33)/2),"n/a")</f>
-        <v/>
-      </c>
-      <c r="G6" s="13">
-        <f>IFERROR(G$46/((G$33+F$33)/2),"n/a")</f>
-        <v/>
-      </c>
-      <c r="H6" s="13">
-        <f>IFERROR(H$46/((H$33+G$33)/2),"n/a")</f>
-        <v/>
-      </c>
-      <c r="I6" s="13">
-        <f>IFERROR(I$46/((I$33+H$33)/2),"n/a")</f>
-        <v/>
-      </c>
+      <c r="A6" s="30" t="inlineStr">
+        <is>
+          <t>Lợi nhuận trước thuế thu nhập doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="B6" s="31" t="n">
+        <v>7109</v>
+      </c>
+      <c r="C6" s="31" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>Tăng trưởng LN Cổ đông Cty mẹ</t>
-        </is>
-      </c>
-      <c r="B7" s="12" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C7" s="13">
-        <f>IFERROR((C$47-B$47)/ABS(B$47),"n/a")</f>
-        <v/>
-      </c>
-      <c r="D7" s="13">
-        <f>IFERROR((D$47-C$47)/ABS(C$47),"n/a")</f>
-        <v/>
-      </c>
-      <c r="E7" s="13">
-        <f>IFERROR((E$47-D$47)/ABS(D$47),"n/a")</f>
-        <v/>
-      </c>
-      <c r="F7" s="13">
-        <f>IFERROR((F$47-E$47)/ABS(E$47),"n/a")</f>
-        <v/>
-      </c>
-      <c r="G7" s="13">
-        <f>IFERROR((G$47-F$47)/ABS(F$47),"n/a")</f>
-        <v/>
-      </c>
-      <c r="H7" s="13">
-        <f>IFERROR((H$47-G$47)/ABS(G$47),"n/a")</f>
-        <v/>
-      </c>
-      <c r="I7" s="13">
-        <f>IFERROR((I$47-H$47)/ABS(H$47),"n/a")</f>
-        <v/>
-      </c>
+      <c r="A7" s="30" t="inlineStr">
+        <is>
+          <t>%thực hiện</t>
+        </is>
+      </c>
+      <c r="B7" s="38">
+        <f>B6/B5</f>
+        <v/>
+      </c>
+      <c r="C7" s="38" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="inlineStr">
-        <is>
-          <t>Tăng trưởng Doanh thu thuần</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C8" s="13">
-        <f>IFERROR((C$39-B$39)/ABS(B$39),"n/a")</f>
-        <v/>
-      </c>
-      <c r="D8" s="13">
-        <f>IFERROR((D$39-C$39)/ABS(C$39),"n/a")</f>
-        <v/>
-      </c>
-      <c r="E8" s="13">
-        <f>IFERROR((E$39-D$39)/ABS(D$39),"n/a")</f>
-        <v/>
-      </c>
-      <c r="F8" s="13">
-        <f>IFERROR((F$39-E$39)/ABS(E$39),"n/a")</f>
-        <v/>
-      </c>
-      <c r="G8" s="13">
-        <f>IFERROR((G$39-F$39)/ABS(F$39),"n/a")</f>
-        <v/>
-      </c>
-      <c r="H8" s="13">
-        <f>IFERROR((H$39-G$39)/ABS(G$39),"n/a")</f>
-        <v/>
-      </c>
-      <c r="I8" s="13">
-        <f>IFERROR((I$39-H$39)/ABS(H$39),"n/a")</f>
-        <v/>
-      </c>
+      <c r="A8" s="39" t="n"/>
+      <c r="B8" s="39" t="n"/>
+      <c r="C8" s="39" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>2. Biên lợi nhuận</t>
-        </is>
-      </c>
+      <c r="A9" s="30" t="inlineStr">
+        <is>
+          <t>Trung vị %thực hiện DT</t>
+        </is>
+      </c>
+      <c r="B9" s="38">
+        <f>MEDIAN(B4:C4)</f>
+        <v/>
+      </c>
+      <c r="C9" s="39" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
-        <is>
-          <t>Biên lợi nhuận gộp</t>
-        </is>
-      </c>
-      <c r="B10" s="13">
-        <f>IFERROR(B$41/B$39,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C10" s="13">
-        <f>IFERROR(C$41/C$39,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D10" s="13">
-        <f>IFERROR(D$41/D$39,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E10" s="13">
-        <f>IFERROR(E$41/E$39,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F10" s="13">
-        <f>IFERROR(F$41/F$39,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G10" s="13">
-        <f>IFERROR(G$41/G$39,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H10" s="13">
-        <f>IFERROR(H$41/H$39,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I10" s="13">
-        <f>IFERROR(I$41/I$39,"n/a")</f>
-        <v/>
-      </c>
+      <c r="A10" s="30" t="inlineStr">
+        <is>
+          <t>Trung vị %thực hiện LNST</t>
+        </is>
+      </c>
+      <c r="B10" s="38">
+        <f>MEDIAN(B7:C7)</f>
+        <v/>
+      </c>
+      <c r="C10" s="39" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>Biên lợi nhuận ròng</t>
-        </is>
-      </c>
-      <c r="B11" s="13">
-        <f>IFERROR(B$46/B$39,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C11" s="13">
-        <f>IFERROR(C$46/C$39,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D11" s="13">
-        <f>IFERROR(D$46/D$39,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E11" s="13">
-        <f>IFERROR(E$46/E$39,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F11" s="13">
-        <f>IFERROR(F$46/F$39,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G11" s="13">
-        <f>IFERROR(G$46/G$39,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H11" s="13">
-        <f>IFERROR(H$46/H$39,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I11" s="13">
-        <f>IFERROR(I$46/I$39,"n/a")</f>
-        <v/>
-      </c>
+      <c r="A11" s="39" t="n"/>
+      <c r="B11" s="39" t="n"/>
+      <c r="C11" s="39" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr">
-        <is>
-          <t>3. Đòn bẩy tài chính</t>
-        </is>
-      </c>
+      <c r="A12" s="30" t="inlineStr">
+        <is>
+          <t>Tỷ lệ hoàn thành DT trên 95%</t>
+        </is>
+      </c>
+      <c r="B12" s="38">
+        <f>COUNTIF(B4:C4,"&gt;=95%")/COUNT(B4:C4)</f>
+        <v/>
+      </c>
+      <c r="C12" s="39" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>D/E (Nợ vay / Vốn chủ sở hữu)</t>
-        </is>
-      </c>
-      <c r="B13" s="14">
-        <f>IFERROR((B$37+B$38)/B$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C13" s="14">
-        <f>IFERROR((C$37+C$38)/C$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D13" s="14">
-        <f>IFERROR((D$37+D$38)/D$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E13" s="14">
-        <f>IFERROR((E$37+E$38)/E$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F13" s="14">
-        <f>IFERROR((F$37+F$38)/F$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G13" s="14">
-        <f>IFERROR((G$37+G$38)/G$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H13" s="14">
-        <f>IFERROR((H$37+H$38)/H$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I13" s="14">
-        <f>IFERROR((I$37+I$38)/I$32,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     - Nợ vay dài hạn/Vốn chủ sở hữu</t>
-        </is>
-      </c>
-      <c r="B14" s="14">
-        <f>IFERROR(B$38/B$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C14" s="14">
-        <f>IFERROR(C$38/C$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D14" s="14">
-        <f>IFERROR(D$38/D$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E14" s="14">
-        <f>IFERROR(E$38/E$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F14" s="14">
-        <f>IFERROR(F$38/F$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G14" s="14">
-        <f>IFERROR(G$38/G$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H14" s="14">
-        <f>IFERROR(H$38/H$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I14" s="14">
-        <f>IFERROR(I$38/I$32,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     - Nợ vay ngắn hạn/Vốn chủ sở hữu</t>
-        </is>
-      </c>
-      <c r="B15" s="14">
-        <f>IFERROR(B$37/B$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C15" s="14">
-        <f>IFERROR(C$37/C$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D15" s="14">
-        <f>IFERROR(D$37/D$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E15" s="14">
-        <f>IFERROR(E$37/E$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F15" s="14">
-        <f>IFERROR(F$37/F$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G15" s="14">
-        <f>IFERROR(G$37/G$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H15" s="14">
-        <f>IFERROR(H$37/H$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I15" s="14">
-        <f>IFERROR(I$37/I$32,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="11" t="inlineStr">
-        <is>
-          <t>Nợ phải trả/Vốn chủ sở hữu</t>
-        </is>
-      </c>
-      <c r="B16" s="14">
-        <f>IFERROR(B$34/B$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C16" s="14">
-        <f>IFERROR(C$34/C$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D16" s="14">
-        <f>IFERROR(D$34/D$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E16" s="14">
-        <f>IFERROR(E$34/E$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F16" s="14">
-        <f>IFERROR(F$34/F$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G16" s="14">
-        <f>IFERROR(G$34/G$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H16" s="14">
-        <f>IFERROR(H$34/H$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I16" s="14">
-        <f>IFERROR(I$34/I$32,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     - Nợ dài hạn/Vốn chủ sở hữu</t>
-        </is>
-      </c>
-      <c r="B17" s="14">
-        <f>IFERROR(B$36/B$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C17" s="14">
-        <f>IFERROR(C$36/C$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D17" s="14">
-        <f>IFERROR(D$36/D$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E17" s="14">
-        <f>IFERROR(E$36/E$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F17" s="14">
-        <f>IFERROR(F$36/F$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G17" s="14">
-        <f>IFERROR(G$36/G$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H17" s="14">
-        <f>IFERROR(H$36/H$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I17" s="14">
-        <f>IFERROR(I$36/I$32,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     - Nợ ngắn hạn/Vốn chủ sở hữu</t>
-        </is>
-      </c>
-      <c r="B18" s="14">
-        <f>IFERROR(B$35/B$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C18" s="14">
-        <f>IFERROR(C$35/C$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D18" s="14">
-        <f>IFERROR(D$35/D$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E18" s="14">
-        <f>IFERROR(E$35/E$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F18" s="14">
-        <f>IFERROR(F$35/F$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G18" s="14">
-        <f>IFERROR(G$35/G$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H18" s="14">
-        <f>IFERROR(H$35/H$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I18" s="14">
-        <f>IFERROR(I$35/I$32,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>4. Chi phí &amp; khả năng trả lãi</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="11" t="inlineStr">
-        <is>
-          <t>Chi phí bán hàng, quản lý/LN gộp</t>
-        </is>
-      </c>
-      <c r="B20" s="13">
-        <f>IFERROR((ABS(B$42)+ABS(B$43))/B$41,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C20" s="13">
-        <f>IFERROR((ABS(C$42)+ABS(C$43))/C$41,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D20" s="13">
-        <f>IFERROR((ABS(D$42)+ABS(D$43))/D$41,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E20" s="13">
-        <f>IFERROR((ABS(E$42)+ABS(E$43))/E$41,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F20" s="13">
-        <f>IFERROR((ABS(F$42)+ABS(F$43))/F$41,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G20" s="13">
-        <f>IFERROR((ABS(G$42)+ABS(G$43))/G$41,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H20" s="13">
-        <f>IFERROR((ABS(H$42)+ABS(H$43))/H$41,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I20" s="13">
-        <f>IFERROR((ABS(I$42)+ABS(I$43))/I$41,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="11" t="inlineStr">
-        <is>
-          <t>Chi phí lãi vay/LN từ hoạt động kinh doanh</t>
-        </is>
-      </c>
-      <c r="B21" s="13">
-        <f>IFERROR(ABS(B$45)/B$44,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C21" s="13">
-        <f>IFERROR(ABS(C$45)/C$44,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D21" s="13">
-        <f>IFERROR(ABS(D$45)/D$44,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E21" s="13">
-        <f>IFERROR(ABS(E$45)/E$44,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F21" s="13">
-        <f>IFERROR(ABS(F$45)/F$44,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G21" s="13">
-        <f>IFERROR(ABS(G$45)/G$44,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H21" s="13">
-        <f>IFERROR(ABS(H$45)/H$44,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I21" s="13">
-        <f>IFERROR(ABS(I$45)/I$44,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t>5. Chu kỳ hoạt động vốn lưu động</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="11" t="inlineStr">
-        <is>
-          <t>Số ngày phải trả (DPO)</t>
-        </is>
-      </c>
-      <c r="B23" s="12" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C23" s="15">
-        <f>IFERROR(((C$49+B$49)/2)/ABS(C$40)*365,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D23" s="15">
-        <f>IFERROR(((D$49+C$49)/2)/ABS(D$40)*365,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E23" s="15">
-        <f>IFERROR(((E$49+D$49)/2)/ABS(E$40)*365,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F23" s="15">
-        <f>IFERROR(((F$49+E$49)/2)/ABS(F$40)*365,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G23" s="15">
-        <f>IFERROR(((G$49+F$49)/2)/ABS(G$40)*365,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H23" s="15">
-        <f>IFERROR(((H$49+G$49)/2)/ABS(H$40)*365,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I23" s="15">
-        <f>IFERROR(((I$49+H$49)/2)/ABS(I$40)*365,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="11" t="inlineStr">
-        <is>
-          <t>Số ngày phải thu (DSO)</t>
-        </is>
-      </c>
-      <c r="B24" s="12" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C24" s="15">
-        <f>IFERROR(((C$48+B$48)/2)/C$39*365,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D24" s="15">
-        <f>IFERROR(((D$48+C$48)/2)/D$39*365,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E24" s="15">
-        <f>IFERROR(((E$48+D$48)/2)/E$39*365,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F24" s="15">
-        <f>IFERROR(((F$48+E$48)/2)/F$39*365,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G24" s="15">
-        <f>IFERROR(((G$48+F$48)/2)/G$39*365,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H24" s="15">
-        <f>IFERROR(((H$48+G$48)/2)/H$39*365,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I24" s="15">
-        <f>IFERROR(((I$48+H$48)/2)/I$39*365,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="11" t="inlineStr">
-        <is>
-          <t>Số ngày tồn kho (DIO)</t>
-        </is>
-      </c>
-      <c r="B25" s="12" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C25" s="15">
-        <f>IFERROR(((C$50+B$50)/2)/ABS(C$40)*365,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D25" s="15">
-        <f>IFERROR(((D$50+C$50)/2)/ABS(D$40)*365,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E25" s="15">
-        <f>IFERROR(((E$50+D$50)/2)/ABS(E$40)*365,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F25" s="15">
-        <f>IFERROR(((F$50+E$50)/2)/ABS(F$40)*365,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G25" s="15">
-        <f>IFERROR(((G$50+F$50)/2)/ABS(G$40)*365,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H25" s="15">
-        <f>IFERROR(((H$50+G$50)/2)/ABS(H$40)*365,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I25" s="15">
-        <f>IFERROR(((I$50+H$50)/2)/ABS(I$40)*365,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="10" t="inlineStr">
-        <is>
-          <t>6. Cơ cấu tài sản</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="11" t="inlineStr">
-        <is>
-          <t>Tiền và tương đương tiền/Tài sản</t>
-        </is>
-      </c>
-      <c r="B27" s="13">
-        <f>IFERROR(B$51/B$33,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C27" s="13">
-        <f>IFERROR(C$51/C$33,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D27" s="13">
-        <f>IFERROR(D$51/D$33,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E27" s="13">
-        <f>IFERROR(E$51/E$33,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F27" s="13">
-        <f>IFERROR(F$51/F$33,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G27" s="13">
-        <f>IFERROR(G$51/G$33,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H27" s="13">
-        <f>IFERROR(H$51/H$33,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I27" s="13">
-        <f>IFERROR(I$51/I$33,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="11" t="inlineStr">
-        <is>
-          <t>Hàng tồn kho/Tài sản</t>
-        </is>
-      </c>
-      <c r="B28" s="13">
-        <f>IFERROR(B$50/B$33,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C28" s="13">
-        <f>IFERROR(C$50/C$33,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D28" s="13">
-        <f>IFERROR(D$50/D$33,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E28" s="13">
-        <f>IFERROR(E$50/E$33,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F28" s="13">
-        <f>IFERROR(F$50/F$33,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G28" s="13">
-        <f>IFERROR(G$50/G$33,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H28" s="13">
-        <f>IFERROR(H$50/H$33,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I28" s="13">
-        <f>IFERROR(I$50/I$33,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>II. DỮ LIỆU TRÍCH XUẤT (tự động dò theo tên khoản mục)</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="n"/>
-      <c r="C30" s="7" t="n"/>
-      <c r="D30" s="7" t="n"/>
-      <c r="E30" s="7" t="n"/>
-      <c r="F30" s="7" t="n"/>
-      <c r="G30" s="7" t="n"/>
-      <c r="H30" s="7" t="n"/>
-      <c r="I30" s="7" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="8" t="inlineStr">
-        <is>
-          <t>Khoản mục</t>
-        </is>
-      </c>
-      <c r="B31" s="9">
-        <f>'balance_sheet'!B1</f>
-        <v/>
-      </c>
-      <c r="C31" s="9">
-        <f>'balance_sheet'!C1</f>
-        <v/>
-      </c>
-      <c r="D31" s="9">
-        <f>'balance_sheet'!D1</f>
-        <v/>
-      </c>
-      <c r="E31" s="9">
-        <f>'balance_sheet'!E1</f>
-        <v/>
-      </c>
-      <c r="F31" s="9">
-        <f>'balance_sheet'!F1</f>
-        <v/>
-      </c>
-      <c r="G31" s="9">
-        <f>'balance_sheet'!G1</f>
-        <v/>
-      </c>
-      <c r="H31" s="9">
-        <f>'balance_sheet'!H1</f>
-        <v/>
-      </c>
-      <c r="I31" s="9">
-        <f>'balance_sheet'!I1</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>Vốn chủ sở hữu</t>
-        </is>
-      </c>
-      <c r="B32" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C32" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D32" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E32" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F32" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G32" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H32" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I32" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>TỔNG CỘNG TÀI SẢN</t>
-        </is>
-      </c>
-      <c r="B33" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C33" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D33" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E33" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F33" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G33" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H33" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I33" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>NỢ PHẢI TRẢ</t>
-        </is>
-      </c>
-      <c r="B34" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C34" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D34" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E34" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F34" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G34" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H34" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I34" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>Nợ phải trả ngắn hạn</t>
-        </is>
-      </c>
-      <c r="B35" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả ngắn hạn",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C35" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả ngắn hạn",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D35" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả ngắn hạn",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E35" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả ngắn hạn",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F35" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả ngắn hạn",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G35" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả ngắn hạn",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H35" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả ngắn hạn",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I35" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả ngắn hạn",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>Nợ phải trả dài hạn</t>
-        </is>
-      </c>
-      <c r="B36" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả dài hạn",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C36" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả dài hạn",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D36" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả dài hạn",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E36" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả dài hạn",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F36" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả dài hạn",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G36" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả dài hạn",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H36" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả dài hạn",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I36" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả dài hạn",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>Vay ngắn hạn</t>
-        </is>
-      </c>
-      <c r="B37" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C37" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D37" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E37" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F37" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G37" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H37" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I37" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>Vay dài hạn</t>
-        </is>
-      </c>
-      <c r="B38" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C38" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D38" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E38" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F38" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G38" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H38" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I38" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>Doanh thu thuần về hoạt động kinh doanh</t>
-        </is>
-      </c>
-      <c r="B39" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần về hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C39" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần về hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D39" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần về hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E39" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần về hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F39" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần về hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G39" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần về hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H39" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần về hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I39" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần về hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>CHI PHÍ HOẠT ĐỘNG</t>
-        </is>
-      </c>
-      <c r="B40" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C40" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D40" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E40" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F40" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G40" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H40" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I40" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>LỢI NHUẬN GỘP</t>
-        </is>
-      </c>
-      <c r="B41" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN GỘP",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C41" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN GỘP",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D41" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN GỘP",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E41" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN GỘP",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F41" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN GỘP",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G41" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN GỘP",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H41" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN GỘP",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I41" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN GỘP",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>CHI PHÍ BÁN HÀNG</t>
-        </is>
-      </c>
-      <c r="B42" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ BÁN HÀNG",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C42" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ BÁN HÀNG",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D42" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ BÁN HÀNG",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E42" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ BÁN HÀNG",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F42" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ BÁN HÀNG",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G42" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ BÁN HÀNG",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H42" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ BÁN HÀNG",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I42" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ BÁN HÀNG",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>CHI PHÍ QUẢN LÝ CÔNG TY CHỨNG KHOÁN</t>
-        </is>
-      </c>
-      <c r="B43" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ QUẢN LÝ CÔNG TY CHỨNG KHOÁN",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C43" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ QUẢN LÝ CÔNG TY CHỨNG KHOÁN",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D43" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ QUẢN LÝ CÔNG TY CHỨNG KHOÁN",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E43" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ QUẢN LÝ CÔNG TY CHỨNG KHOÁN",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F43" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ QUẢN LÝ CÔNG TY CHỨNG KHOÁN",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G43" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ QUẢN LÝ CÔNG TY CHỨNG KHOÁN",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H43" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ QUẢN LÝ CÔNG TY CHỨNG KHOÁN",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I43" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ QUẢN LÝ CÔNG TY CHỨNG KHOÁN",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>KẾT QUẢ HOẠT ĐỘNG</t>
-        </is>
-      </c>
-      <c r="B44" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("KẾT QUẢ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C44" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("KẾT QUẢ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D44" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("KẾT QUẢ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E44" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("KẾT QUẢ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F44" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("KẾT QUẢ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G44" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("KẾT QUẢ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H44" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("KẾT QUẢ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I44" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("KẾT QUẢ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>Chi phí lãi vay</t>
-        </is>
-      </c>
-      <c r="B45" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C45" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D45" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E45" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F45" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G45" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H45" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I45" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>LỢI NHUẬN KẾ TOÁN SAU THUẾ</t>
-        </is>
-      </c>
-      <c r="B46" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN KẾ TOÁN SAU THUẾ",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C46" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN KẾ TOÁN SAU THUẾ",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D46" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN KẾ TOÁN SAU THUẾ",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E46" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN KẾ TOÁN SAU THUẾ",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F46" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN KẾ TOÁN SAU THUẾ",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G46" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN KẾ TOÁN SAU THUẾ",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H46" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN KẾ TOÁN SAU THUẾ",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I46" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN KẾ TOÁN SAU THUẾ",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>Lợi nhuận sau thuế phân bổ cho chủ sở hữu</t>
-        </is>
-      </c>
-      <c r="B47" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận sau thuế phân bổ cho chủ sở hữu",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C47" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận sau thuế phân bổ cho chủ sở hữu",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D47" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận sau thuế phân bổ cho chủ sở hữu",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E47" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận sau thuế phân bổ cho chủ sở hữu",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F47" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận sau thuế phân bổ cho chủ sở hữu",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G47" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận sau thuế phân bổ cho chủ sở hữu",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H47" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận sau thuế phân bổ cho chủ sở hữu",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I47" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận sau thuế phân bổ cho chủ sở hữu",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>Phải thu khách hàng</t>
-        </is>
-      </c>
-      <c r="B48" s="12" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C48" s="12" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="D48" s="12" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="E48" s="12" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="F48" s="12" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="G48" s="12" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="H48" s="12" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="I48" s="12" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>Phải trả người bán ngắn hạn</t>
-        </is>
-      </c>
-      <c r="B49" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán ngắn hạn",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C49" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán ngắn hạn",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D49" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán ngắn hạn",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E49" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán ngắn hạn",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F49" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán ngắn hạn",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G49" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán ngắn hạn",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H49" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán ngắn hạn",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I49" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán ngắn hạn",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t>Hàng tồn kho, ròng</t>
-        </is>
-      </c>
-      <c r="B50" s="12" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C50" s="12" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="D50" s="12" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="E50" s="12" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="F50" s="12" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="G50" s="12" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="H50" s="12" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="I50" s="12" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>Tiền và tương đương tiền</t>
-        </is>
-      </c>
-      <c r="B51" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C51" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D51" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E51" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F51" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G51" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H51" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I51" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
+      <c r="A13" s="30" t="inlineStr">
+        <is>
+          <t>Tỷ lệ hoàn thành LNST trên 95%</t>
+        </is>
+      </c>
+      <c r="B13" s="38">
+        <f>COUNTIF(B7:C7,"&gt;=95%")/COUNT(B7:C7)</f>
+        <v/>
+      </c>
+      <c r="C13" s="39" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:I1"/>
-  </mergeCells>
+  <conditionalFormatting sqref="B9:B10">
+    <cfRule type="cellIs" priority="4" operator="lessThanOrEqual" dxfId="0" stopIfTrue="1">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="5" operator="greaterThanOrEqual" dxfId="1" stopIfTrue="1">
+      <formula>0.95</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="6" operator="between" dxfId="2">
+      <formula>0.9</formula>
+      <formula>0.95</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B12:B13">
+    <cfRule type="cellIs" priority="2" operator="lessThan" dxfId="0">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="greaterThanOrEqual" dxfId="1">
+      <formula>0.8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B4:C4 B7:C7">
+    <cfRule type="cellIs" priority="7" operator="greaterThanOrEqual" dxfId="3">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/financials/TCX/TCX.xlsx
+++ b/financials/TCX/TCX.xlsx
@@ -1215,16 +1215,16 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>0</v>
+        <v>466100148</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0</v>
+        <v>903251937</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0</v>
+        <v>1159272837</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0</v>
+        <v>7421889829</v>
       </c>
       <c r="F18" s="4" t="n">
         <v>0</v>
@@ -1338,10 +1338,18 @@
           <t>Tài sản ngắn hạn khác</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr"/>
-      <c r="C22" s="4" t="inlineStr"/>
-      <c r="D22" s="4" t="inlineStr"/>
-      <c r="E22" s="4" t="inlineStr"/>
+      <c r="B22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="F22" s="4" t="n">
         <v>0</v>
       </c>
@@ -11165,7 +11173,7 @@
         <v>0</v>
       </c>
       <c r="C48" s="4" t="n">
-        <v>0</v>
+        <v>400000000000</v>
       </c>
       <c r="D48" s="4" t="n">
         <v>0</v>
@@ -11223,10 +11231,18 @@
           <t>Tiền gửi ngân hàng cho hoạt động CTCK</t>
         </is>
       </c>
-      <c r="B50" s="4" t="inlineStr"/>
-      <c r="C50" s="4" t="inlineStr"/>
-      <c r="D50" s="4" t="inlineStr"/>
-      <c r="E50" s="4" t="inlineStr"/>
+      <c r="B50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="F50" s="4" t="n">
         <v>0</v>
       </c>
@@ -11246,10 +11262,18 @@
           <t>Các khoản tương đương tiền</t>
         </is>
       </c>
-      <c r="B51" s="4" t="inlineStr"/>
-      <c r="C51" s="4" t="inlineStr"/>
-      <c r="D51" s="4" t="inlineStr"/>
-      <c r="E51" s="4" t="inlineStr"/>
+      <c r="B51" s="4" t="n">
+        <v>400000000000</v>
+      </c>
+      <c r="C51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="F51" s="4" t="n">
         <v>0</v>
       </c>
@@ -11269,10 +11293,18 @@
           <t>Ảnh hưởng của thay đổi tỷ giá hối đoái quy đổi ngoại tệ</t>
         </is>
       </c>
-      <c r="B52" s="4" t="inlineStr"/>
-      <c r="C52" s="4" t="inlineStr"/>
-      <c r="D52" s="4" t="inlineStr"/>
-      <c r="E52" s="4" t="inlineStr"/>
+      <c r="B52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="F52" s="4" t="n">
         <v>0</v>
       </c>
@@ -11851,16 +11883,16 @@
         </is>
       </c>
       <c r="B71" s="4" t="n">
+        <v>250301666222</v>
+      </c>
+      <c r="C71" s="4" t="n">
         <v>396892320865</v>
       </c>
-      <c r="C71" s="4" t="n">
+      <c r="D71" s="4" t="n">
         <v>447669875435</v>
       </c>
-      <c r="D71" s="4" t="n">
+      <c r="E71" s="4" t="n">
         <v>2218020327029</v>
-      </c>
-      <c r="E71" s="4" t="n">
-        <v>4575045031535</v>
       </c>
       <c r="F71" s="4" t="n">
         <v>2278125882711</v>
@@ -11975,16 +12007,16 @@
         </is>
       </c>
       <c r="B75" s="4" t="n">
-        <v>938077574583</v>
+        <v>0</v>
       </c>
       <c r="C75" s="4" t="n">
-        <v>2084430659</v>
+        <v>0</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>367528400</v>
+        <v>0</v>
       </c>
       <c r="E75" s="4" t="n">
-        <v>2052242343</v>
+        <v>0</v>
       </c>
       <c r="F75" s="4" t="n">
         <v>51919186748</v>
@@ -12005,10 +12037,18 @@
           <t>Trong đó: có kỳ hạn</t>
         </is>
       </c>
-      <c r="B76" s="4" t="inlineStr"/>
-      <c r="C76" s="4" t="inlineStr"/>
-      <c r="D76" s="4" t="inlineStr"/>
-      <c r="E76" s="4" t="inlineStr"/>
+      <c r="B76" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C76" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D76" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="F76" s="4" t="n">
         <v>0</v>
       </c>
@@ -12029,16 +12069,16 @@
         </is>
       </c>
       <c r="B77" s="4" t="n">
-        <v>0</v>
+        <v>1283833447510</v>
       </c>
       <c r="C77" s="4" t="n">
-        <v>0</v>
+        <v>938077574583</v>
       </c>
       <c r="D77" s="4" t="n">
-        <v>0</v>
+        <v>2084430659</v>
       </c>
       <c r="E77" s="4" t="n">
-        <v>0</v>
+        <v>367528400</v>
       </c>
       <c r="F77" s="4" t="n">
         <v>0</v>
@@ -12090,10 +12130,18 @@
           <t>Các khoản tương đương tiền</t>
         </is>
       </c>
-      <c r="B79" s="4" t="inlineStr"/>
-      <c r="C79" s="4" t="inlineStr"/>
-      <c r="D79" s="4" t="inlineStr"/>
-      <c r="E79" s="4" t="inlineStr"/>
+      <c r="B79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="F79" s="4" t="n">
         <v>0</v>
       </c>
@@ -12113,10 +12161,18 @@
           <t>Ảnh hưởng của thay đổi tỷ giá hối đoái quy đổi ngoại tệ</t>
         </is>
       </c>
-      <c r="B80" s="4" t="inlineStr"/>
-      <c r="C80" s="4" t="inlineStr"/>
-      <c r="D80" s="4" t="inlineStr"/>
-      <c r="E80" s="4" t="inlineStr"/>
+      <c r="B80" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C80" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D80" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="F80" s="4" t="n">
         <v>0</v>
       </c>
@@ -12198,10 +12254,18 @@
           <t>Tiền gửi của NĐT về GDCK theo phương thức CTCK quản lý</t>
         </is>
       </c>
-      <c r="B83" s="4" t="inlineStr"/>
-      <c r="C83" s="4" t="inlineStr"/>
-      <c r="D83" s="4" t="inlineStr"/>
-      <c r="E83" s="4" t="inlineStr"/>
+      <c r="B83" s="4" t="n">
+        <v>396892320865</v>
+      </c>
+      <c r="C83" s="4" t="n">
+        <v>447669875435</v>
+      </c>
+      <c r="D83" s="4" t="n">
+        <v>2218020327029</v>
+      </c>
+      <c r="E83" s="4" t="n">
+        <v>4575045031535</v>
+      </c>
       <c r="F83" s="4" t="n">
         <v>2278125882711</v>
       </c>
@@ -12221,10 +12285,18 @@
           <t>Trong đó: có kỳ hạn</t>
         </is>
       </c>
-      <c r="B84" s="4" t="inlineStr"/>
-      <c r="C84" s="4" t="inlineStr"/>
-      <c r="D84" s="4" t="inlineStr"/>
-      <c r="E84" s="4" t="inlineStr"/>
+      <c r="B84" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C84" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D84" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="F84" s="4" t="n">
         <v>0</v>
       </c>
@@ -12244,10 +12316,18 @@
           <t>Tiền gửi của NĐT về GDCK theo phương thức NHTM quản lý (Trước năm 2016)</t>
         </is>
       </c>
-      <c r="B85" s="4" t="inlineStr"/>
-      <c r="C85" s="4" t="inlineStr"/>
-      <c r="D85" s="4" t="inlineStr"/>
-      <c r="E85" s="4" t="inlineStr"/>
+      <c r="B85" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C85" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="F85" s="4" t="n">
         <v>0</v>
       </c>
@@ -12267,10 +12347,18 @@
           <t>Trong đó: có kỳ hạn (Trước năm 2016)</t>
         </is>
       </c>
-      <c r="B86" s="4" t="inlineStr"/>
-      <c r="C86" s="4" t="inlineStr"/>
-      <c r="D86" s="4" t="inlineStr"/>
-      <c r="E86" s="4" t="inlineStr"/>
+      <c r="B86" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C86" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D86" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="F86" s="4" t="n">
         <v>0</v>
       </c>
@@ -12290,10 +12378,18 @@
           <t>Tiền gửi tổng hợp GDCK cho khách hàng</t>
         </is>
       </c>
-      <c r="B87" s="4" t="inlineStr"/>
-      <c r="C87" s="4" t="inlineStr"/>
-      <c r="D87" s="4" t="inlineStr"/>
-      <c r="E87" s="4" t="inlineStr"/>
+      <c r="B87" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C87" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D87" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="F87" s="4" t="n">
         <v>0</v>
       </c>
@@ -12313,10 +12409,18 @@
           <t>Tiền gửi bù trừ và thanh toán GDCK</t>
         </is>
       </c>
-      <c r="B88" s="4" t="inlineStr"/>
-      <c r="C88" s="4" t="inlineStr"/>
-      <c r="D88" s="4" t="inlineStr"/>
-      <c r="E88" s="4" t="inlineStr"/>
+      <c r="B88" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C88" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D88" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E88" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="F88" s="4" t="n">
         <v>0</v>
       </c>
@@ -12336,10 +12440,18 @@
           <t>Tiền gửi của tổ chức phát hành</t>
         </is>
       </c>
-      <c r="B89" s="4" t="inlineStr"/>
-      <c r="C89" s="4" t="inlineStr"/>
-      <c r="D89" s="4" t="inlineStr"/>
-      <c r="E89" s="4" t="inlineStr"/>
+      <c r="B89" s="4" t="n">
+        <v>938077574583</v>
+      </c>
+      <c r="C89" s="4" t="n">
+        <v>2084430659</v>
+      </c>
+      <c r="D89" s="4" t="n">
+        <v>367528400</v>
+      </c>
+      <c r="E89" s="4" t="n">
+        <v>2052242343</v>
+      </c>
       <c r="F89" s="4" t="n">
         <v>51919186748</v>
       </c>
@@ -12359,10 +12471,18 @@
           <t>Trong đó: có kỳ hạn</t>
         </is>
       </c>
-      <c r="B90" s="4" t="inlineStr"/>
-      <c r="C90" s="4" t="inlineStr"/>
-      <c r="D90" s="4" t="inlineStr"/>
-      <c r="E90" s="4" t="inlineStr"/>
+      <c r="B90" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C90" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D90" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="F90" s="4" t="n">
         <v>0</v>
       </c>
@@ -12382,10 +12502,18 @@
           <t>Các khoản tương đương tiền</t>
         </is>
       </c>
-      <c r="B91" s="4" t="inlineStr"/>
-      <c r="C91" s="4" t="inlineStr"/>
-      <c r="D91" s="4" t="inlineStr"/>
-      <c r="E91" s="4" t="inlineStr"/>
+      <c r="B91" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C91" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="F91" s="4" t="n">
         <v>0</v>
       </c>
@@ -12405,10 +12533,18 @@
           <t>Ảnh hưởng của thay đổi tỷ giá hối đoái quy đổi ngoại tệ</t>
         </is>
       </c>
-      <c r="B92" s="4" t="inlineStr"/>
-      <c r="C92" s="4" t="inlineStr"/>
-      <c r="D92" s="4" t="inlineStr"/>
-      <c r="E92" s="4" t="inlineStr"/>
+      <c r="B92" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C92" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="F92" s="4" t="n">
         <v>0</v>
       </c>
